--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marin\Desktop\project\readme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE3A837-98D0-405C-AF6C-BDC616F14459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B284C3A9-FC58-4D66-B63D-2D1A95EFC869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기입 안내" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="356">
   <si>
     <t>골든셋 라벨링 킷</t>
   </si>
@@ -643,359 +643,556 @@
     <t>정격 유량계수 (밸브 카탈로그 값). 요구 Cv 와 다름</t>
   </si>
   <si>
+    <t>정상 운전 조건에서 요구되는 Cv. 정격 Cv 와 다르며, 공정조건으로 계산 가능</t>
+  </si>
+  <si>
+    <t>REQ'D FLOW COEFF., CV, NORMAL, REQ'D FLOW COEFF, REQUIRED FLOW COEFFICIENT</t>
+  </si>
+  <si>
+    <t>바디 등급</t>
+  </si>
+  <si>
+    <t>바디 사이즈</t>
+  </si>
+  <si>
+    <t>몸체 재질</t>
+  </si>
+  <si>
+    <t>ACTUATOR FAIL ACTION</t>
+  </si>
+  <si>
+    <t>액추에이터 실패 조치</t>
+  </si>
+  <si>
+    <t>안전</t>
+  </si>
+  <si>
+    <t>FAIL POSITION, FAIL ACTION</t>
+  </si>
+  <si>
+    <t>TYPE NAME</t>
+  </si>
+  <si>
+    <t>밸브 종류. 문서에 항목이 없고 Tag 접두에서 도출 (FV→Flow Control Valve)</t>
+  </si>
+  <si>
+    <t>FLOW CONTROL VALVE</t>
+  </si>
+  <si>
+    <t>EQUIPMENT FULL DESCRIPTION</t>
+  </si>
+  <si>
+    <t>설비 Full Name</t>
+  </si>
+  <si>
+    <t>RECYCLE TO DHC FEED FILTERS</t>
+  </si>
+  <si>
+    <t>APPLICATION</t>
+  </si>
+  <si>
+    <t>FLUID NAME</t>
+  </si>
+  <si>
+    <t>유체 이름</t>
+  </si>
+  <si>
+    <t>FLOWING MEDIA</t>
+  </si>
+  <si>
+    <t>FLUID STATE</t>
+  </si>
+  <si>
+    <t>유체 상태. 문서에 항목이 없고 FLUID NAME 에서 유추</t>
+  </si>
+  <si>
+    <t>NORMAL FLOW RATE</t>
+  </si>
+  <si>
+    <t>정상 유량</t>
+  </si>
+  <si>
+    <t>FLOW RATE</t>
+  </si>
+  <si>
+    <t>NORMAL PRESSURE</t>
+  </si>
+  <si>
+    <t>정상 압력</t>
+  </si>
+  <si>
+    <t>INLET PRESSURE NORMAL</t>
+  </si>
+  <si>
+    <t>NORMAL TEMPERATURE</t>
+  </si>
+  <si>
+    <t>정상 온도. 공정 조건은 모두 Normal 열을 쓴다</t>
+  </si>
+  <si>
+    <t>INLET TEMPERATURE, NORMAL, INLET TEMPERATURE</t>
+  </si>
+  <si>
+    <t>SPECIFIC GRAVITY</t>
+  </si>
+  <si>
+    <t>비중</t>
+  </si>
+  <si>
+    <t>VISCOSITY</t>
+  </si>
+  <si>
+    <t>점도</t>
+  </si>
+  <si>
+    <t>VALVE BODY TYPE</t>
+  </si>
+  <si>
+    <t>몸체 형상 (Globe / Angle / Ball 등). 문서에서는 Style 칸의 체크박스</t>
+  </si>
+  <si>
+    <t>STYLE, VALVE STYLE, BODY TYPE, BODY STYLE</t>
+  </si>
+  <si>
+    <t>VALVE LEAKAGE CLASS</t>
+  </si>
+  <si>
+    <t>누설 등급</t>
+  </si>
+  <si>
+    <t>CHARACTERISTIC (TRIM FORM)</t>
+  </si>
+  <si>
+    <t>특성(트림 형태)</t>
+  </si>
+  <si>
+    <t>CHARACTERISTIC</t>
+  </si>
+  <si>
+    <t>VALVE PLUG MATERIAL</t>
+  </si>
+  <si>
+    <t>플러그 재질</t>
+  </si>
+  <si>
+    <t>VALVE CAGE MATERIAL</t>
+  </si>
+  <si>
+    <t>케이지 재질</t>
+  </si>
+  <si>
+    <t>VALVE SEAT MATERIAL</t>
+  </si>
+  <si>
+    <t>시트 재질</t>
+  </si>
+  <si>
+    <t>VALVE STEM MATERIAL</t>
+  </si>
+  <si>
+    <t>스템 재질</t>
+  </si>
+  <si>
+    <t>ACTUATOR TYPE</t>
+  </si>
+  <si>
+    <t>액추에이터 타입</t>
+  </si>
+  <si>
+    <t>POSITIONER MANUFACTURER</t>
+  </si>
+  <si>
+    <t>포지셔너 제조사. 양식 로고·꼬리말에 있을 수 있음</t>
+  </si>
+  <si>
+    <t>POSITIONER MODEL NO.</t>
+  </si>
+  <si>
+    <t>포지셔너 모델 번호</t>
+  </si>
+  <si>
+    <t>10FV011-DATA SHEET_REV1.tif</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-FV-011</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>3"</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA (Note에 현재 Valve의 Body 사용(Model : ED, FISHER라고 써있음)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>667-ED</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model No.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Body Rated Cv</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>600#</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BODY Rating</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BODY Trim Size</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>WC5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATERIAL Body</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACT'N Fail Position</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>HS CRUDE</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIQUID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>123 M3/H</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>40 kgf/cm2G</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>In.Press. NOR</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flow Rate</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fluid</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>271 ℃</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>288 ℃</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temp. NOR</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Body Type</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Body Style</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Globe</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLASS 4</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BODY Leakage Spec.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modified Percentage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BODY Characteristic</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUS403</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATERIAL Plug</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATERIAL Retainer or Cage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATERIAL Seat Ring</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>INCONEL</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATERIAL Stem</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIAPHRAGM</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actuator Type</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>4200P</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Positioner Model No.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Masoneilan</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note. 1. 3)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>2003년 Valve Retrofit을 하며 바뀐 데이터 시트가 1페이지에 있음. 해당 시트가 Latest라고 봐야함</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RATED CV</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <t>VALVE COEFFICIENT</t>
-  </si>
-  <si>
-    <t>정상 운전 조건에서 요구되는 Cv. 정격 Cv 와 다르며, 공정조건으로 계산 가능</t>
-  </si>
-  <si>
-    <t>REQ'D FLOW COEFF., CV, NORMAL, REQ'D FLOW COEFF, REQUIRED FLOW COEFFICIENT</t>
-  </si>
-  <si>
-    <t>바디 등급</t>
-  </si>
-  <si>
-    <t>바디 사이즈</t>
-  </si>
-  <si>
-    <t>몸체 재질</t>
-  </si>
-  <si>
-    <t>ACTUATOR FAIL ACTION</t>
-  </si>
-  <si>
-    <t>액추에이터 실패 조치</t>
-  </si>
-  <si>
-    <t>안전</t>
-  </si>
-  <si>
-    <t>FAIL POSITION, FAIL ACTION</t>
-  </si>
-  <si>
-    <t>TYPE NAME</t>
-  </si>
-  <si>
-    <t>밸브 종류. 문서에 항목이 없고 Tag 접두에서 도출 (FV→Flow Control Valve)</t>
-  </si>
-  <si>
-    <t>FLOW CONTROL VALVE</t>
-  </si>
-  <si>
-    <t>EQUIPMENT FULL DESCRIPTION</t>
-  </si>
-  <si>
-    <t>설비 Full Name</t>
-  </si>
-  <si>
-    <t>RECYCLE TO DHC FEED FILTERS</t>
-  </si>
-  <si>
-    <t>APPLICATION</t>
-  </si>
-  <si>
-    <t>FLUID NAME</t>
-  </si>
-  <si>
-    <t>유체 이름</t>
-  </si>
-  <si>
-    <t>FLOWING MEDIA</t>
-  </si>
-  <si>
-    <t>FLUID STATE</t>
-  </si>
-  <si>
-    <t>유체 상태. 문서에 항목이 없고 FLUID NAME 에서 유추</t>
-  </si>
-  <si>
-    <t>NORMAL FLOW RATE</t>
-  </si>
-  <si>
-    <t>정상 유량</t>
-  </si>
-  <si>
-    <t>FLOW RATE</t>
-  </si>
-  <si>
-    <t>NORMAL PRESSURE</t>
-  </si>
-  <si>
-    <t>정상 압력</t>
-  </si>
-  <si>
-    <t>INLET PRESSURE NORMAL</t>
-  </si>
-  <si>
-    <t>NORMAL TEMPERATURE</t>
-  </si>
-  <si>
-    <t>정상 온도. 공정 조건은 모두 Normal 열을 쓴다</t>
-  </si>
-  <si>
-    <t>INLET TEMPERATURE, NORMAL, INLET TEMPERATURE</t>
-  </si>
-  <si>
-    <t>SPECIFIC GRAVITY</t>
-  </si>
-  <si>
-    <t>비중</t>
-  </si>
-  <si>
-    <t>VISCOSITY</t>
-  </si>
-  <si>
-    <t>점도</t>
-  </si>
-  <si>
-    <t>VALVE BODY TYPE</t>
-  </si>
-  <si>
-    <t>몸체 형상 (Globe / Angle / Ball 등). 문서에서는 Style 칸의 체크박스</t>
-  </si>
-  <si>
-    <t>STYLE, VALVE STYLE, BODY TYPE, BODY STYLE</t>
-  </si>
-  <si>
-    <t>VALVE LEAKAGE CLASS</t>
-  </si>
-  <si>
-    <t>누설 등급</t>
-  </si>
-  <si>
-    <t>CHARACTERISTIC (TRIM FORM)</t>
-  </si>
-  <si>
-    <t>특성(트림 형태)</t>
-  </si>
-  <si>
-    <t>CHARACTERISTIC</t>
-  </si>
-  <si>
-    <t>VALVE PLUG MATERIAL</t>
-  </si>
-  <si>
-    <t>플러그 재질</t>
-  </si>
-  <si>
-    <t>VALVE CAGE MATERIAL</t>
-  </si>
-  <si>
-    <t>케이지 재질</t>
-  </si>
-  <si>
-    <t>VALVE SEAT MATERIAL</t>
-  </si>
-  <si>
-    <t>시트 재질</t>
-  </si>
-  <si>
-    <t>VALVE STEM MATERIAL</t>
-  </si>
-  <si>
-    <t>스템 재질</t>
-  </si>
-  <si>
-    <t>ACTUATOR TYPE</t>
-  </si>
-  <si>
-    <t>액추에이터 타입</t>
-  </si>
-  <si>
-    <t>POSITIONER MANUFACTURER</t>
-  </si>
-  <si>
-    <t>포지셔너 제조사. 양식 로고·꼬리말에 있을 수 있음</t>
-  </si>
-  <si>
-    <t>POSITIONER MODEL NO.</t>
-  </si>
-  <si>
-    <t>포지셔너 모델 번호</t>
-  </si>
-  <si>
-    <t>10FV011-DATA SHEET_REV1.tif</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-FV-011</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>3"</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA (Note에 현재 Valve의 Body 사용(Model : ED, FISHER라고 써있음)</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>667-ED</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model No.</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Body Rated Cv</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Calculated Cv</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>600#</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>BODY Rating</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>BODY Trim Size</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>WC5</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATERIAL Body</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACT'N Fail Position</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>HS CRUDE</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIQUID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>123 M3/H</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>40 kgf/cm2G</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>In.Press. NOR</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flow Rate</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fluid</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>271 ℃</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>288 ℃</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Temp. NOR</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>GLOBE</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Body Type</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Body Style</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Globe</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLASS 4</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>BODY Leakage Spec.</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Modified Percentage</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>BODY Characteristic</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUS403</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATERIAL Plug</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATERIAL Retainer or Cage</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATERIAL Seat Ring</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>INCONEL</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATERIAL Stem</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>DIAPHRAGM</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Actuator Type</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>4200P</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Positioner Model No.</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Masoneilan</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note. 1. 3)</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>2003년 Valve Retrofit을 하며 바뀐 데이터 시트가 1페이지에 있음. 해당 시트가 Latest라고 봐야함</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10FV079-DATA SHEET_REV2.xlsx</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>xlsx</t>
+  </si>
+  <si>
+    <t>현행</t>
+  </si>
+  <si>
+    <t>datasheet_embedded</t>
+  </si>
+  <si>
+    <t>이종수</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-FV-079</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tag Number</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>metso</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA (문서 좌측 상단)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GU-VDR</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model Number</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trim Rated Cv</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Calculated Cv Normal</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Required Cv NOR.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>300#</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>VALVE BODY / BONNET Rating</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1/2"</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>VALVE BODY / BONNET Size</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>A351 CF8M</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>VALVE BODY / BONNET Material</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fail Close</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTUATOR Fail Position</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>WATER</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GENERAL Fluid</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GENERAL Fluid Type</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 M3/H</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>18 kgf/cm2G</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inlet Pressure, NOR.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>142 ℃</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inlet Temperature, NOR.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Density</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>VALVE BODY / BONNET Type</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLASS IV</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>VALVE BODY / BONNET Seat Leakage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>EQ%</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRIM Flow Char.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>316 SST + STELLITE</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRIM Plug Material</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>316 SST</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRIM Retainer / Cage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRIM Seat Ring Material</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>316SST + CR PLATE</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRIM Stem Material</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>PNEUMATIC DIAPHRAGM</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Azbil</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note. 3)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AVP-302</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITIONER Model No. / Mfr.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지가 아닌 Excel Sheet를 기준으로 총 5페이지(5시트) 중 2번 페이지(2번 시트)에 데이터 시트가 있음</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10PV018-REPAIR REPORT_REV1.xlsx</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>xlsm</t>
   </si>
 </sst>
 </file>
@@ -1200,10 +1397,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1807,15 +2004,15 @@
   <dimension ref="A1:BN32"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="1" max="1" width="7.625" customWidth="1"/>
+    <col min="2" max="2" width="27.9375" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="9.0625" customWidth="1"/>
+    <col min="5" max="5" width="11.8125" customWidth="1"/>
+    <col min="6" max="6" width="8.375" customWidth="1"/>
+    <col min="7" max="7" width="9.0625" customWidth="1"/>
+    <col min="8" max="8" width="7.5625" customWidth="1"/>
+    <col min="9" max="9" width="5.3125" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
@@ -1903,42 +2100,42 @@
       <c r="I1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="21" t="s">
+      <c r="K1" s="21"/>
+      <c r="L1" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21" t="s">
+      <c r="M1" s="20"/>
+      <c r="N1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21" t="s">
+      <c r="O1" s="20"/>
+      <c r="P1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21" t="s">
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21" t="s">
+      <c r="S1" s="20"/>
+      <c r="T1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21" t="s">
+      <c r="U1" s="20"/>
+      <c r="V1" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21" t="s">
+      <c r="W1" s="20"/>
+      <c r="X1" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="20" t="s">
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AA1" s="20"/>
+      <c r="AA1" s="21"/>
       <c r="AB1" s="19" t="s">
         <v>64</v>
       </c>
@@ -2356,10 +2553,10 @@
         <v>118</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AV3" s="13" t="s">
         <v>130</v>
@@ -2554,10 +2751,10 @@
         <v>118</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AU4" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AV4" s="13" t="s">
         <v>130</v>
@@ -2734,7 +2931,7 @@
         <v>126</v>
       </c>
       <c r="AN5" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AO5" s="13" t="s">
         <v>128</v>
@@ -2752,10 +2949,10 @@
         <v>118</v>
       </c>
       <c r="AT5" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AU5" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AV5" s="13" t="s">
         <v>130</v>
@@ -2818,7 +3015,7 @@
         <v>162</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>97</v>
@@ -2842,7 +3039,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>102</v>
@@ -2851,49 +3048,49 @@
         <v>103</v>
       </c>
       <c r="M6" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="N6" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="O6" s="13" t="s">
         <v>264</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>265</v>
       </c>
       <c r="P6" s="13">
         <v>95</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R6" s="13">
         <v>26.53</v>
       </c>
       <c r="S6" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="T6" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="U6" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="T6" s="13" t="s">
+      <c r="V6" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="W6" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="U6" s="13" t="s">
+      <c r="X6" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="V6" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="W6" s="13" t="s">
+      <c r="Y6" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="X6" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y6" s="13" t="s">
-        <v>272</v>
       </c>
       <c r="Z6" s="13" t="s">
         <v>161</v>
       </c>
       <c r="AA6" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AB6" s="13" t="s">
         <v>116</v>
@@ -2908,189 +3105,327 @@
         <v>118</v>
       </c>
       <c r="AF6" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AG6" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AH6" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AI6" s="13" t="s">
         <v>122</v>
       </c>
       <c r="AJ6" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="AK6" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="AL6" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="AM6" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="AK6" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="AL6" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="AM6" s="13" t="s">
-        <v>278</v>
-      </c>
       <c r="AN6" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="AO6" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="AP6" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="AO6" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="AP6" s="13" t="s">
-        <v>284</v>
-      </c>
       <c r="AQ6" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AR6" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AS6" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AT6" s="13" t="s">
         <v>285</v>
       </c>
       <c r="AU6" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="AV6" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="AV6" s="13" t="s">
+      <c r="AW6" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="AX6" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY6" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="AW6" s="13" t="s">
+      <c r="AZ6" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="AX6" s="13" t="s">
+      <c r="BA6" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="AY6" s="13" t="s">
+      <c r="BB6" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="BC6" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="AZ6" s="13" t="s">
+      <c r="BD6" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="BE6" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="BA6" s="13" t="s">
+      <c r="BF6" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="BB6" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="BC6" s="13" t="s">
+      <c r="BG6" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="BD6" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="BE6" s="13" t="s">
+      <c r="BH6" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="BF6" s="13" t="s">
+      <c r="BI6" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="BG6" s="13" t="s">
+      <c r="BJ6" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="BK6" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="BL6" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="BH6" s="13" t="s">
+      <c r="BM6" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="BI6" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="BJ6" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="BK6" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="BL6" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="BM6" s="13" t="s">
+      <c r="BN6" s="13" t="s">
         <v>302</v>
-      </c>
-      <c r="BN6" s="13" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:66" x14ac:dyDescent="0.6">
       <c r="A7" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="13"/>
-      <c r="AM7" s="13"/>
-      <c r="AN7" s="13"/>
-      <c r="AO7" s="13"/>
-      <c r="AP7" s="13"/>
-      <c r="AQ7" s="13"/>
-      <c r="AR7" s="13"/>
-      <c r="AS7" s="13"/>
-      <c r="AT7" s="13"/>
-      <c r="AU7" s="13"/>
-      <c r="AV7" s="13"/>
-      <c r="AW7" s="13"/>
-      <c r="AX7" s="13"/>
-      <c r="AY7" s="13"/>
-      <c r="AZ7" s="13"/>
-      <c r="BA7" s="13"/>
-      <c r="BB7" s="13"/>
-      <c r="BC7" s="13"/>
-      <c r="BD7" s="13"/>
-      <c r="BE7" s="13"/>
-      <c r="BF7" s="13"/>
-      <c r="BG7" s="13"/>
-      <c r="BH7" s="13"/>
-      <c r="BI7" s="13"/>
-      <c r="BJ7" s="13"/>
-      <c r="BK7" s="13"/>
-      <c r="BL7" s="13"/>
-      <c r="BM7" s="13"/>
-      <c r="BN7" s="13"/>
+      <c r="B7" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="F7" s="12">
+        <v>5</v>
+      </c>
+      <c r="G7" s="12">
+        <v>2</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="I7" s="12">
+        <v>11</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="P7" s="13">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="R7" s="13">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="T7" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="V7" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="W7" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="X7" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z7" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA7" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB7" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC7" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD7" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE7" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF7" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="AG7" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="AH7" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="AI7" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ7" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="AK7" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="AL7" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="AM7" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="AN7" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="AO7" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="AP7" s="13">
+        <v>0.92</v>
+      </c>
+      <c r="AQ7" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="AR7" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="AS7" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="AT7" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="AU7" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="AV7" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="AW7" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="AX7" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="AY7" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="AZ7" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="BA7" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="BB7" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="BC7" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="BD7" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="BE7" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="BF7" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="BG7" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="BH7" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="BI7" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="BJ7" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="BK7" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="BL7" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="BM7" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="BN7" s="13" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.6">
       <c r="A8" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="B8" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>308</v>
+      </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
@@ -4835,6 +5170,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="R1:S1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="BL1:BM1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -4851,18 +5198,6 @@
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="3">
@@ -4965,7 +5300,7 @@
     </row>
     <row r="5" spans="1:6" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A5" s="13" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>202</v>
@@ -4976,7 +5311,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="18" t="s">
-        <v>203</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="47.25" x14ac:dyDescent="0.6">
@@ -4984,13 +5319,13 @@
         <v>59</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.6">
@@ -4998,7 +5333,7 @@
         <v>60</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>191</v>
@@ -5012,7 +5347,7 @@
         <v>61</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>191</v>
@@ -5026,7 +5361,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>191</v>
@@ -5037,74 +5372,74 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A10" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>210</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>191</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A11" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>213</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>214</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>191</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A12" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>216</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>217</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>218</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A13" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>220</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>221</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A14" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>223</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>224</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -5113,52 +5448,52 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A15" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>225</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>226</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A16" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>228</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>229</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A17" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>231</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>232</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>234</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>235</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -5167,10 +5502,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>236</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -5179,10 +5514,10 @@
     </row>
     <row r="20" spans="1:6" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A20" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>238</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>239</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>191</v>
@@ -5190,15 +5525,15 @@
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A21" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>241</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>242</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -5207,10 +5542,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A22" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>243</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>244</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>191</v>
@@ -5218,15 +5553,15 @@
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A23" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>246</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>247</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>191</v>
@@ -5237,10 +5572,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A24" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>248</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>249</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -5249,10 +5584,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A25" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>250</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>251</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>191</v>
@@ -5263,10 +5598,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A26" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="18" t="s">
         <v>252</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>253</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -5275,10 +5610,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A27" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B27" s="18" t="s">
         <v>254</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>255</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>191</v>
@@ -5289,10 +5624,10 @@
     </row>
     <row r="28" spans="1:6" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A28" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>256</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>257</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -5301,10 +5636,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A29" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>258</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>259</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>191</v>

--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -288,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -390,6 +390,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5408,14 +5417,14 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>현행</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>datasheet_embedded</t>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>datasheet</t>
         </is>
       </c>
       <c r="F14" s="23" t="n">
@@ -5429,8 +5438,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I14" s="25" t="n">
-        <v>15</v>
+      <c r="I14" s="40" t="n">
+        <v>12</v>
       </c>
       <c r="J14" s="26" t="inlineStr">
         <is>
@@ -5704,7 +5713,11 @@
           <t>Positioner</t>
         </is>
       </c>
-      <c r="BN14" s="27" t="n"/>
+      <c r="BN14" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 2008</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="38" t="inlineStr">
@@ -5722,7 +5735,7 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t>현행</t>
         </is>
@@ -5743,8 +5756,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I15" s="25" t="n">
-        <v>15</v>
+      <c r="I15" s="40" t="n">
+        <v>9</v>
       </c>
       <c r="J15" s="31" t="inlineStr">
         <is>
@@ -6024,7 +6037,11 @@
           <t>Model No.</t>
         </is>
       </c>
-      <c r="BN15" s="27" t="n"/>
+      <c r="BN15" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 2006</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="38" t="inlineStr">
@@ -6042,7 +6059,7 @@
           <t>pdf(텍스트)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>현행</t>
         </is>
@@ -6063,7 +6080,9 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I16" s="25" t="n"/>
+      <c r="I16" s="40" t="n">
+        <v>9</v>
+      </c>
       <c r="J16" s="31" t="inlineStr">
         <is>
           <t>11-FV-502</t>
@@ -6344,7 +6363,11 @@
           <t>Model #</t>
         </is>
       </c>
-      <c r="BN16" s="27" t="n"/>
+      <c r="BN16" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 2021</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="37" t="inlineStr">
@@ -6362,7 +6385,7 @@
           <t>pdf(텍스트)</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>현행</t>
         </is>
@@ -6381,7 +6404,9 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I17" s="34" t="n"/>
+      <c r="I17" s="41" t="n">
+        <v>4</v>
+      </c>
       <c r="J17" s="27" t="n"/>
       <c r="K17" s="27" t="n"/>
       <c r="L17" s="27" t="n"/>
@@ -6440,7 +6465,7 @@
       <c r="BM17" s="27" t="n"/>
       <c r="BN17" s="27" t="inlineStr">
         <is>
-          <t>제외 · 컨트롤밸브가 아님 — DAMPER ACTUATOR 정비보고서. 표지 'DAMPER ACTUATOR REPAIR REPORT', Model A200 SR, Maker AUTOMAX USA, Body Material ALUMINUM, 행정이 각도(0~90°)인 회전형 액추에이터. Cv·바디등급·트림 항목이 문서에 없음. Triage out_of_scope 표본으로는 유효하므로 행은 유지.</t>
+          <t>제외 · 컨트롤밸브가 아님 — DAMPER ACTUATOR 정비보고서. 표지 'DAMPER ACTUATOR REPAIR REPORT', Model A200 SR, Maker AUTOMAX USA, Body Material ALUMINUM, 행정이 각도(0~90°)인 회전형 액추에이터. Cv·바디등급·트림 항목이 문서에 없음. Triage out_of_scope 표본으로는 유효하므로 행은 유지. · 문서 날짜 2012</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6485,7 @@
           <t>pdf(텍스트)</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="41" t="inlineStr">
         <is>
           <t>현행</t>
         </is>
@@ -6479,7 +6504,9 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I18" s="34" t="n"/>
+      <c r="I18" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="J18" s="27" t="n"/>
       <c r="K18" s="27" t="n"/>
       <c r="L18" s="27" t="n"/>
@@ -6538,7 +6565,7 @@
       <c r="BM18" s="27" t="n"/>
       <c r="BN18" s="27" t="inlineStr">
         <is>
-          <t>제외 · 1파일 2자산(B10-TV-040 / B10-TV-1016) — MVP 는 1파일=1자산 전제. 2007 Honeywell 견적서에 밸브 사양서 2건이 첨부된 형태. Triage out_of_scope 표본으로는 유효하므로 행은 유지.</t>
+          <t>제외 · 1파일 2자산(B10-TV-040 / B10-TV-1016) — MVP 는 1파일=1자산 전제. 2007 Honeywell 견적서에 밸브 사양서 2건이 첨부된 형태. Triage out_of_scope 표본으로는 유효하므로 행은 유지. · 문서 날짜 2007</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6585,7 @@
           <t>tif</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="39" t="inlineStr">
         <is>
           <t>레거시</t>
         </is>
@@ -6579,8 +6606,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I19" s="25" t="n">
-        <v>10</v>
+      <c r="I19" s="40" t="n">
+        <v>3</v>
       </c>
       <c r="J19" s="31" t="inlineStr">
         <is>
@@ -6858,7 +6885,11 @@
           <t>Positioner Type</t>
         </is>
       </c>
-      <c r="BN19" s="27" t="n"/>
+      <c r="BN19" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 1986-09-06</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="38" t="inlineStr">
@@ -6876,7 +6907,7 @@
           <t>tif</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>레거시</t>
         </is>
@@ -6897,8 +6928,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I20" s="25" t="n">
-        <v>10</v>
+      <c r="I20" s="40" t="n">
+        <v>3</v>
       </c>
       <c r="J20" s="31" t="inlineStr">
         <is>
@@ -7178,7 +7209,11 @@
           <t>Positioner Type</t>
         </is>
       </c>
-      <c r="BN20" s="27" t="n"/>
+      <c r="BN20" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 1986-09-06</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="38" t="inlineStr">
@@ -7196,7 +7231,7 @@
           <t>tif</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr">
         <is>
           <t>레거시</t>
         </is>
@@ -7217,8 +7252,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I21" s="25" t="n">
-        <v>5</v>
+      <c r="I21" s="40" t="n">
+        <v>3</v>
       </c>
       <c r="J21" s="31" t="inlineStr">
         <is>
@@ -7498,7 +7533,11 @@
           <t>Positioner Type</t>
         </is>
       </c>
-      <c r="BN21" s="27" t="n"/>
+      <c r="BN21" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 1986-09-06</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="38" t="inlineStr">
@@ -7516,7 +7555,7 @@
           <t>tif</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>레거시</t>
         </is>
@@ -7537,8 +7576,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I22" s="36" t="n">
-        <v>5</v>
+      <c r="I22" s="40" t="n">
+        <v>3</v>
       </c>
       <c r="J22" s="31" t="inlineStr">
         <is>
@@ -7818,7 +7857,11 @@
           <t>Positioner Type</t>
         </is>
       </c>
-      <c r="BN22" s="27" t="n"/>
+      <c r="BN22" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 1986-09-06</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
@@ -7836,7 +7879,7 @@
           <t>tif</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="39" t="inlineStr">
         <is>
           <t>레거시</t>
         </is>
@@ -7857,8 +7900,8 @@
           <t>서경빈</t>
         </is>
       </c>
-      <c r="I23" s="36" t="n">
-        <v>5</v>
+      <c r="I23" s="40" t="n">
+        <v>3</v>
       </c>
       <c r="J23" s="31" t="inlineStr">
         <is>
@@ -8138,7 +8181,11 @@
           <t>Positioner Type</t>
         </is>
       </c>
-      <c r="BN23" s="27" t="n"/>
+      <c r="BN23" s="27" t="inlineStr">
+        <is>
+          <t>문서 날짜 1986-09-06</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">

--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -6029,7 +6029,7 @@
       </c>
       <c r="BL15" s="31" t="inlineStr">
         <is>
-          <t>880-2221</t>
+          <t>YT-1200</t>
         </is>
       </c>
       <c r="BM15" s="31" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="BN15" s="27" t="inlineStr">
         <is>
-          <t>문서 날짜 2006</t>
+          <t>문서 날짜 2006 · 포지셔너 모델 정정 880-2221→YT-1200 (880-2221 은 밸브 모델, SPEC!E9)</t>
         </is>
       </c>
     </row>

--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기입 안내" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'라벨링'!$A$2:$BN$32</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1697,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN37"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8630,14 +8630,14 @@
           <t>Tag</t>
         </is>
       </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
+      <c r="L24" s="37" t="inlineStr">
+        <is>
+          <t>MASONEILAN</t>
         </is>
       </c>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>NA (문서 좌측 상단)</t>
+          <t>NA (문서 하단 MANUFACTURER)</t>
         </is>
       </c>
       <c r="N24" s="13" t="inlineStr">
@@ -9597,6 +9597,2876 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>d036</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>10FV634-DATA SHEET_REV0.pdf</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>pdf(텍스트)</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>10-FV-634</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Valve Tag #</t>
+        </is>
+      </c>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>FLOWSERVE</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N38" s="13" t="inlineStr">
+        <is>
+          <t>?Mark One</t>
+        </is>
+      </c>
+      <c r="O38" s="13" t="inlineStr">
+        <is>
+          <t>Model / Body Type / Trim Type</t>
+        </is>
+      </c>
+      <c r="P38" s="13" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q38" s="13" t="inlineStr">
+        <is>
+          <t>Trim # - Cv</t>
+        </is>
+      </c>
+      <c r="R38" s="13" t="inlineStr">
+        <is>
+          <t>249.719</t>
+        </is>
+      </c>
+      <c r="S38" s="13" t="inlineStr">
+        <is>
+          <t>Flow Coeff. (Cv)</t>
+        </is>
+      </c>
+      <c r="T38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="U38" s="13" t="inlineStr">
+        <is>
+          <t>Size/Pressure Class/Body Form</t>
+        </is>
+      </c>
+      <c r="V38" s="13" t="inlineStr">
+        <is>
+          <t>8"</t>
+        </is>
+      </c>
+      <c r="W38" s="13" t="inlineStr">
+        <is>
+          <t>Size/Pressure Class/Body Form</t>
+        </is>
+      </c>
+      <c r="X38" s="13" t="inlineStr">
+        <is>
+          <t>Cr-Mo C5; F5a</t>
+        </is>
+      </c>
+      <c r="Y38" s="13" t="inlineStr">
+        <is>
+          <t>Body Matl / Bonnet Matl</t>
+        </is>
+      </c>
+      <c r="Z38" s="13" t="inlineStr">
+        <is>
+          <t>Fail Open</t>
+        </is>
+      </c>
+      <c r="AA38" s="13" t="inlineStr">
+        <is>
+          <t>Fail/Air-To</t>
+        </is>
+      </c>
+      <c r="AB38" s="13" t="inlineStr">
+        <is>
+          <t>Flow Control Valve</t>
+        </is>
+      </c>
+      <c r="AC38" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 FV를 보고 Flow Control Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF38" s="13" t="inlineStr">
+        <is>
+          <t>LS AR / LIQUID</t>
+        </is>
+      </c>
+      <c r="AG38" s="13" t="inlineStr">
+        <is>
+          <t>Process Fluid</t>
+        </is>
+      </c>
+      <c r="AH38" s="13" t="inlineStr">
+        <is>
+          <t>LIQUID</t>
+        </is>
+      </c>
+      <c r="AI38" s="13" t="inlineStr">
+        <is>
+          <t>Process Fluid</t>
+        </is>
+      </c>
+      <c r="AJ38" s="13" t="inlineStr">
+        <is>
+          <t>164332.000 kg/h</t>
+        </is>
+      </c>
+      <c r="AK38" s="13" t="inlineStr">
+        <is>
+          <t>Liq Flow Rate (kg/h)</t>
+        </is>
+      </c>
+      <c r="AL38" s="13" t="inlineStr">
+        <is>
+          <t>19.1 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM38" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Press</t>
+        </is>
+      </c>
+      <c r="AN38" s="13" t="inlineStr">
+        <is>
+          <t>291.2 °C</t>
+        </is>
+      </c>
+      <c r="AO38" s="13" t="inlineStr">
+        <is>
+          <t>Temperature (°C)</t>
+        </is>
+      </c>
+      <c r="AP38" s="13" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="AQ38" s="13" t="inlineStr">
+        <is>
+          <t>SG-MW</t>
+        </is>
+      </c>
+      <c r="AR38" s="13" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="AS38" s="13" t="inlineStr">
+        <is>
+          <t>Viscosity (cP)</t>
+        </is>
+      </c>
+      <c r="AT38" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU38" s="13" t="inlineStr">
+        <is>
+          <t>Model / Body Type / Trim Type</t>
+        </is>
+      </c>
+      <c r="AV38" s="13" t="inlineStr">
+        <is>
+          <t>Class IV</t>
+        </is>
+      </c>
+      <c r="AW38" s="13" t="inlineStr">
+        <is>
+          <t>Max Shutoff / Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX38" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENT</t>
+        </is>
+      </c>
+      <c r="AY38" s="13" t="inlineStr">
+        <is>
+          <t>Trim # - Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ38" s="13" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BA38" s="13" t="inlineStr">
+        <is>
+          <t>Plug Mtl/ Facing|Treatment / Stem Cvr</t>
+        </is>
+      </c>
+      <c r="BB38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD38" s="13" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BE38" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring Mtl/ Facing|Treatment</t>
+        </is>
+      </c>
+      <c r="BF38" s="29" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BG38" s="13" t="inlineStr">
+        <is>
+          <t>Stem Mtl/ Facing|Treatment / Pilot Spr</t>
+        </is>
+      </c>
+      <c r="BH38" s="13" t="inlineStr">
+        <is>
+          <t>VL Cylinder</t>
+        </is>
+      </c>
+      <c r="BI38" s="13" t="inlineStr">
+        <is>
+          <t>Act. Type</t>
+        </is>
+      </c>
+      <c r="BJ38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL38" s="13" t="inlineStr">
+        <is>
+          <t>3821-28EA-D41L-0130-00</t>
+        </is>
+      </c>
+      <c r="BM38" s="13" t="inlineStr">
+        <is>
+          <t>Positioner Model #</t>
+        </is>
+      </c>
+      <c r="BN38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>d037</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>10HV010-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>10-HV-010</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M39" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>667-ED</t>
+        </is>
+      </c>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T39" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="U39" s="13" t="inlineStr">
+        <is>
+          <t>Fig. ANSI class</t>
+        </is>
+      </c>
+      <c r="V39" s="13" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W39" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X39" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y39" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="Z39" s="13" t="inlineStr">
+        <is>
+          <t>Fail Close</t>
+        </is>
+      </c>
+      <c r="AA39" s="13" t="inlineStr">
+        <is>
+          <t>Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB39" s="13" t="inlineStr">
+        <is>
+          <t>Hand Valve</t>
+        </is>
+      </c>
+      <c r="AC39" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 HV를 보고 Hand Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF39" s="13" t="inlineStr">
+        <is>
+          <t>S.H. STEAM</t>
+        </is>
+      </c>
+      <c r="AG39" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH39" s="13" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="AI39" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK39" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units</t>
+        </is>
+      </c>
+      <c r="AL39" s="13" t="inlineStr">
+        <is>
+          <t>2.7 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM39" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure</t>
+        </is>
+      </c>
+      <c r="AN39" s="13" t="inlineStr">
+        <is>
+          <t>371 ℃</t>
+        </is>
+      </c>
+      <c r="AO39" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature</t>
+        </is>
+      </c>
+      <c r="AP39" s="13" t="inlineStr">
+        <is>
+          <t>1.196 kg/m3</t>
+        </is>
+      </c>
+      <c r="AQ39" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT39" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU39" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="AV39" s="13" t="inlineStr">
+        <is>
+          <t>ANSI Class IV</t>
+        </is>
+      </c>
+      <c r="AW39" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX39" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENT</t>
+        </is>
+      </c>
+      <c r="AY39" s="13" t="inlineStr">
+        <is>
+          <t>Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ39" s="13" t="inlineStr">
+        <is>
+          <t>316 SST/CoCr-A</t>
+        </is>
+      </c>
+      <c r="BA39" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BB39" s="13" t="inlineStr">
+        <is>
+          <t>17-4PH SST</t>
+        </is>
+      </c>
+      <c r="BC39" s="13" t="inlineStr">
+        <is>
+          <t>Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD39" s="13" t="inlineStr">
+        <is>
+          <t>CAST CoCr-A</t>
+        </is>
+      </c>
+      <c r="BE39" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF39" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH39" s="13" t="inlineStr">
+        <is>
+          <t>Diaph</t>
+        </is>
+      </c>
+      <c r="BI39" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="BJ39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL39" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM39" s="13" t="inlineStr">
+        <is>
+          <t>Positioner Type</t>
+        </is>
+      </c>
+      <c r="BN39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>d038</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>10HV013-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>10-HV-013</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L40" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N40" s="13" t="inlineStr">
+        <is>
+          <t>667-ES</t>
+        </is>
+      </c>
+      <c r="O40" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T40" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="U40" s="13" t="inlineStr">
+        <is>
+          <t>Flg. ANSI Class</t>
+        </is>
+      </c>
+      <c r="V40" s="13" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W40" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X40" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y40" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="Z40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AB40" s="13" t="inlineStr">
+        <is>
+          <t>Hand Valve</t>
+        </is>
+      </c>
+      <c r="AC40" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 HV를 보고 Hand Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF40" s="13" t="inlineStr">
+        <is>
+          <t>M.P. STEAM</t>
+        </is>
+      </c>
+      <c r="AG40" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH40" s="13" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="AI40" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK40" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units</t>
+        </is>
+      </c>
+      <c r="AL40" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM40" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure</t>
+        </is>
+      </c>
+      <c r="AN40" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO40" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature °C</t>
+        </is>
+      </c>
+      <c r="AP40" s="13" t="inlineStr">
+        <is>
+          <t>4.95 kg/m3</t>
+        </is>
+      </c>
+      <c r="AQ40" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT40" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU40" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="AV40" s="13" t="inlineStr">
+        <is>
+          <t>ANSI Class IV</t>
+        </is>
+      </c>
+      <c r="AW40" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX40" s="13" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="AY40" s="13" t="inlineStr">
+        <is>
+          <t>Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ40" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA40" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BB40" s="13" t="inlineStr">
+        <is>
+          <t>316 SST/ENC</t>
+        </is>
+      </c>
+      <c r="BC40" s="13" t="inlineStr">
+        <is>
+          <t>Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD40" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE40" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF40" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH40" s="13" t="inlineStr">
+        <is>
+          <t>Diaph.</t>
+        </is>
+      </c>
+      <c r="BI40" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="BJ40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL40" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM40" s="13" t="inlineStr">
+        <is>
+          <t>Positioner Type</t>
+        </is>
+      </c>
+      <c r="BN40" s="13" t="inlineStr">
+        <is>
+          <t>Fail Close/Open 식별 불가(중복 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>d039</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>10HV014-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>10-HV-014</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N41" s="13" t="inlineStr">
+        <is>
+          <t>667-ED</t>
+        </is>
+      </c>
+      <c r="O41" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T41" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="U41" s="13" t="inlineStr">
+        <is>
+          <t>Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V41" s="13" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="W41" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X41" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y41" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="Z41" s="13" t="inlineStr">
+        <is>
+          <t>Fail Close</t>
+        </is>
+      </c>
+      <c r="AA41" s="13" t="inlineStr">
+        <is>
+          <t>Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB41" s="13" t="inlineStr">
+        <is>
+          <t>Hand Valve</t>
+        </is>
+      </c>
+      <c r="AC41" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 HV를 보고 Hand Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF41" s="13" t="inlineStr">
+        <is>
+          <t>M.P. STEAM</t>
+        </is>
+      </c>
+      <c r="AG41" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH41" s="13" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="AI41" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK41" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units</t>
+        </is>
+      </c>
+      <c r="AL41" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM41" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure</t>
+        </is>
+      </c>
+      <c r="AN41" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO41" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature</t>
+        </is>
+      </c>
+      <c r="AP41" s="13" t="inlineStr">
+        <is>
+          <t>4.96 kg/m3</t>
+        </is>
+      </c>
+      <c r="AQ41" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT41" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU41" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="AV41" s="13" t="inlineStr">
+        <is>
+          <t>ANSI Class IV</t>
+        </is>
+      </c>
+      <c r="AW41" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX41" s="13" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ41" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA41" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BB41" s="13" t="inlineStr">
+        <is>
+          <t>316 SST/ENC</t>
+        </is>
+      </c>
+      <c r="BC41" s="13" t="inlineStr">
+        <is>
+          <t>Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD41" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE41" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF41" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH41" s="13" t="inlineStr">
+        <is>
+          <t>Diaph.</t>
+        </is>
+      </c>
+      <c r="BI41" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="BJ41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK41" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL41" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM41" s="13" t="inlineStr">
+        <is>
+          <t>Positioner Type</t>
+        </is>
+      </c>
+      <c r="BN41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>d040</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>10LV012-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>10-LV-012</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M42" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N42" s="13" t="inlineStr">
+        <is>
+          <t>1051-7600</t>
+        </is>
+      </c>
+      <c r="O42" s="13" t="inlineStr">
+        <is>
+          <t>Size Type and Class</t>
+        </is>
+      </c>
+      <c r="P42" s="13" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q42" s="13" t="inlineStr">
+        <is>
+          <t>Maximum Valve Coefficient, Cv</t>
+        </is>
+      </c>
+      <c r="R42" s="13" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="S42" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cv</t>
+        </is>
+      </c>
+      <c r="T42" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="U42" s="13" t="inlineStr">
+        <is>
+          <t>End Connections, ANSI Class</t>
+        </is>
+      </c>
+      <c r="V42" s="13" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W42" s="13" t="inlineStr">
+        <is>
+          <t>Size Type and Class</t>
+        </is>
+      </c>
+      <c r="X42" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y42" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="Z42" s="13" t="inlineStr">
+        <is>
+          <t>Fail Close</t>
+        </is>
+      </c>
+      <c r="AA42" s="13" t="inlineStr">
+        <is>
+          <t>Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB42" s="13" t="inlineStr">
+        <is>
+          <t>Level Control Valve</t>
+        </is>
+      </c>
+      <c r="AC42" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 LV를 보고 Level Control Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF42" s="13" t="inlineStr">
+        <is>
+          <t>KEROSENE</t>
+        </is>
+      </c>
+      <c r="AG42" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH42" s="13" t="inlineStr">
+        <is>
+          <t>LIQUID</t>
+        </is>
+      </c>
+      <c r="AI42" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ42" s="13" t="inlineStr">
+        <is>
+          <t>102.4 m3/H</t>
+        </is>
+      </c>
+      <c r="AK42" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units</t>
+        </is>
+      </c>
+      <c r="AL42" s="13" t="inlineStr">
+        <is>
+          <t>2.86 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM42" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure</t>
+        </is>
+      </c>
+      <c r="AN42" s="13" t="inlineStr">
+        <is>
+          <t>195 ℃</t>
+        </is>
+      </c>
+      <c r="AO42" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature</t>
+        </is>
+      </c>
+      <c r="AP42" s="13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ42" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV42" s="13" t="inlineStr">
+        <is>
+          <t>ANSI Class I</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX42" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENT</t>
+        </is>
+      </c>
+      <c r="AY42" s="13" t="inlineStr">
+        <is>
+          <t>Trim Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB42" s="13" t="inlineStr">
+        <is>
+          <t>TFE Lined Fiberglass</t>
+        </is>
+      </c>
+      <c r="BC42" s="13" t="inlineStr">
+        <is>
+          <t>Bushing/Bearing Material</t>
+        </is>
+      </c>
+      <c r="BD42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BF42" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH42" s="13" t="inlineStr">
+        <is>
+          <t>Diaph.</t>
+        </is>
+      </c>
+      <c r="BI42" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="BJ42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK42" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL42" s="13" t="inlineStr">
+        <is>
+          <t>3610J</t>
+        </is>
+      </c>
+      <c r="BM42" s="13" t="inlineStr">
+        <is>
+          <t>Positioner Type</t>
+        </is>
+      </c>
+      <c r="BN42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>d041</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>10PCV071-DATA SHEET_REV1.pdf</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>pdf(텍스트)</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>10-PCV-071</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M43" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N43" s="13" t="inlineStr">
+        <is>
+          <t>1098-EGR</t>
+        </is>
+      </c>
+      <c r="O43" s="13" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="P43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>21.119</t>
+        </is>
+      </c>
+      <c r="S43" s="13" t="inlineStr">
+        <is>
+          <t>Sizing Coefficient (Cv)</t>
+        </is>
+      </c>
+      <c r="T43" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="U43" s="13" t="inlineStr">
+        <is>
+          <t>End Connect/In/Out</t>
+        </is>
+      </c>
+      <c r="V43" s="13" t="inlineStr">
+        <is>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="X43" s="13" t="inlineStr">
+        <is>
+          <t>WCC Steel</t>
+        </is>
+      </c>
+      <c r="Y43" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="Z43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AB43" s="13" t="inlineStr">
+        <is>
+          <t>Pressure Control Valve</t>
+        </is>
+      </c>
+      <c r="AC43" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 PV를 보고 Pressure Control Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF43" s="13" t="inlineStr">
+        <is>
+          <t>Fuel GAS</t>
+        </is>
+      </c>
+      <c r="AG43" s="13" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="AH43" s="13" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="AI43" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ43" s="13" t="inlineStr">
+        <is>
+          <t>1730.00000Nm3/h</t>
+        </is>
+      </c>
+      <c r="AK43" s="13" t="inlineStr">
+        <is>
+          <t>Volumetric Flow Rate Gas (Qg)</t>
+        </is>
+      </c>
+      <c r="AL43" s="13" t="inlineStr">
+        <is>
+          <t>2.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM43" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure (P1)</t>
+        </is>
+      </c>
+      <c r="AN43" s="13" t="inlineStr">
+        <is>
+          <t>49  ℃</t>
+        </is>
+      </c>
+      <c r="AO43" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature (T1)</t>
+        </is>
+      </c>
+      <c r="AP43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AR43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS43" s="13" t="inlineStr">
+        <is>
+          <t>Dynamic Viscosity (Mu)</t>
+        </is>
+      </c>
+      <c r="AT43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD43" s="13" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
+      </c>
+      <c r="BE43" s="13" t="inlineStr">
+        <is>
+          <t>Disk/Seat Material:</t>
+        </is>
+      </c>
+      <c r="BF43" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BJ43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL43" s="13" t="inlineStr">
+        <is>
+          <t>?6351</t>
+        </is>
+      </c>
+      <c r="BM43" s="13" t="inlineStr">
+        <is>
+          <t>Pilot Type</t>
+        </is>
+      </c>
+      <c r="BN43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>d042</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>10PDV067-DATA SHEET_REV2.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>datasheet_embedded</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>10-PDV-067</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>Tag No.</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N44" s="13" t="inlineStr">
+        <is>
+          <t>667-EZ</t>
+        </is>
+      </c>
+      <c r="O44" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="P44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T44" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="U44" s="13" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="V44" s="13" t="inlineStr">
+        <is>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="W44" s="13" t="inlineStr">
+        <is>
+          <t>Body Size</t>
+        </is>
+      </c>
+      <c r="X44" s="13" t="inlineStr">
+        <is>
+          <t>A216 Gr-WCB</t>
+        </is>
+      </c>
+      <c r="Y44" s="13" t="inlineStr">
+        <is>
+          <t>Material - Body</t>
+        </is>
+      </c>
+      <c r="Z44" s="13" t="inlineStr">
+        <is>
+          <t>Fail Close</t>
+        </is>
+      </c>
+      <c r="AA44" s="13" t="inlineStr">
+        <is>
+          <t>Fail Position</t>
+        </is>
+      </c>
+      <c r="AB44" s="13" t="inlineStr">
+        <is>
+          <t>Pressure Differential Valve</t>
+        </is>
+      </c>
+      <c r="AC44" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 PDV를 보고 Pressure Differential Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF44" s="13" t="inlineStr">
+        <is>
+          <t>ATOMIZING STEAM</t>
+        </is>
+      </c>
+      <c r="AG44" s="13" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="AH44" s="13" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="AI44" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ44" s="13" t="inlineStr">
+        <is>
+          <t>380 kg/h</t>
+        </is>
+      </c>
+      <c r="AK44" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate</t>
+        </is>
+      </c>
+      <c r="AL44" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM44" s="13" t="inlineStr">
+        <is>
+          <t>In.Press.</t>
+        </is>
+      </c>
+      <c r="AN44" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO44" s="13" t="inlineStr">
+        <is>
+          <t>Temp.</t>
+        </is>
+      </c>
+      <c r="AP44" s="13" t="inlineStr">
+        <is>
+          <t>4.95 kg/m3</t>
+        </is>
+      </c>
+      <c r="AQ44" s="13" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="AR44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT44" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU44" s="13" t="inlineStr">
+        <is>
+          <t>Body Type</t>
+        </is>
+      </c>
+      <c r="AV44" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW44" s="13" t="inlineStr">
+        <is>
+          <t>Leakage Spec.</t>
+        </is>
+      </c>
+      <c r="AX44" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENT</t>
+        </is>
+      </c>
+      <c r="AY44" s="13" t="inlineStr">
+        <is>
+          <t>Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ44" s="13" t="inlineStr">
+        <is>
+          <t>316SST+STELLITE</t>
+        </is>
+      </c>
+      <c r="BA44" s="13" t="inlineStr">
+        <is>
+          <t>Plug</t>
+        </is>
+      </c>
+      <c r="BB44" s="13" t="inlineStr">
+        <is>
+          <t>316SST</t>
+        </is>
+      </c>
+      <c r="BC44" s="13" t="inlineStr">
+        <is>
+          <t>Retainer or Cage</t>
+        </is>
+      </c>
+      <c r="BD44" s="13" t="inlineStr">
+        <is>
+          <t>316 SST+STELLITE</t>
+        </is>
+      </c>
+      <c r="BE44" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring</t>
+        </is>
+      </c>
+      <c r="BF44" s="29" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BG44" s="13" t="inlineStr">
+        <is>
+          <t>Stem</t>
+        </is>
+      </c>
+      <c r="BH44" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI44" s="13" t="inlineStr">
+        <is>
+          <t>Actuator Type</t>
+        </is>
+      </c>
+      <c r="BJ44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK44" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL44" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM44" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="BN44" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>d043</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>10PV031-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>10-PV-031</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M45" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N45" s="13" t="inlineStr">
+        <is>
+          <t>657-ED</t>
+        </is>
+      </c>
+      <c r="O45" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T45" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="U45" s="13" t="inlineStr">
+        <is>
+          <t>Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V45" s="13" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="W45" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X45" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y45" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="Z45" s="13" t="inlineStr">
+        <is>
+          <t>Fail Open</t>
+        </is>
+      </c>
+      <c r="AA45" s="13" t="inlineStr">
+        <is>
+          <t>Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB45" s="13" t="inlineStr">
+        <is>
+          <t>Pressure Control Valve</t>
+        </is>
+      </c>
+      <c r="AC45" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 PV를 보고 Pressure Control Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF45" s="13" t="inlineStr">
+        <is>
+          <t>M.P. STEAM</t>
+        </is>
+      </c>
+      <c r="AG45" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH45" s="13" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="AI45" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ45" s="13" t="inlineStr">
+        <is>
+          <t>3330 kg/h</t>
+        </is>
+      </c>
+      <c r="AK45" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units</t>
+        </is>
+      </c>
+      <c r="AL45" s="13" t="inlineStr">
+        <is>
+          <t>12.9 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM45" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure</t>
+        </is>
+      </c>
+      <c r="AN45" s="13" t="inlineStr">
+        <is>
+          <t>194 ℃</t>
+        </is>
+      </c>
+      <c r="AO45" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature</t>
+        </is>
+      </c>
+      <c r="AP45" s="13" t="inlineStr">
+        <is>
+          <t>6.97 kg/m3</t>
+        </is>
+      </c>
+      <c r="AQ45" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT45" s="13" t="inlineStr">
+        <is>
+          <t>Globe</t>
+        </is>
+      </c>
+      <c r="AU45" s="13" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="AV45" s="13" t="inlineStr">
+        <is>
+          <t>ANSI Class II</t>
+        </is>
+      </c>
+      <c r="AW45" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX45" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENT</t>
+        </is>
+      </c>
+      <c r="AY45" s="13" t="inlineStr">
+        <is>
+          <t>Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ45" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA45" s="13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="BB45" s="13" t="inlineStr">
+        <is>
+          <t>17-4PH SST</t>
+        </is>
+      </c>
+      <c r="BC45" s="13" t="inlineStr">
+        <is>
+          <t>Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE45" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF45" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH45" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI45" s="13" t="inlineStr">
+        <is>
+          <t>Actuator - Style</t>
+        </is>
+      </c>
+      <c r="BJ45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK45" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL45" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM45" s="13" t="inlineStr">
+        <is>
+          <t>Positioner - Type</t>
+        </is>
+      </c>
+      <c r="BN45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>d044</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>10PV081-DATA SHEET_REV2.pdf</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>pdf(텍스트)</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>datasheet_embedded</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>AI초안(Claude)</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>10-PV-081</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Tag Number</t>
+        </is>
+      </c>
+      <c r="L46" s="13" t="inlineStr">
+        <is>
+          <t>VALSTONE</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="inlineStr">
+        <is>
+          <t>(우측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N46" s="13" t="inlineStr">
+        <is>
+          <t>680-4122</t>
+        </is>
+      </c>
+      <c r="O46" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="P46" s="13" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="Q46" s="13" t="inlineStr">
+        <is>
+          <t>Rated Cv</t>
+        </is>
+      </c>
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="S46" s="13" t="inlineStr">
+        <is>
+          <t>Calculated Cv</t>
+        </is>
+      </c>
+      <c r="T46" s="13" t="inlineStr">
+        <is>
+          <t>ANSI CLASS 300</t>
+        </is>
+      </c>
+      <c r="U46" s="13" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="V46" s="13" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="W46" s="13" t="inlineStr">
+        <is>
+          <t>Body Size</t>
+        </is>
+      </c>
+      <c r="X46" s="13" t="inlineStr">
+        <is>
+          <t>A216 Gr.-WCB</t>
+        </is>
+      </c>
+      <c r="Y46" s="13" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="Z46" s="13" t="inlineStr">
+        <is>
+          <t>FAIL OPEN</t>
+        </is>
+      </c>
+      <c r="AA46" s="13" t="inlineStr">
+        <is>
+          <t>Fail Position</t>
+        </is>
+      </c>
+      <c r="AB46" s="13" t="inlineStr">
+        <is>
+          <t>Pressure Control Valve</t>
+        </is>
+      </c>
+      <c r="AC46" s="13" t="inlineStr">
+        <is>
+          <t>NA (Tag에서 PV를 보고 Pressure Control Valve임을 유추)</t>
+        </is>
+      </c>
+      <c r="AD46" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE46" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF46" s="13" t="inlineStr">
+        <is>
+          <t>HS CRUDE</t>
+        </is>
+      </c>
+      <c r="AG46" s="13" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="AH46" s="13" t="inlineStr">
+        <is>
+          <t>LIQUID</t>
+        </is>
+      </c>
+      <c r="AI46" s="13" t="inlineStr">
+        <is>
+          <t>NA (FLUID NAME을 보고 유추)</t>
+        </is>
+      </c>
+      <c r="AJ46" s="13" t="inlineStr">
+        <is>
+          <t>553 m3/hr</t>
+        </is>
+      </c>
+      <c r="AK46" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate</t>
+        </is>
+      </c>
+      <c r="AL46" s="13" t="inlineStr">
+        <is>
+          <t>12 kg/cm2</t>
+        </is>
+      </c>
+      <c r="AM46" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Press.</t>
+        </is>
+      </c>
+      <c r="AN46" s="13" t="inlineStr">
+        <is>
+          <t>143 ℃</t>
+        </is>
+      </c>
+      <c r="AO46" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temp.</t>
+        </is>
+      </c>
+      <c r="AP46" s="13" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AQ46" s="13" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="AR46" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS46" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT46" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>Body Type</t>
+        </is>
+      </c>
+      <c r="AV46" s="13" t="inlineStr">
+        <is>
+          <t>ANSI CLASS 3</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>Leakage Spec.</t>
+        </is>
+      </c>
+      <c r="AX46" s="13" t="inlineStr">
+        <is>
+          <t>EQ%</t>
+        </is>
+      </c>
+      <c r="AY46" s="13" t="inlineStr">
+        <is>
+          <t>Flow Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ46" s="13" t="inlineStr">
+        <is>
+          <t>630SST</t>
+        </is>
+      </c>
+      <c r="BA46" s="13" t="inlineStr">
+        <is>
+          <t>Plug</t>
+        </is>
+      </c>
+      <c r="BB46" s="13" t="inlineStr">
+        <is>
+          <t>630SST</t>
+        </is>
+      </c>
+      <c r="BC46" s="13" t="inlineStr">
+        <is>
+          <t>Cage</t>
+        </is>
+      </c>
+      <c r="BD46" s="13" t="inlineStr">
+        <is>
+          <t>410SST</t>
+        </is>
+      </c>
+      <c r="BE46" s="13" t="inlineStr">
+        <is>
+          <t>Seat Ring</t>
+        </is>
+      </c>
+      <c r="BF46" s="29" t="inlineStr">
+        <is>
+          <t>630SST</t>
+        </is>
+      </c>
+      <c r="BG46" s="13" t="inlineStr">
+        <is>
+          <t>Stem</t>
+        </is>
+      </c>
+      <c r="BH46" s="13" t="inlineStr">
+        <is>
+          <t>CYLINDER</t>
+        </is>
+      </c>
+      <c r="BI46" s="13" t="inlineStr">
+        <is>
+          <t>Actuator Type</t>
+        </is>
+      </c>
+      <c r="BJ46" s="13" t="inlineStr">
+        <is>
+          <t>MASONEILAN</t>
+        </is>
+      </c>
+      <c r="BK46" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="BL46" s="13" t="inlineStr">
+        <is>
+          <t>4280E</t>
+        </is>
+      </c>
+      <c r="BM46" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="BN46" s="13" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A2:BN32"/>
   <mergeCells count="28">

--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25mhk\AI_Lesson\조별프로젝트\golden_label\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25mhk\AI_Lesson\조별프로젝트\SNU-HD-POC-01\readme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9873D5-11C0-4675-B536-3B8B4CEB86CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4856F00-8D4C-4529-9A22-143F5692790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1750,9 +1750,6 @@
     <t>10FV634-DATA SHEET_REV0.pdf</t>
   </si>
   <si>
-    <t>AI초안(Claude)</t>
-  </si>
-  <si>
     <t>10-FV-634</t>
   </si>
   <si>
@@ -2613,34 +2610,15 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우측 상단 로고)</t>
-    </r>
+    <t>강민호</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">143 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>℃</t>
-    </r>
+    <t>(우측 상단 로고)</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>143 ℃</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2648,7 +2626,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2741,19 +2719,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2853,7 +2818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2919,8 +2884,20 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2932,11 +2909,29 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4473,10 +4468,10 @@
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="10" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="13" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10" style="38" customWidth="1"/>
+    <col min="7" max="7" width="13" style="38" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="27" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
@@ -4552,130 +4547,130 @@
       <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="33" t="s">
         <v>66</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="27" t="s">
+      <c r="K1" s="29"/>
+      <c r="L1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="25"/>
-      <c r="N1" s="27" t="s">
+      <c r="M1" s="29"/>
+      <c r="N1" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="27" t="s">
+      <c r="O1" s="29"/>
+      <c r="P1" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="27" t="s">
+      <c r="Q1" s="29"/>
+      <c r="R1" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="27" t="s">
+      <c r="S1" s="29"/>
+      <c r="T1" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="25"/>
-      <c r="V1" s="27" t="s">
+      <c r="U1" s="29"/>
+      <c r="V1" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="W1" s="25"/>
-      <c r="X1" s="27" t="s">
+      <c r="W1" s="29"/>
+      <c r="X1" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="26" t="s">
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="24" t="s">
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="24" t="s">
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="24" t="s">
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="24" t="s">
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="24" t="s">
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="AK1" s="25"/>
-      <c r="AL1" s="24" t="s">
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="AM1" s="25"/>
-      <c r="AN1" s="24" t="s">
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="AO1" s="25"/>
-      <c r="AP1" s="24" t="s">
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AQ1" s="25"/>
-      <c r="AR1" s="24" t="s">
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="AS1" s="25"/>
-      <c r="AT1" s="24" t="s">
+      <c r="AS1" s="29"/>
+      <c r="AT1" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="AU1" s="25"/>
-      <c r="AV1" s="24" t="s">
+      <c r="AU1" s="29"/>
+      <c r="AV1" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="25"/>
-      <c r="AX1" s="24" t="s">
+      <c r="AW1" s="29"/>
+      <c r="AX1" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AY1" s="25"/>
-      <c r="AZ1" s="24" t="s">
+      <c r="AY1" s="29"/>
+      <c r="AZ1" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="BA1" s="25"/>
-      <c r="BB1" s="24" t="s">
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="BC1" s="25"/>
-      <c r="BD1" s="24" t="s">
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="BE1" s="25"/>
-      <c r="BF1" s="24" t="s">
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="BG1" s="25"/>
-      <c r="BH1" s="24" t="s">
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="BI1" s="25"/>
-      <c r="BJ1" s="24" t="s">
+      <c r="BI1" s="29"/>
+      <c r="BJ1" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="BK1" s="25"/>
-      <c r="BL1" s="24" t="s">
+      <c r="BK1" s="29"/>
+      <c r="BL1" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="BM1" s="25"/>
+      <c r="BM1" s="29"/>
       <c r="BN1" s="3" t="s">
         <v>95</v>
       </c>
@@ -4696,16 +4691,16 @@
       <c r="E2" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="33" t="s">
         <v>102</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="24" t="s">
         <v>104</v>
       </c>
       <c r="J2" s="15" t="s">
@@ -4896,16 +4891,16 @@
       <c r="E3" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="34">
         <v>4</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="34">
         <v>1</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="25">
         <v>30</v>
       </c>
       <c r="J3" s="11" t="s">
@@ -5068,7 +5063,7 @@
         <v>115</v>
       </c>
       <c r="BK3" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="BL3" s="11" t="s">
         <v>157</v>
@@ -5094,16 +5089,16 @@
       <c r="E4" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="34">
         <v>5</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="34">
         <v>1</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="25">
         <v>15</v>
       </c>
       <c r="J4" s="11" t="s">
@@ -5292,16 +5287,16 @@
       <c r="E5" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="34">
         <v>5</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="34">
         <v>1</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="25">
         <v>5</v>
       </c>
       <c r="J5" s="11" t="s">
@@ -5490,16 +5485,16 @@
       <c r="E6" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="34">
         <v>8</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="34">
         <v>1</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="25">
         <v>30</v>
       </c>
       <c r="J6" s="11" t="s">
@@ -5690,16 +5685,16 @@
       <c r="E7" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="34">
         <v>5</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="34">
         <v>2</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="25">
         <v>11</v>
       </c>
       <c r="J7" s="11" t="s">
@@ -5742,7 +5737,7 @@
         <v>228</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="X7" s="11" t="s">
         <v>229</v>
@@ -5890,16 +5885,16 @@
       <c r="E8" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="34">
         <v>4</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="34">
         <v>3</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="25">
         <v>10</v>
       </c>
       <c r="J8" s="11" t="s">
@@ -5957,7 +5952,7 @@
         <v>268</v>
       </c>
       <c r="AB8" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AC8" s="11" t="s">
         <v>270</v>
@@ -6090,16 +6085,16 @@
       <c r="E9" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="34">
         <v>19</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="34">
         <v>5</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="25">
         <v>10</v>
       </c>
       <c r="J9" s="11" t="s">
@@ -6288,16 +6283,16 @@
       <c r="E10" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="34">
         <v>1</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="34">
         <v>1</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="25">
         <v>10</v>
       </c>
       <c r="J10" s="11" t="s">
@@ -6340,7 +6335,7 @@
         <v>123</v>
       </c>
       <c r="W10" s="19" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="X10" s="11" t="s">
         <v>327</v>
@@ -6488,16 +6483,16 @@
       <c r="E11" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="34">
         <v>3</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="34">
         <v>1</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="25">
         <v>10</v>
       </c>
       <c r="J11" s="11" t="s">
@@ -6688,16 +6683,16 @@
       <c r="E12" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="34">
         <v>5</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="34">
         <v>2</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="25">
         <v>10</v>
       </c>
       <c r="J12" s="11" t="s">
@@ -6740,7 +6735,7 @@
         <v>185</v>
       </c>
       <c r="W12" s="19" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="X12" s="11" t="s">
         <v>387</v>
@@ -6758,7 +6753,7 @@
         <v>269</v>
       </c>
       <c r="AC12" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="AD12" s="11" t="s">
         <v>130</v>
@@ -6886,16 +6881,16 @@
       <c r="E13" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="34">
         <v>1</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="34">
         <v>1</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="25">
         <v>10</v>
       </c>
       <c r="J13" s="11" t="s">
@@ -7084,16 +7079,16 @@
       <c r="E14" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="34">
         <v>3</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="34">
         <v>2</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="25">
         <v>15</v>
       </c>
       <c r="J14" s="11" t="s">
@@ -7278,16 +7273,16 @@
       <c r="E15" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="34">
         <v>2</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="34">
         <v>2</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="25">
         <v>15</v>
       </c>
       <c r="J15" s="11" t="s">
@@ -7476,16 +7471,16 @@
       <c r="E16" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="34">
         <v>1</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="34">
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="25">
         <v>15</v>
       </c>
       <c r="J16" s="11" t="s">
@@ -7674,16 +7669,16 @@
       <c r="E17" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="35">
         <v>4</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="35">
         <v>2</v>
       </c>
       <c r="H17" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="25">
         <v>30</v>
       </c>
       <c r="J17" s="11" t="s">
@@ -7838,14 +7833,14 @@
       <c r="E18" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="36">
         <v>7</v>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="36"/>
       <c r="H18" s="22" t="s">
         <v>422</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="25">
         <v>30</v>
       </c>
       <c r="J18" s="11"/>
@@ -7924,16 +7919,16 @@
       <c r="E19" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="34">
         <v>5</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="37">
         <v>1</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="25">
         <v>10</v>
       </c>
       <c r="J19" s="11" t="s">
@@ -8015,7 +8010,7 @@
         <v>134</v>
       </c>
       <c r="AJ19" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AK19" s="11" t="s">
         <v>513</v>
@@ -8096,13 +8091,13 @@
         <v>115</v>
       </c>
       <c r="BK19" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="BL19" s="11" t="s">
         <v>524</v>
       </c>
       <c r="BM19" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="BN19" s="11"/>
     </row>
@@ -8122,16 +8117,16 @@
       <c r="E20" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="34">
         <v>5</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="37">
         <v>1</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="25">
         <v>10</v>
       </c>
       <c r="J20" s="11" t="s">
@@ -8183,7 +8178,7 @@
         <v>511</v>
       </c>
       <c r="Z20" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AA20" s="11" t="s">
         <v>127</v>
@@ -8216,7 +8211,7 @@
         <v>532</v>
       </c>
       <c r="AK20" s="11" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AL20" s="11" t="s">
         <v>533</v>
@@ -8294,7 +8289,7 @@
         <v>115</v>
       </c>
       <c r="BK20" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="BL20" s="11" t="s">
         <v>157</v>
@@ -8320,16 +8315,16 @@
       <c r="E21" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="34">
         <v>5</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="37">
         <v>1</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="25">
         <v>5</v>
       </c>
       <c r="J21" s="11" t="s">
@@ -8381,7 +8376,7 @@
         <v>511</v>
       </c>
       <c r="Z21" s="11" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AA21" s="11" t="s">
         <v>127</v>
@@ -8417,7 +8412,7 @@
         <v>513</v>
       </c>
       <c r="AL21" s="11" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AM21" s="11" t="s">
         <v>373</v>
@@ -8492,7 +8487,7 @@
         <v>115</v>
       </c>
       <c r="BK21" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="BL21" s="11" t="s">
         <v>157</v>
@@ -8518,16 +8513,16 @@
       <c r="E22" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="34">
         <v>5</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="37">
         <v>1</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="25">
         <v>5</v>
       </c>
       <c r="J22" s="11" t="s">
@@ -8540,7 +8535,7 @@
         <v>115</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="N22" s="11" t="s">
         <v>507</v>
@@ -8606,7 +8601,7 @@
         <v>133</v>
       </c>
       <c r="AI22" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AJ22" s="11" t="s">
         <v>550</v>
@@ -8621,7 +8616,7 @@
         <v>373</v>
       </c>
       <c r="AN22" s="11" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AO22" s="11" t="s">
         <v>375</v>
@@ -8651,7 +8646,7 @@
         <v>145</v>
       </c>
       <c r="AX22" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AY22" s="11" t="s">
         <v>520</v>
@@ -8690,7 +8685,7 @@
         <v>115</v>
       </c>
       <c r="BK22" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="BL22" s="11" t="s">
         <v>157</v>
@@ -8716,16 +8711,16 @@
       <c r="E23" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="34">
         <v>5</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="37">
         <v>1</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="25">
         <v>5</v>
       </c>
       <c r="J23" s="11" t="s">
@@ -8735,7 +8730,7 @@
         <v>114</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>506</v>
@@ -8786,7 +8781,7 @@
         <v>128</v>
       </c>
       <c r="AC23" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD23" s="11" t="s">
         <v>130</v>
@@ -8813,13 +8808,13 @@
         <v>513</v>
       </c>
       <c r="AL23" s="11" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AM23" s="11" t="s">
         <v>373</v>
       </c>
       <c r="AN23" s="11" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AO23" s="11" t="s">
         <v>375</v>
@@ -8837,7 +8832,7 @@
         <v>130</v>
       </c>
       <c r="AT23" s="11" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AU23" s="11" t="s">
         <v>517</v>
@@ -8888,7 +8883,7 @@
         <v>115</v>
       </c>
       <c r="BK23" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="BL23" s="11" t="s">
         <v>157</v>
@@ -8898,1972 +8893,1984 @@
       </c>
       <c r="BN23" s="11"/>
     </row>
-    <row r="24" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A24" s="28" t="s">
+    <row r="24" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A24" s="19" t="s">
         <v>562</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="19" t="s">
         <v>563</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="19">
         <v>1</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="19">
         <v>1</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I24" s="26">
+        <v>35</v>
+      </c>
+      <c r="J24" s="19" t="s">
         <v>564</v>
       </c>
-      <c r="I24" s="28">
-        <v>35</v>
-      </c>
-      <c r="J24" s="28" t="s">
+      <c r="K24" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>712</v>
+      </c>
+      <c r="O24" s="19" t="s">
         <v>565</v>
       </c>
-      <c r="K24" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="M24" s="28" t="s">
+      <c r="P24" s="19">
+        <v>538</v>
+      </c>
+      <c r="Q24" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="R24" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="T24" s="19">
+        <v>300</v>
+      </c>
+      <c r="U24" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="V24" s="19" t="s">
+        <v>717</v>
+      </c>
+      <c r="W24" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="X24" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="Y24" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="Z24" s="19" t="s">
+        <v>719</v>
+      </c>
+      <c r="AA24" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="AB24" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC24" s="19" t="s">
+        <v>720</v>
+      </c>
+      <c r="AD24" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE24" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF24" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="AG24" s="19" t="s">
+        <v>749</v>
+      </c>
+      <c r="AH24" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI24" s="19" t="s">
+        <v>749</v>
+      </c>
+      <c r="AJ24" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="AK24" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="AL24" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="AM24" s="19" t="s">
+        <v>724</v>
+      </c>
+      <c r="AN24" s="19" t="s">
+        <v>725</v>
+      </c>
+      <c r="AO24" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="AP24" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="AQ24" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="AR24" s="19">
+        <v>1.7050000000000001</v>
+      </c>
+      <c r="AS24" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="AT24" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="AU24" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="AV24" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="AW24" s="19" t="s">
+        <v>727</v>
+      </c>
+      <c r="AX24" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="AY24" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="AZ24" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="BA24" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="BB24" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BC24" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BD24" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="BE24" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="BF24" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="BG24" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="BH24" s="19" t="s">
+        <v>730</v>
+      </c>
+      <c r="BI24" s="19" t="s">
+        <v>731</v>
+      </c>
+      <c r="BJ24" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK24" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL24" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="BM24" s="19" t="s">
+        <v>775</v>
+      </c>
+      <c r="BN24" s="19"/>
+    </row>
+    <row r="25" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A25" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="19">
+        <v>5</v>
+      </c>
+      <c r="G25" s="19">
+        <v>1</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I25" s="26">
+        <v>20</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>734</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>735</v>
+      </c>
+      <c r="N25" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="O25" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="P25" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="S25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="U25" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="V25" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="W25" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="X25" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y25" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="Z25" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA25" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB25" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="AC25" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="AD25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF25" s="19" t="s">
+        <v>738</v>
+      </c>
+      <c r="AG25" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH25" s="19" t="s">
+        <v>748</v>
+      </c>
+      <c r="AI25" s="19" t="s">
+        <v>721</v>
+      </c>
+      <c r="AJ25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK25" s="19" t="s">
+        <v>776</v>
+      </c>
+      <c r="AL25" s="19" t="s">
+        <v>742</v>
+      </c>
+      <c r="AM25" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN25" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="AO25" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AP25" s="19" t="s">
+        <v>745</v>
+      </c>
+      <c r="AQ25" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS25" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT25" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="AU25" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="AV25" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="AW25" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX25" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="AY25" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="AZ25" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="BA25" s="19" t="s">
+        <v>771</v>
+      </c>
+      <c r="BB25" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="BC25" s="19" t="s">
+        <v>746</v>
+      </c>
+      <c r="BD25" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="BE25" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="BF25" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BG25" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BH25" s="19" t="s">
+        <v>582</v>
+      </c>
+      <c r="BI25" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="BJ25" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK25" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL25" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="BM25" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="BN25" s="19"/>
+    </row>
+    <row r="26" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A26" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="19">
+        <v>5</v>
+      </c>
+      <c r="G26" s="19">
+        <v>1</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I26" s="26">
+        <v>10</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M26" s="19" t="s">
         <v>506</v>
       </c>
-      <c r="N24" s="28" t="s">
-        <v>713</v>
-      </c>
-      <c r="O24" s="28" t="s">
-        <v>566</v>
-      </c>
-      <c r="P24" s="28">
-        <v>538</v>
-      </c>
-      <c r="Q24" s="28" t="s">
-        <v>714</v>
-      </c>
-      <c r="R24" s="28" t="s">
-        <v>567</v>
-      </c>
-      <c r="S24" s="28" t="s">
-        <v>568</v>
-      </c>
-      <c r="T24" s="28">
+      <c r="N26" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="O26" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="P26" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q26" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="R26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="S26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="T26" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="U26" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="V26" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="W26" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="X26" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y26" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="Z26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB26" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="AC26" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="AD26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF26" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="AG26" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH26" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="AI26" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK26" s="19" t="s">
+        <v>776</v>
+      </c>
+      <c r="AL26" s="19" t="s">
+        <v>751</v>
+      </c>
+      <c r="AM26" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN26" s="19" t="s">
+        <v>754</v>
+      </c>
+      <c r="AO26" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP26" s="19" t="s">
+        <v>752</v>
+      </c>
+      <c r="AQ26" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT26" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="AU26" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="AV26" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="AW26" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX26" s="19" t="s">
+        <v>758</v>
+      </c>
+      <c r="AY26" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="AZ26" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA26" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB26" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="BC26" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="BD26" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE26" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="BF26" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BG26" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BH26" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="BI26" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="BJ26" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK26" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL26" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="BM26" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="BN26" s="19" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="27" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A27" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>592</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="19">
+        <v>5</v>
+      </c>
+      <c r="G27" s="19">
+        <v>1</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I27" s="26">
+        <v>10</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>755</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="N27" s="19" t="s">
+        <v>756</v>
+      </c>
+      <c r="O27" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="P27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="S27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="T27" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="U27" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="V27" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="W27" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="X27" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y27" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="Z27" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA27" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB27" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="AC27" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="AD27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF27" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="AG27" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH27" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="AI27" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK27" s="19" t="s">
+        <v>776</v>
+      </c>
+      <c r="AL27" s="19" t="s">
+        <v>751</v>
+      </c>
+      <c r="AM27" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN27" s="19" t="s">
+        <v>754</v>
+      </c>
+      <c r="AO27" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AP27" s="19" t="s">
+        <v>757</v>
+      </c>
+      <c r="AQ27" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT27" s="19" t="s">
+        <v>726</v>
+      </c>
+      <c r="AU27" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="AV27" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="AW27" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX27" s="19" t="s">
+        <v>758</v>
+      </c>
+      <c r="AY27" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="AZ27" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA27" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB27" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="BC27" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="BD27" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE27" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="BF27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BG27" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BH27" s="19" t="s">
+        <v>772</v>
+      </c>
+      <c r="BI27" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="BJ27" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK27" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL27" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="BM27" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="BN27" s="19"/>
+    </row>
+    <row r="28" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A28" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>595</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="19">
+        <v>4</v>
+      </c>
+      <c r="G28" s="19">
+        <v>1</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I28" s="26">
+        <v>15</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>759</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="N28" s="19" t="s">
+        <v>760</v>
+      </c>
+      <c r="O28" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="P28" s="19">
+        <v>357</v>
+      </c>
+      <c r="Q28" s="19" t="s">
+        <v>761</v>
+      </c>
+      <c r="R28" s="19">
+        <v>96.8</v>
+      </c>
+      <c r="S28" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="T28" s="19">
         <v>300</v>
       </c>
-      <c r="U24" s="28" t="s">
-        <v>715</v>
-      </c>
-      <c r="V24" s="28" t="s">
-        <v>718</v>
-      </c>
-      <c r="W24" s="28" t="s">
-        <v>715</v>
-      </c>
-      <c r="X24" s="28" t="s">
-        <v>468</v>
-      </c>
-      <c r="Y24" s="28" t="s">
+      <c r="U28" s="19" t="s">
+        <v>762</v>
+      </c>
+      <c r="V28" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="W28" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="X28" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y28" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="Z28" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA28" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB28" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="AC28" s="19" t="s">
+        <v>764</v>
+      </c>
+      <c r="AD28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF28" s="19" t="s">
+        <v>765</v>
+      </c>
+      <c r="AG28" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH28" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI28" s="19" t="s">
+        <v>721</v>
+      </c>
+      <c r="AJ28" s="19" t="s">
+        <v>770</v>
+      </c>
+      <c r="AK28" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="AL28" s="19" t="s">
+        <v>767</v>
+      </c>
+      <c r="AM28" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN28" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="AO28" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AP28" s="19">
+        <v>0.64</v>
+      </c>
+      <c r="AQ28" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT28" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="AU28" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="AV28" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="AW28" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX28" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="AY28" s="19" t="s">
+        <v>598</v>
+      </c>
+      <c r="AZ28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB28" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="BC28" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="BD28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BE28" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BF28" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BG28" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BH28" s="19" t="s">
+        <v>772</v>
+      </c>
+      <c r="BI28" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="BJ28" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK28" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL28" s="19" t="s">
+        <v>773</v>
+      </c>
+      <c r="BM28" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="BN28" s="19"/>
+    </row>
+    <row r="29" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A29" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="19">
+        <v>3</v>
+      </c>
+      <c r="G29" s="19">
+        <v>1</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I29" s="26">
+        <v>10</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>777</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="N29" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="O29" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="P29" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q29" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="R29" s="19" t="s">
+        <v>605</v>
+      </c>
+      <c r="S29" s="19" t="s">
+        <v>779</v>
+      </c>
+      <c r="T29" s="19">
+        <v>300</v>
+      </c>
+      <c r="U29" s="19" t="s">
+        <v>787</v>
+      </c>
+      <c r="V29" s="19" t="s">
+        <v>786</v>
+      </c>
+      <c r="W29" s="19" t="s">
+        <v>778</v>
+      </c>
+      <c r="X29" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y29" s="19" t="s">
+        <v>771</v>
+      </c>
+      <c r="Z29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB29" s="19" t="s">
+        <v>803</v>
+      </c>
+      <c r="AC29" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF29" s="19" t="s">
+        <v>780</v>
+      </c>
+      <c r="AG29" s="19" t="s">
+        <v>781</v>
+      </c>
+      <c r="AH29" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="AI29" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ29" s="19" t="s">
+        <v>782</v>
+      </c>
+      <c r="AK29" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="AL29" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="AM29" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="AN29" s="19" t="s">
+        <v>785</v>
+      </c>
+      <c r="AO29" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="AP29" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="AQ29" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="AR29" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="AT29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AU29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BC29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BD29" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="BE29" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="BF29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BG29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BH29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BI29" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BJ29" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK29" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL29" s="19" t="s">
+        <v>789</v>
+      </c>
+      <c r="BM29" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="BN29" s="19"/>
+    </row>
+    <row r="30" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A30" s="19" t="s">
+        <v>610</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" s="19">
+        <v>3</v>
+      </c>
+      <c r="G30" s="19">
+        <v>2</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I30" s="26">
+        <v>10</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="O30" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="P30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="R30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="S30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="T30" s="19">
+        <v>300</v>
+      </c>
+      <c r="U30" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="V30" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="W30" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="X30" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y30" s="19" t="s">
+        <v>792</v>
+      </c>
+      <c r="Z30" s="19" t="s">
+        <v>736</v>
+      </c>
+      <c r="AA30" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB30" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="AC30" s="19" t="s">
+        <v>796</v>
+      </c>
+      <c r="AD30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF30" s="19" t="s">
+        <v>793</v>
+      </c>
+      <c r="AG30" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="AH30" s="19" t="s">
+        <v>781</v>
+      </c>
+      <c r="AI30" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ30" s="19" t="s">
+        <v>797</v>
+      </c>
+      <c r="AK30" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL30" s="19" t="s">
+        <v>751</v>
+      </c>
+      <c r="AM30" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="AN30" s="19" t="s">
+        <v>754</v>
+      </c>
+      <c r="AO30" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="AP30" s="19" t="s">
+        <v>752</v>
+      </c>
+      <c r="AQ30" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT30" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="AU30" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AV30" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AW30" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="AX30" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="AY30" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="AZ30" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="BA30" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB30" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="BC30" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="BD30" s="19" t="s">
+        <v>806</v>
+      </c>
+      <c r="BE30" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="BF30" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="BG30" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="BH30" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="BI30" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="BJ30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK30" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BL30" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="BM30" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="BN30" s="19"/>
+    </row>
+    <row r="31" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A31" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="F31" s="19">
+        <v>4</v>
+      </c>
+      <c r="G31" s="19">
+        <v>3</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I31" s="26">
+        <v>10</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>617</v>
+      </c>
+      <c r="N31" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="O31" s="19" t="s">
+        <v>799</v>
+      </c>
+      <c r="P31" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q31" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="R31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="S31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="T31" s="19">
+        <v>300</v>
+      </c>
+      <c r="U31" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="V31" s="19" t="s">
+        <v>800</v>
+      </c>
+      <c r="W31" s="19" t="s">
+        <v>801</v>
+      </c>
+      <c r="X31" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y31" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z31" s="19" t="s">
         <v>719</v>
       </c>
-      <c r="Z24" s="28" t="s">
-        <v>720</v>
-      </c>
-      <c r="AA24" s="28" t="s">
-        <v>569</v>
-      </c>
-      <c r="AB24" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="AC24" s="28" t="s">
+      <c r="AA31" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB31" s="19" t="s">
+        <v>803</v>
+      </c>
+      <c r="AC31" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="AD31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AR31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AU31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV31" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AW31" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="AX31" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="AY31" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="AZ31" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="BA31" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="BB31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BC31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BD31" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE31" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="BF31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BG31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BH31" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="BI31" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="BJ31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK31" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BL31" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="BM31" s="19" t="s">
+        <v>805</v>
+      </c>
+      <c r="BN31" s="19"/>
+    </row>
+    <row r="32" spans="1:66" s="23" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A32" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="19">
+        <v>5</v>
+      </c>
+      <c r="G32" s="19">
+        <v>1</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="I32" s="26">
+        <v>10</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>807</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="N32" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="O32" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="P32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="R32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="S32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="T32" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="U32" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="V32" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="W32" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="X32" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y32" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="Z32" s="19" t="s">
+        <v>719</v>
+      </c>
+      <c r="AA32" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB32" s="19" t="s">
+        <v>803</v>
+      </c>
+      <c r="AC32" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="AD32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF32" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="AG32" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH32" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="AI32" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ32" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="AK32" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="AL32" s="19" t="s">
+        <v>809</v>
+      </c>
+      <c r="AM32" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN32" s="19" t="s">
+        <v>814</v>
+      </c>
+      <c r="AO32" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AP32" s="19" t="s">
+        <v>810</v>
+      </c>
+      <c r="AQ32" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT32" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU32" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="AV32" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="AW32" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX32" s="19" t="s">
+        <v>728</v>
+      </c>
+      <c r="AY32" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="AZ32" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA32" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="BB32" s="19" t="s">
+        <v>811</v>
+      </c>
+      <c r="BC32" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="BD32" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE32" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="BF32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BG32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="BH32" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="BI32" s="19" t="s">
+        <v>813</v>
+      </c>
+      <c r="BJ32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BK32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="BL32" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="BM32" s="19" t="s">
+        <v>812</v>
+      </c>
+      <c r="BN32" s="19"/>
+    </row>
+    <row r="33" spans="1:65" s="32" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A33" s="32" t="s">
+        <v>621</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>622</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="F33" s="32">
+        <v>7</v>
+      </c>
+      <c r="G33" s="32">
+        <v>2</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>816</v>
+      </c>
+      <c r="I33" s="39">
+        <v>10</v>
+      </c>
+      <c r="J33" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="K33" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="L33" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="M33" s="32" t="s">
+        <v>817</v>
+      </c>
+      <c r="N33" s="32" t="s">
+        <v>624</v>
+      </c>
+      <c r="O33" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="P33" s="32" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q33" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="R33" s="32" t="s">
+        <v>626</v>
+      </c>
+      <c r="S33" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="T33" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="U33" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="V33" s="32" t="s">
+        <v>815</v>
+      </c>
+      <c r="W33" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="X33" s="32" t="s">
+        <v>627</v>
+      </c>
+      <c r="Y33" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z33" s="32" t="s">
+        <v>618</v>
+      </c>
+      <c r="AA33" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB33" s="19" t="s">
+        <v>803</v>
+      </c>
+      <c r="AC33" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="AD33" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE33" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF33" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG33" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH33" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI33" s="19" t="s">
         <v>721</v>
       </c>
-      <c r="AD24" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE24" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF24" s="28" t="s">
-        <v>570</v>
-      </c>
-      <c r="AG24" s="28" t="s">
-        <v>750</v>
-      </c>
-      <c r="AH24" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI24" s="28" t="s">
-        <v>750</v>
-      </c>
-      <c r="AJ24" s="28" t="s">
-        <v>723</v>
-      </c>
-      <c r="AK24" s="28" t="s">
-        <v>571</v>
-      </c>
-      <c r="AL24" s="28" t="s">
-        <v>724</v>
-      </c>
-      <c r="AM24" s="28" t="s">
-        <v>725</v>
-      </c>
-      <c r="AN24" s="28" t="s">
-        <v>726</v>
-      </c>
-      <c r="AO24" s="28" t="s">
-        <v>572</v>
-      </c>
-      <c r="AP24" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="AQ24" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="AR24" s="28">
-        <v>1.7050000000000001</v>
-      </c>
-      <c r="AS24" s="28" t="s">
-        <v>573</v>
-      </c>
-      <c r="AT24" s="28" t="s">
-        <v>727</v>
-      </c>
-      <c r="AU24" s="28" t="s">
-        <v>566</v>
-      </c>
-      <c r="AV24" s="28" t="s">
-        <v>340</v>
-      </c>
-      <c r="AW24" s="28" t="s">
-        <v>728</v>
-      </c>
-      <c r="AX24" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="AY24" s="28" t="s">
-        <v>730</v>
-      </c>
-      <c r="AZ24" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="BA24" s="28" t="s">
-        <v>574</v>
-      </c>
-      <c r="BB24" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BC24" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BD24" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="BE24" s="28" t="s">
-        <v>575</v>
-      </c>
-      <c r="BF24" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="BG24" s="28" t="s">
-        <v>576</v>
-      </c>
-      <c r="BH24" s="28" t="s">
-        <v>731</v>
-      </c>
-      <c r="BI24" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="BJ24" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK24" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL24" s="28" t="s">
-        <v>734</v>
-      </c>
-      <c r="BM24" s="28" t="s">
-        <v>776</v>
-      </c>
-      <c r="BN24" s="28"/>
-    </row>
-    <row r="25" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>577</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>578</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="28">
-        <v>5</v>
-      </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I25" s="28">
-        <v>20</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>579</v>
-      </c>
-      <c r="K25" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="L25" s="28" t="s">
-        <v>735</v>
-      </c>
-      <c r="M25" s="28" t="s">
-        <v>736</v>
-      </c>
-      <c r="N25" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="O25" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="P25" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q25" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="R25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="S25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="T25" s="28" t="s">
-        <v>580</v>
-      </c>
-      <c r="U25" s="28" t="s">
-        <v>581</v>
-      </c>
-      <c r="V25" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="W25" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="X25" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y25" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="Z25" s="28" t="s">
-        <v>737</v>
-      </c>
-      <c r="AA25" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB25" s="28" t="s">
-        <v>740</v>
-      </c>
-      <c r="AC25" s="28" t="s">
-        <v>741</v>
-      </c>
-      <c r="AD25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF25" s="28" t="s">
-        <v>739</v>
-      </c>
-      <c r="AG25" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH25" s="28" t="s">
-        <v>749</v>
-      </c>
-      <c r="AI25" s="28" t="s">
-        <v>722</v>
-      </c>
-      <c r="AJ25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK25" s="28" t="s">
-        <v>777</v>
-      </c>
-      <c r="AL25" s="28" t="s">
-        <v>743</v>
-      </c>
-      <c r="AM25" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="AN25" s="28" t="s">
-        <v>745</v>
-      </c>
-      <c r="AO25" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="AP25" s="28" t="s">
-        <v>746</v>
-      </c>
-      <c r="AQ25" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="AR25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT25" s="28" t="s">
-        <v>727</v>
-      </c>
-      <c r="AU25" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="AV25" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="AW25" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX25" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="AY25" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="AZ25" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="BA25" s="28" t="s">
-        <v>772</v>
-      </c>
-      <c r="BB25" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="BC25" s="28" t="s">
-        <v>747</v>
-      </c>
-      <c r="BD25" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="BE25" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="BF25" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BG25" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BH25" s="28" t="s">
-        <v>583</v>
-      </c>
-      <c r="BI25" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="BJ25" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK25" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL25" s="28" t="s">
-        <v>748</v>
-      </c>
-      <c r="BM25" s="28" t="s">
-        <v>775</v>
-      </c>
-      <c r="BN25" s="28"/>
-    </row>
-    <row r="26" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>584</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>585</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="28">
-        <v>5</v>
-      </c>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I26" s="28">
-        <v>10</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>586</v>
-      </c>
-      <c r="K26" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="L26" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="M26" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="N26" s="28" t="s">
-        <v>587</v>
-      </c>
-      <c r="O26" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="P26" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q26" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="R26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="S26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="T26" s="28" t="s">
-        <v>580</v>
-      </c>
-      <c r="U26" s="28" t="s">
-        <v>588</v>
-      </c>
-      <c r="V26" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="W26" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="X26" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y26" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="Z26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB26" s="28" t="s">
-        <v>740</v>
-      </c>
-      <c r="AC26" s="28" t="s">
-        <v>741</v>
-      </c>
-      <c r="AD26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF26" s="28" t="s">
-        <v>589</v>
-      </c>
-      <c r="AG26" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH26" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="AI26" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK26" s="28" t="s">
-        <v>777</v>
-      </c>
-      <c r="AL26" s="28" t="s">
-        <v>752</v>
-      </c>
-      <c r="AM26" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="AN26" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="AO26" s="28" t="s">
-        <v>590</v>
-      </c>
-      <c r="AP26" s="28" t="s">
-        <v>753</v>
-      </c>
-      <c r="AQ26" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="AR26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT26" s="28" t="s">
-        <v>727</v>
-      </c>
-      <c r="AU26" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="AV26" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="AW26" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX26" s="28" t="s">
-        <v>759</v>
-      </c>
-      <c r="AY26" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="AZ26" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA26" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="BB26" s="28" t="s">
-        <v>591</v>
-      </c>
-      <c r="BC26" s="28" t="s">
-        <v>523</v>
-      </c>
-      <c r="BD26" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE26" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="BF26" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BG26" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BH26" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI26" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="BJ26" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK26" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL26" s="28" t="s">
-        <v>748</v>
-      </c>
-      <c r="BM26" s="28" t="s">
-        <v>775</v>
-      </c>
-      <c r="BN26" s="28" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="27" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>592</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>593</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="28">
-        <v>5</v>
-      </c>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I27" s="28">
-        <v>10</v>
-      </c>
-      <c r="J27" s="28" t="s">
-        <v>756</v>
-      </c>
-      <c r="K27" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="L27" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="M27" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="N27" s="28" t="s">
-        <v>757</v>
-      </c>
-      <c r="O27" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="P27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="R27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="S27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="T27" s="28" t="s">
-        <v>580</v>
-      </c>
-      <c r="U27" s="28" t="s">
-        <v>594</v>
-      </c>
-      <c r="V27" s="28" t="s">
-        <v>428</v>
-      </c>
-      <c r="W27" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="X27" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y27" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="Z27" s="28" t="s">
-        <v>737</v>
-      </c>
-      <c r="AA27" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB27" s="28" t="s">
-        <v>740</v>
-      </c>
-      <c r="AC27" s="28" t="s">
-        <v>741</v>
-      </c>
-      <c r="AD27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF27" s="28" t="s">
-        <v>589</v>
-      </c>
-      <c r="AG27" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH27" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="AI27" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK27" s="28" t="s">
-        <v>777</v>
-      </c>
-      <c r="AL27" s="28" t="s">
-        <v>752</v>
-      </c>
-      <c r="AM27" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="AN27" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="AO27" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="AP27" s="28" t="s">
-        <v>758</v>
-      </c>
-      <c r="AQ27" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="AR27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT27" s="28" t="s">
-        <v>727</v>
-      </c>
-      <c r="AU27" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="AV27" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="AW27" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX27" s="28" t="s">
-        <v>759</v>
-      </c>
-      <c r="AY27" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="AZ27" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA27" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="BB27" s="28" t="s">
-        <v>591</v>
-      </c>
-      <c r="BC27" s="28" t="s">
-        <v>523</v>
-      </c>
-      <c r="BD27" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE27" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="BF27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BG27" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BH27" s="28" t="s">
-        <v>773</v>
-      </c>
-      <c r="BI27" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="BJ27" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK27" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL27" s="28" t="s">
-        <v>748</v>
-      </c>
-      <c r="BM27" s="28" t="s">
-        <v>775</v>
-      </c>
-      <c r="BN27" s="28"/>
-    </row>
-    <row r="28" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>595</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>596</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="28">
-        <v>4</v>
-      </c>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I28" s="28">
-        <v>15</v>
-      </c>
-      <c r="J28" s="28" t="s">
-        <v>760</v>
-      </c>
-      <c r="K28" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="L28" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="M28" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="N28" s="28" t="s">
-        <v>761</v>
-      </c>
-      <c r="O28" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="P28" s="28">
-        <v>357</v>
-      </c>
-      <c r="Q28" s="28" t="s">
-        <v>762</v>
-      </c>
-      <c r="R28" s="28">
-        <v>96.8</v>
-      </c>
-      <c r="S28" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="T28" s="28">
-        <v>300</v>
-      </c>
-      <c r="U28" s="28" t="s">
-        <v>763</v>
-      </c>
-      <c r="V28" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="W28" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="X28" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y28" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="Z28" s="28" t="s">
-        <v>737</v>
-      </c>
-      <c r="AA28" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB28" s="28" t="s">
-        <v>764</v>
-      </c>
-      <c r="AC28" s="28" t="s">
-        <v>765</v>
-      </c>
-      <c r="AD28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF28" s="28" t="s">
-        <v>766</v>
-      </c>
-      <c r="AG28" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH28" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI28" s="28" t="s">
-        <v>722</v>
-      </c>
-      <c r="AJ28" s="28" t="s">
-        <v>771</v>
-      </c>
-      <c r="AK28" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="AL28" s="28" t="s">
-        <v>768</v>
-      </c>
-      <c r="AM28" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="AN28" s="28" t="s">
-        <v>769</v>
-      </c>
-      <c r="AO28" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="AP28" s="28">
-        <v>0.64</v>
-      </c>
-      <c r="AQ28" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="AR28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT28" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="AU28" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="AV28" s="28" t="s">
-        <v>598</v>
-      </c>
-      <c r="AW28" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX28" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="AY28" s="28" t="s">
-        <v>599</v>
-      </c>
-      <c r="AZ28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BA28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BB28" s="28" t="s">
-        <v>600</v>
-      </c>
-      <c r="BC28" s="28" t="s">
-        <v>601</v>
-      </c>
-      <c r="BD28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF28" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BG28" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BH28" s="28" t="s">
-        <v>773</v>
-      </c>
-      <c r="BI28" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="BJ28" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK28" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL28" s="28" t="s">
-        <v>774</v>
-      </c>
-      <c r="BM28" s="28" t="s">
-        <v>775</v>
-      </c>
-      <c r="BN28" s="28"/>
-    </row>
-    <row r="29" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>602</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="28">
-        <v>3</v>
-      </c>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I29" s="28">
-        <v>10</v>
-      </c>
-      <c r="J29" s="28" t="s">
-        <v>604</v>
-      </c>
-      <c r="K29" s="28" t="s">
-        <v>778</v>
-      </c>
-      <c r="L29" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="M29" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="N29" s="28" t="s">
-        <v>605</v>
-      </c>
-      <c r="O29" s="28" t="s">
-        <v>789</v>
-      </c>
-      <c r="P29" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q29" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="R29" s="28" t="s">
-        <v>606</v>
-      </c>
-      <c r="S29" s="28" t="s">
-        <v>780</v>
-      </c>
-      <c r="T29" s="28">
-        <v>300</v>
-      </c>
-      <c r="U29" s="28" t="s">
-        <v>788</v>
-      </c>
-      <c r="V29" s="28" t="s">
-        <v>787</v>
-      </c>
-      <c r="W29" s="28" t="s">
-        <v>779</v>
-      </c>
-      <c r="X29" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="Y29" s="28" t="s">
-        <v>772</v>
-      </c>
-      <c r="Z29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB29" s="28" t="s">
-        <v>804</v>
-      </c>
-      <c r="AC29" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="AD29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF29" s="28" t="s">
-        <v>781</v>
-      </c>
-      <c r="AG29" s="28" t="s">
-        <v>782</v>
-      </c>
-      <c r="AH29" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="AI29" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ29" s="28" t="s">
-        <v>783</v>
-      </c>
-      <c r="AK29" s="28" t="s">
-        <v>784</v>
-      </c>
-      <c r="AL29" s="28" t="s">
-        <v>785</v>
-      </c>
-      <c r="AM29" s="28" t="s">
-        <v>607</v>
-      </c>
-      <c r="AN29" s="28" t="s">
-        <v>786</v>
-      </c>
-      <c r="AO29" s="28" t="s">
-        <v>608</v>
-      </c>
-      <c r="AP29" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="AQ29" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="AR29" s="28">
-        <v>1</v>
-      </c>
-      <c r="AS29" s="28" t="s">
-        <v>609</v>
-      </c>
-      <c r="AT29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AV29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AW29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AX29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AY29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AZ29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BA29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BB29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BD29" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="BE29" s="28" t="s">
-        <v>610</v>
-      </c>
-      <c r="BF29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BG29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BH29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BI29" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BJ29" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK29" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL29" s="28" t="s">
-        <v>790</v>
-      </c>
-      <c r="BM29" s="28" t="s">
-        <v>791</v>
-      </c>
-      <c r="BN29" s="28"/>
-    </row>
-    <row r="30" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>611</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>612</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="F30" s="28">
-        <v>3</v>
-      </c>
-      <c r="G30" s="28">
-        <v>2</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I30" s="28">
-        <v>10</v>
-      </c>
-      <c r="J30" s="28" t="s">
-        <v>613</v>
-      </c>
-      <c r="K30" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="L30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="M30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="N30" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="O30" s="28" t="s">
+      <c r="AJ33" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK33" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL33" s="32" t="s">
+        <v>629</v>
+      </c>
+      <c r="AM33" s="32" t="s">
+        <v>630</v>
+      </c>
+      <c r="AN33" s="32" t="s">
+        <v>818</v>
+      </c>
+      <c r="AO33" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="AP33" s="32" t="s">
+        <v>632</v>
+      </c>
+      <c r="AQ33" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR33" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS33" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT33" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="AU33" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="AV33" s="32" t="s">
+        <v>633</v>
+      </c>
+      <c r="AW33" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="AX33" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="AY33" s="32" t="s">
+        <v>634</v>
+      </c>
+      <c r="AZ33" s="32" t="s">
+        <v>635</v>
+      </c>
+      <c r="BA33" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="BB33" s="32" t="s">
+        <v>635</v>
+      </c>
+      <c r="BC33" s="32" t="s">
+        <v>636</v>
+      </c>
+      <c r="BD33" s="32" t="s">
+        <v>637</v>
+      </c>
+      <c r="BE33" s="32" t="s">
+        <v>453</v>
+      </c>
+      <c r="BF33" s="32" t="s">
+        <v>635</v>
+      </c>
+      <c r="BG33" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="BH33" s="32" t="s">
+        <v>638</v>
+      </c>
+      <c r="BI33" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="BJ33" s="32" t="s">
+        <v>639</v>
+      </c>
+      <c r="BK33" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="P30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="R30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="S30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="T30" s="28">
-        <v>300</v>
-      </c>
-      <c r="U30" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="V30" s="28" t="s">
-        <v>792</v>
-      </c>
-      <c r="W30" s="28" t="s">
-        <v>292</v>
-      </c>
-      <c r="X30" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y30" s="28" t="s">
-        <v>793</v>
-      </c>
-      <c r="Z30" s="28" t="s">
-        <v>737</v>
-      </c>
-      <c r="AA30" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB30" s="28" t="s">
-        <v>796</v>
-      </c>
-      <c r="AC30" s="28" t="s">
-        <v>797</v>
-      </c>
-      <c r="AD30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF30" s="28" t="s">
-        <v>794</v>
-      </c>
-      <c r="AG30" s="28" t="s">
-        <v>795</v>
-      </c>
-      <c r="AH30" s="28" t="s">
-        <v>782</v>
-      </c>
-      <c r="AI30" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ30" s="28" t="s">
-        <v>798</v>
-      </c>
-      <c r="AK30" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL30" s="28" t="s">
-        <v>752</v>
-      </c>
-      <c r="AM30" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="AN30" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="AO30" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="AP30" s="28" t="s">
-        <v>753</v>
-      </c>
-      <c r="AQ30" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT30" s="28" t="s">
-        <v>430</v>
-      </c>
-      <c r="AU30" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="AV30" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="AW30" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX30" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="AY30" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="AZ30" s="28" t="s">
-        <v>614</v>
-      </c>
-      <c r="BA30" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="BB30" s="28" t="s">
-        <v>615</v>
-      </c>
-      <c r="BC30" s="28" t="s">
-        <v>451</v>
-      </c>
-      <c r="BD30" s="28" t="s">
-        <v>807</v>
-      </c>
-      <c r="BE30" s="28" t="s">
-        <v>453</v>
-      </c>
-      <c r="BF30" s="28" t="s">
-        <v>805</v>
-      </c>
-      <c r="BG30" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="BH30" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="BI30" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="BJ30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BK30" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL30" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM30" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="BN30" s="28"/>
-    </row>
-    <row r="31" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>616</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="F31" s="28">
-        <v>4</v>
-      </c>
-      <c r="G31" s="28">
-        <v>3</v>
-      </c>
-      <c r="H31" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I31" s="28">
-        <v>10</v>
-      </c>
-      <c r="J31" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="K31" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="L31" s="28" t="s">
-        <v>617</v>
-      </c>
-      <c r="M31" s="28" t="s">
-        <v>618</v>
-      </c>
-      <c r="N31" s="28" t="s">
-        <v>799</v>
-      </c>
-      <c r="O31" s="28" t="s">
-        <v>800</v>
-      </c>
-      <c r="P31" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q31" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="R31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="S31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="T31" s="28">
-        <v>300</v>
-      </c>
-      <c r="U31" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="V31" s="28" t="s">
-        <v>801</v>
-      </c>
-      <c r="W31" s="28" t="s">
-        <v>802</v>
-      </c>
-      <c r="X31" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y31" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z31" s="28" t="s">
-        <v>720</v>
-      </c>
-      <c r="AA31" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB31" s="28" t="s">
-        <v>804</v>
-      </c>
-      <c r="AC31" s="28" t="s">
-        <v>803</v>
-      </c>
-      <c r="AD31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AH31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AI31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AM31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AO31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AQ31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AR31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AV31" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="AW31" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX31" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="AY31" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="AZ31" s="28" t="s">
-        <v>805</v>
-      </c>
-      <c r="BA31" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="BB31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BC31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BD31" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE31" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="BF31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BG31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BH31" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="BI31" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="BJ31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BK31" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL31" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM31" s="28" t="s">
-        <v>806</v>
-      </c>
-      <c r="BN31" s="28"/>
-    </row>
-    <row r="32" spans="1:66" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>620</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>621</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="28">
-        <v>5</v>
-      </c>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="I32" s="28">
-        <v>10</v>
-      </c>
-      <c r="J32" s="28" t="s">
-        <v>808</v>
-      </c>
-      <c r="K32" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="L32" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="M32" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="N32" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="O32" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="P32" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q32" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="R32" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="S32" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="T32" s="28" t="s">
-        <v>580</v>
-      </c>
-      <c r="U32" s="28" t="s">
-        <v>594</v>
-      </c>
-      <c r="V32" s="28" t="s">
-        <v>428</v>
-      </c>
-      <c r="W32" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="X32" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y32" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="Z32" s="28" t="s">
-        <v>720</v>
-      </c>
-      <c r="AA32" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB32" s="28" t="s">
-        <v>804</v>
-      </c>
-      <c r="AC32" s="28" t="s">
-        <v>803</v>
-      </c>
-      <c r="AD32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF32" s="28" t="s">
-        <v>589</v>
-      </c>
-      <c r="AG32" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="AH32" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="AI32" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ32" s="28" t="s">
-        <v>809</v>
-      </c>
-      <c r="AK32" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="AL32" s="28" t="s">
-        <v>810</v>
-      </c>
-      <c r="AM32" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="AN32" s="28" t="s">
-        <v>815</v>
-      </c>
-      <c r="AO32" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="AP32" s="28" t="s">
-        <v>811</v>
-      </c>
-      <c r="AQ32" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="AR32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT32" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="AU32" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="AV32" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="AW32" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX32" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="AY32" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="AZ32" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA32" s="28" t="s">
-        <v>582</v>
-      </c>
-      <c r="BB32" s="28" t="s">
-        <v>812</v>
-      </c>
-      <c r="BC32" s="28" t="s">
-        <v>523</v>
-      </c>
-      <c r="BD32" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE32" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="BF32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BG32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="BH32" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="BI32" s="28" t="s">
-        <v>814</v>
-      </c>
-      <c r="BJ32" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BK32" s="28" t="s">
-        <v>738</v>
-      </c>
-      <c r="BL32" s="28" t="s">
-        <v>748</v>
-      </c>
-      <c r="BM32" s="28" t="s">
-        <v>813</v>
-      </c>
-      <c r="BN32" s="28"/>
-    </row>
-    <row r="33" spans="1:65" s="29" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>622</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>623</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="F33" s="29">
-        <v>7</v>
-      </c>
-      <c r="G33" s="29">
-        <v>2</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>564</v>
-      </c>
-      <c r="I33" s="29">
-        <v>10</v>
-      </c>
-      <c r="J33" s="29" t="s">
-        <v>624</v>
-      </c>
-      <c r="K33" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="L33" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="M33" s="29" t="s">
-        <v>817</v>
-      </c>
-      <c r="N33" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="O33" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="P33" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q33" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="R33" s="29" t="s">
-        <v>627</v>
-      </c>
-      <c r="S33" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="T33" s="29" t="s">
-        <v>427</v>
-      </c>
-      <c r="U33" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="V33" s="29" t="s">
-        <v>816</v>
-      </c>
-      <c r="W33" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="X33" s="29" t="s">
-        <v>628</v>
-      </c>
-      <c r="Y33" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="Z33" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="AA33" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="AB33" s="28" t="s">
-        <v>804</v>
-      </c>
-      <c r="AC33" s="28" t="s">
-        <v>803</v>
-      </c>
-      <c r="AD33" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE33" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF33" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="AG33" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH33" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI33" s="28" t="s">
-        <v>722</v>
-      </c>
-      <c r="AJ33" s="29" t="s">
-        <v>629</v>
-      </c>
-      <c r="AK33" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL33" s="29" t="s">
-        <v>630</v>
-      </c>
-      <c r="AM33" s="29" t="s">
-        <v>631</v>
-      </c>
-      <c r="AN33" s="29" t="s">
-        <v>818</v>
-      </c>
-      <c r="AO33" s="29" t="s">
-        <v>632</v>
-      </c>
-      <c r="AP33" s="29" t="s">
-        <v>633</v>
-      </c>
-      <c r="AQ33" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR33" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="AS33" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT33" s="29" t="s">
-        <v>430</v>
-      </c>
-      <c r="AU33" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="AV33" s="29" t="s">
-        <v>634</v>
-      </c>
-      <c r="AW33" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX33" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="AY33" s="29" t="s">
-        <v>635</v>
-      </c>
-      <c r="AZ33" s="29" t="s">
-        <v>636</v>
-      </c>
-      <c r="BA33" s="29" t="s">
-        <v>450</v>
-      </c>
-      <c r="BB33" s="29" t="s">
-        <v>636</v>
-      </c>
-      <c r="BC33" s="29" t="s">
-        <v>637</v>
-      </c>
-      <c r="BD33" s="29" t="s">
-        <v>638</v>
-      </c>
-      <c r="BE33" s="29" t="s">
-        <v>453</v>
-      </c>
-      <c r="BF33" s="29" t="s">
-        <v>636</v>
-      </c>
-      <c r="BG33" s="29" t="s">
-        <v>454</v>
-      </c>
-      <c r="BH33" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="BI33" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="BJ33" s="29" t="s">
+      <c r="BL33" s="32" t="s">
         <v>640</v>
       </c>
-      <c r="BK33" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="BL33" s="29" t="s">
-        <v>641</v>
-      </c>
-      <c r="BM33" s="29" t="s">
+      <c r="BM33" s="32" t="s">
         <v>181</v>
       </c>
     </row>
@@ -11898,42 +11905,42 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1">
       <c r="A1" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>642</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1">
       <c r="A2" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>651</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="47.25" customHeight="1">
@@ -11941,10 +11948,10 @@
         <v>68</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11" t="s">
@@ -11957,10 +11964,10 @@
         <v>69</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -11971,15 +11978,15 @@
         <v>70</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="47.25" customHeight="1">
@@ -11987,13 +11994,13 @@
         <v>71</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1">
@@ -12001,10 +12008,10 @@
         <v>72</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -12015,10 +12022,10 @@
         <v>73</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -12029,10 +12036,10 @@
         <v>74</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -12040,74 +12047,74 @@
     </row>
     <row r="10" spans="1:6" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>663</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>664</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="47.25" customHeight="1">
       <c r="A11" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>667</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" customHeight="1">
       <c r="A12" s="11" t="s">
+        <v>668</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>669</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>670</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>671</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.5" customHeight="1">
       <c r="A13" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>673</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>674</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="31.5" customHeight="1">
       <c r="A14" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>676</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>677</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -12116,52 +12123,52 @@
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1">
       <c r="A15" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>678</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>679</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" customHeight="1">
       <c r="A16" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>681</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>682</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="31.5" customHeight="1">
       <c r="A17" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>684</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>685</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="12" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" customHeight="1">
       <c r="A18" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>687</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>688</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -12170,10 +12177,10 @@
     </row>
     <row r="19" spans="1:6" ht="16.5" customHeight="1">
       <c r="A19" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>689</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>690</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -12182,26 +12189,26 @@
     </row>
     <row r="20" spans="1:6" ht="47.25" customHeight="1">
       <c r="A20" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>692</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="12" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5" customHeight="1">
       <c r="A21" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>694</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>695</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -12210,29 +12217,29 @@
     </row>
     <row r="22" spans="1:6" ht="16.5" customHeight="1">
       <c r="A22" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>696</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>697</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5" customHeight="1">
       <c r="A23" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>700</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -12240,10 +12247,10 @@
     </row>
     <row r="24" spans="1:6" ht="16.5" customHeight="1">
       <c r="A24" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>701</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>702</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -12252,13 +12259,13 @@
     </row>
     <row r="25" spans="1:6" ht="16.5" customHeight="1">
       <c r="A25" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>704</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
@@ -12266,10 +12273,10 @@
     </row>
     <row r="26" spans="1:6" ht="16.5" customHeight="1">
       <c r="A26" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>705</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>706</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -12278,13 +12285,13 @@
     </row>
     <row r="27" spans="1:6" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>707</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>708</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
@@ -12292,10 +12299,10 @@
     </row>
     <row r="28" spans="1:6" ht="31.5" customHeight="1">
       <c r="A28" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>709</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>710</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -12304,13 +12311,13 @@
     </row>
     <row r="29" spans="1:6" ht="16.5" customHeight="1">
       <c r="A29" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>712</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>

--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기입 안내" sheetId="1" state="visible" r:id="rId1"/>
@@ -177,7 +177,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -242,6 +242,23 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE4E4E4"/>
         <bgColor rgb="FFE4E4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -316,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -432,6 +449,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2411,10 +2444,9 @@
           <t>300#</t>
         </is>
       </c>
-      <c r="U3" s="13" t="inlineStr">
-        <is>
-          <t>End Connection
-(Casting Rating이 공란일 경우 End connection과 동일)</t>
+      <c r="U3" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
         </is>
       </c>
       <c r="V3" s="13" t="inlineStr">
@@ -2434,7 +2466,7 @@
       </c>
       <c r="Y3" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z3" s="13" t="inlineStr">
@@ -2494,7 +2526,7 @@
       </c>
       <c r="AK3" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL3" s="13" t="inlineStr">
@@ -2540,9 +2572,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU3" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU3" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV3" s="13" t="inlineStr">
@@ -2560,9 +2592,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY3" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY3" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ3" s="13" t="inlineStr">
@@ -2572,7 +2604,7 @@
       </c>
       <c r="BA3" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB3" s="13" t="inlineStr">
@@ -2582,7 +2614,7 @@
       </c>
       <c r="BC3" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD3" s="13" t="inlineStr">
@@ -2592,7 +2624,7 @@
       </c>
       <c r="BE3" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF3" s="29" t="inlineStr">
@@ -2600,9 +2632,9 @@
           <t>Std.</t>
         </is>
       </c>
-      <c r="BG3" s="13" t="inlineStr">
-        <is>
-          <t>Trim Stem</t>
+      <c r="BG3" s="29" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH3" s="13" t="inlineStr">
@@ -2610,9 +2642,9 @@
           <t>DIAPHRAGM</t>
         </is>
       </c>
-      <c r="BI3" s="13" t="inlineStr">
-        <is>
-          <t>Actuator Style</t>
+      <c r="BI3" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ3" s="13" t="inlineStr">
@@ -2632,7 +2664,7 @@
       </c>
       <c r="BM3" s="13" t="inlineStr">
         <is>
-          <t>Positioner Type</t>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN3" s="13" t="n"/>
@@ -2728,10 +2760,9 @@
           <t>600#</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr">
-        <is>
-          <t>End Connection
-(Casting Rating이 공란일 경우 End connection과 동일)</t>
+      <c r="U4" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
         </is>
       </c>
       <c r="V4" s="13" t="inlineStr">
@@ -2751,7 +2782,7 @@
       </c>
       <c r="Y4" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z4" s="13" t="inlineStr">
@@ -2811,7 +2842,7 @@
       </c>
       <c r="AK4" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL4" s="13" t="inlineStr">
@@ -2857,9 +2888,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU4" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU4" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV4" s="13" t="inlineStr">
@@ -2877,9 +2908,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY4" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY4" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ4" s="13" t="inlineStr">
@@ -2889,7 +2920,7 @@
       </c>
       <c r="BA4" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB4" s="13" t="inlineStr">
@@ -2899,7 +2930,7 @@
       </c>
       <c r="BC4" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD4" s="13" t="inlineStr">
@@ -2909,7 +2940,7 @@
       </c>
       <c r="BE4" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF4" s="29" t="inlineStr">
@@ -2917,9 +2948,9 @@
           <t>Std.</t>
         </is>
       </c>
-      <c r="BG4" s="13" t="inlineStr">
-        <is>
-          <t>Trim Stem</t>
+      <c r="BG4" s="29" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH4" s="13" t="inlineStr">
@@ -2927,9 +2958,9 @@
           <t>DIAPHRAGM</t>
         </is>
       </c>
-      <c r="BI4" s="13" t="inlineStr">
-        <is>
-          <t>Actuator Style</t>
+      <c r="BI4" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ4" s="13" t="inlineStr">
@@ -2949,7 +2980,7 @@
       </c>
       <c r="BM4" s="13" t="inlineStr">
         <is>
-          <t>Positioner Type</t>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN4" s="13" t="n"/>
@@ -3045,10 +3076,9 @@
           <t>600#</t>
         </is>
       </c>
-      <c r="U5" s="13" t="inlineStr">
-        <is>
-          <t>End Connection
-(Casting Rating이 공란일 경우 End connection과 동일)</t>
+      <c r="U5" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
         </is>
       </c>
       <c r="V5" s="13" t="inlineStr">
@@ -3068,7 +3098,7 @@
       </c>
       <c r="Y5" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z5" s="13" t="inlineStr">
@@ -3128,7 +3158,7 @@
       </c>
       <c r="AK5" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL5" s="13" t="inlineStr">
@@ -3174,9 +3204,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU5" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU5" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV5" s="13" t="inlineStr">
@@ -3194,9 +3224,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY5" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY5" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ5" s="13" t="inlineStr">
@@ -3206,7 +3236,7 @@
       </c>
       <c r="BA5" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB5" s="13" t="inlineStr">
@@ -3216,7 +3246,7 @@
       </c>
       <c r="BC5" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD5" s="13" t="inlineStr">
@@ -3226,7 +3256,7 @@
       </c>
       <c r="BE5" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF5" s="29" t="inlineStr">
@@ -3234,9 +3264,9 @@
           <t>Std.</t>
         </is>
       </c>
-      <c r="BG5" s="13" t="inlineStr">
-        <is>
-          <t>Trim Stem</t>
+      <c r="BG5" s="29" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH5" s="13" t="inlineStr">
@@ -3244,9 +3274,9 @@
           <t>DIAPHRAGM</t>
         </is>
       </c>
-      <c r="BI5" s="13" t="inlineStr">
-        <is>
-          <t>Actuator Style</t>
+      <c r="BI5" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ5" s="13" t="inlineStr">
@@ -3266,7 +3296,7 @@
       </c>
       <c r="BM5" s="13" t="inlineStr">
         <is>
-          <t>Positioner Type</t>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN5" s="13" t="n"/>
@@ -3444,7 +3474,7 @@
       </c>
       <c r="AK6" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL6" s="13" t="inlineStr">
@@ -3490,9 +3520,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU6" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU6" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV6" s="13" t="inlineStr">
@@ -3560,9 +3590,9 @@
           <t>DIAPHRAGM</t>
         </is>
       </c>
-      <c r="BI6" s="13" t="inlineStr">
-        <is>
-          <t>Actuator Type</t>
+      <c r="BI6" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ6" s="13" t="inlineStr">
@@ -6576,7 +6606,7 @@
       </c>
       <c r="Z16" s="20" t="inlineStr">
         <is>
-          <t>Fail Close</t>
+          <t>FAIL CLOSE</t>
         </is>
       </c>
       <c r="AA16" s="27" t="inlineStr">
@@ -7087,7 +7117,7 @@
       </c>
       <c r="Y19" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z19" s="20" t="inlineStr">
@@ -7097,7 +7127,7 @@
       </c>
       <c r="AA19" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB19" s="13" t="inlineStr">
@@ -7147,7 +7177,7 @@
       </c>
       <c r="AK19" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL19" s="27" t="inlineStr">
@@ -7195,9 +7225,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU19" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU19" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV19" s="13" t="inlineStr">
@@ -7215,9 +7245,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY19" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY19" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ19" s="27" t="inlineStr">
@@ -7227,7 +7257,7 @@
       </c>
       <c r="BA19" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB19" s="27" t="inlineStr">
@@ -7237,7 +7267,7 @@
       </c>
       <c r="BC19" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD19" s="27" t="inlineStr">
@@ -7247,7 +7277,7 @@
       </c>
       <c r="BE19" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF19" s="29" t="inlineStr">
@@ -7257,7 +7287,7 @@
       </c>
       <c r="BG19" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH19" s="13" t="inlineStr">
@@ -7267,7 +7297,7 @@
       </c>
       <c r="BI19" s="29" t="inlineStr">
         <is>
-          <t>Actuator Style</t>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ19" s="13" t="inlineStr">
@@ -7285,9 +7315,9 @@
           <t>3582</t>
         </is>
       </c>
-      <c r="BM19" s="29" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
+      <c r="BM19" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN19" s="20" t="n"/>
@@ -7409,7 +7439,7 @@
       </c>
       <c r="Y20" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z20" s="20" t="inlineStr">
@@ -7419,7 +7449,7 @@
       </c>
       <c r="AA20" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB20" s="13" t="inlineStr">
@@ -7469,7 +7499,7 @@
       </c>
       <c r="AK20" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL20" s="27" t="inlineStr">
@@ -7517,9 +7547,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU20" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU20" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV20" s="13" t="inlineStr">
@@ -7537,9 +7567,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY20" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY20" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ20" s="27" t="inlineStr">
@@ -7549,7 +7579,7 @@
       </c>
       <c r="BA20" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB20" s="27" t="inlineStr">
@@ -7559,7 +7589,7 @@
       </c>
       <c r="BC20" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD20" s="27" t="inlineStr">
@@ -7569,7 +7599,7 @@
       </c>
       <c r="BE20" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF20" s="29" t="inlineStr">
@@ -7579,7 +7609,7 @@
       </c>
       <c r="BG20" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH20" s="13" t="inlineStr">
@@ -7589,7 +7619,7 @@
       </c>
       <c r="BI20" s="29" t="inlineStr">
         <is>
-          <t>Actuator Style</t>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ20" s="13" t="inlineStr">
@@ -7607,9 +7637,9 @@
           <t>3582G</t>
         </is>
       </c>
-      <c r="BM20" s="29" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
+      <c r="BM20" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN20" s="20" t="n"/>
@@ -7731,7 +7761,7 @@
       </c>
       <c r="Y21" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z21" s="20" t="inlineStr">
@@ -7741,7 +7771,7 @@
       </c>
       <c r="AA21" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB21" s="13" t="inlineStr">
@@ -7791,7 +7821,7 @@
       </c>
       <c r="AK21" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL21" s="27" t="inlineStr">
@@ -7839,9 +7869,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU21" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU21" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV21" s="13" t="inlineStr">
@@ -7859,9 +7889,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY21" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY21" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ21" s="27" t="inlineStr">
@@ -7871,7 +7901,7 @@
       </c>
       <c r="BA21" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB21" s="27" t="inlineStr">
@@ -7881,7 +7911,7 @@
       </c>
       <c r="BC21" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD21" s="27" t="inlineStr">
@@ -7891,7 +7921,7 @@
       </c>
       <c r="BE21" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF21" s="29" t="inlineStr">
@@ -7901,7 +7931,7 @@
       </c>
       <c r="BG21" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH21" s="13" t="inlineStr">
@@ -7911,7 +7941,7 @@
       </c>
       <c r="BI21" s="29" t="inlineStr">
         <is>
-          <t>Actuator Style</t>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ21" s="13" t="inlineStr">
@@ -7929,9 +7959,9 @@
           <t>3582G</t>
         </is>
       </c>
-      <c r="BM21" s="29" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
+      <c r="BM21" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN21" s="20" t="n"/>
@@ -8053,7 +8083,7 @@
       </c>
       <c r="Y22" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z22" s="29" t="inlineStr">
@@ -8063,7 +8093,7 @@
       </c>
       <c r="AA22" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB22" s="13" t="inlineStr">
@@ -8113,7 +8143,7 @@
       </c>
       <c r="AK22" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL22" s="27" t="inlineStr">
@@ -8161,9 +8191,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU22" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU22" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV22" s="13" t="inlineStr">
@@ -8181,9 +8211,9 @@
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY22" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY22" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ22" s="27" t="inlineStr">
@@ -8193,7 +8223,7 @@
       </c>
       <c r="BA22" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB22" s="27" t="inlineStr">
@@ -8203,7 +8233,7 @@
       </c>
       <c r="BC22" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD22" s="27" t="inlineStr">
@@ -8213,7 +8243,7 @@
       </c>
       <c r="BE22" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF22" s="29" t="inlineStr">
@@ -8223,7 +8253,7 @@
       </c>
       <c r="BG22" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH22" s="13" t="inlineStr">
@@ -8233,7 +8263,7 @@
       </c>
       <c r="BI22" s="29" t="inlineStr">
         <is>
-          <t>Actuator Style</t>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ22" s="13" t="inlineStr">
@@ -8251,9 +8281,9 @@
           <t>3582G</t>
         </is>
       </c>
-      <c r="BM22" s="29" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
+      <c r="BM22" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN22" s="20" t="n"/>
@@ -8375,7 +8405,7 @@
       </c>
       <c r="Y23" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z23" s="29" t="inlineStr">
@@ -8385,7 +8415,7 @@
       </c>
       <c r="AA23" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB23" s="13" t="inlineStr">
@@ -8435,7 +8465,7 @@
       </c>
       <c r="AK23" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL23" s="27" t="inlineStr">
@@ -8483,9 +8513,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU23" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU23" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV23" s="13" t="inlineStr">
@@ -8503,9 +8533,9 @@
           <t>LINEAR</t>
         </is>
       </c>
-      <c r="AY23" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY23" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ23" s="27" t="inlineStr">
@@ -8515,7 +8545,7 @@
       </c>
       <c r="BA23" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB23" s="27" t="inlineStr">
@@ -8525,7 +8555,7 @@
       </c>
       <c r="BC23" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD23" s="27" t="inlineStr">
@@ -8535,7 +8565,7 @@
       </c>
       <c r="BE23" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF23" s="29" t="inlineStr">
@@ -8545,7 +8575,7 @@
       </c>
       <c r="BG23" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH23" s="13" t="inlineStr">
@@ -8555,7 +8585,7 @@
       </c>
       <c r="BI23" s="29" t="inlineStr">
         <is>
-          <t>Actuator Style</t>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ23" s="13" t="inlineStr">
@@ -8573,9 +8603,9 @@
           <t>3582G</t>
         </is>
       </c>
-      <c r="BM23" s="29" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
+      <c r="BM23" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
         </is>
       </c>
       <c r="BN23" s="20" t="n"/>
@@ -8694,7 +8724,7 @@
       </c>
       <c r="Y24" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z24" s="13" t="inlineStr">
@@ -8704,7 +8734,7 @@
       </c>
       <c r="AA24" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB24" s="13" t="inlineStr">
@@ -8754,7 +8784,7 @@
       </c>
       <c r="AK24" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL24" s="13" t="inlineStr">
@@ -8800,9 +8830,9 @@
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU24" s="13" t="inlineStr">
-        <is>
-          <t>Body Style</t>
+      <c r="AU24" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV24" s="13" t="inlineStr">
@@ -8820,9 +8850,9 @@
           <t>LINEAR</t>
         </is>
       </c>
-      <c r="AY24" s="13" t="inlineStr">
-        <is>
-          <t>Trim Plug or Cage</t>
+      <c r="AY24" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ24" s="13" t="inlineStr">
@@ -8832,7 +8862,7 @@
       </c>
       <c r="BA24" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB24" s="13" t="inlineStr">
@@ -8842,7 +8872,7 @@
       </c>
       <c r="BC24" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD24" s="13" t="inlineStr">
@@ -8852,7 +8882,7 @@
       </c>
       <c r="BE24" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF24" s="29" t="inlineStr">
@@ -8862,7 +8892,7 @@
       </c>
       <c r="BG24" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH24" s="13" t="inlineStr">
@@ -8872,7 +8902,7 @@
       </c>
       <c r="BI24" s="29" t="inlineStr">
         <is>
-          <t>Actuator Style</t>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ24" s="27" t="inlineStr">
@@ -9017,7 +9047,7 @@
       </c>
       <c r="Y25" s="13" t="inlineStr">
         <is>
-          <t>Body Material</t>
+          <t>Body, Material</t>
         </is>
       </c>
       <c r="Z25" s="38" t="inlineStr">
@@ -9027,7 +9057,7 @@
       </c>
       <c r="AA25" s="27" t="inlineStr">
         <is>
-          <t>Air Fails Valve to</t>
+          <t>Actuator, Air Fails Valve to</t>
         </is>
       </c>
       <c r="AB25" s="13" t="inlineStr">
@@ -9077,7 +9107,7 @@
       </c>
       <c r="AK25" s="13" t="inlineStr">
         <is>
-          <t>Flow Rate, Normal</t>
+          <t>Flow Rate, Give Units, Normal</t>
         </is>
       </c>
       <c r="AL25" s="37" t="inlineStr">
@@ -9125,7 +9155,7 @@
       </c>
       <c r="AU25" s="38" t="inlineStr">
         <is>
-          <t>Body Style</t>
+          <t>Body, Style</t>
         </is>
       </c>
       <c r="AV25" s="38" t="inlineStr">
@@ -9145,7 +9175,7 @@
       </c>
       <c r="AY25" s="38" t="inlineStr">
         <is>
-          <t>Trim Plug or Cage</t>
+          <t>Trim, Plug or Cage</t>
         </is>
       </c>
       <c r="AZ25" s="37" t="inlineStr">
@@ -9155,7 +9185,7 @@
       </c>
       <c r="BA25" s="13" t="inlineStr">
         <is>
-          <t>Trim Valve Plug Material</t>
+          <t>Trim, Valve Plug Material</t>
         </is>
       </c>
       <c r="BB25" s="37" t="inlineStr">
@@ -9165,7 +9195,7 @@
       </c>
       <c r="BC25" s="13" t="inlineStr">
         <is>
-          <t>Trim Cage and/or Bushing Material</t>
+          <t>Trim, Cage and/or Bushing Material</t>
         </is>
       </c>
       <c r="BD25" s="37" t="inlineStr">
@@ -9175,7 +9205,7 @@
       </c>
       <c r="BE25" s="13" t="inlineStr">
         <is>
-          <t>Trim  Seat Ring Material</t>
+          <t>Trim, Seat Ring Material</t>
         </is>
       </c>
       <c r="BF25" s="29" t="inlineStr">
@@ -9185,7 +9215,7 @@
       </c>
       <c r="BG25" s="29" t="inlineStr">
         <is>
-          <t>Trim Stem</t>
+          <t>Trim, Stem</t>
         </is>
       </c>
       <c r="BH25" s="38" t="inlineStr">
@@ -9193,9 +9223,9 @@
           <t>CYLINDER</t>
         </is>
       </c>
-      <c r="BI25" s="39" t="inlineStr">
-        <is>
-          <t>Actuator Style</t>
+      <c r="BI25" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
         </is>
       </c>
       <c r="BJ25" s="38" t="inlineStr">
@@ -9227,13 +9257,329 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="48">
+      <c r="A26" s="44" t="inlineStr">
         <is>
           <t>d024</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>10FV634-DATA SHEET_REV0.pdf</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>pdf(텍스트)</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="n">
+        <v>35</v>
+      </c>
+      <c r="J26" s="45" t="inlineStr">
+        <is>
+          <t>10-FV-634</t>
+        </is>
+      </c>
+      <c r="K26" s="45" t="inlineStr">
+        <is>
+          <t>Valve Tag #</t>
+        </is>
+      </c>
+      <c r="L26" s="45" t="inlineStr">
+        <is>
+          <t>FLOWSERVE</t>
+        </is>
+      </c>
+      <c r="M26" s="45" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N26" s="45" t="inlineStr">
+        <is>
+          <t>Mark One</t>
+        </is>
+      </c>
+      <c r="O26" s="45" t="inlineStr">
+        <is>
+          <t>Model / Body Type / Trim Type</t>
+        </is>
+      </c>
+      <c r="P26" s="45" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q26" s="45" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Trim # - Cv</t>
+        </is>
+      </c>
+      <c r="R26" s="45" t="inlineStr">
+        <is>
+          <t>249.719</t>
+        </is>
+      </c>
+      <c r="S26" s="45" t="inlineStr">
+        <is>
+          <t>Calculated Data, Flow Coeff. (Cv), Nor</t>
+        </is>
+      </c>
+      <c r="T26" s="45" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U26" s="45" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Size/Pressure Class/Body Form</t>
+        </is>
+      </c>
+      <c r="V26" s="45" t="inlineStr">
+        <is>
+          <t>8"</t>
+        </is>
+      </c>
+      <c r="W26" s="45" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Size/Pressure Class/Body Form</t>
+        </is>
+      </c>
+      <c r="X26" s="45" t="inlineStr">
+        <is>
+          <t>Cr-Mo C5; F5a</t>
+        </is>
+      </c>
+      <c r="Y26" s="45" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Body Matl / Bonnet Matl</t>
+        </is>
+      </c>
+      <c r="Z26" s="46" t="inlineStr">
+        <is>
+          <t>FAIL OPEN</t>
+        </is>
+      </c>
+      <c r="AA26" s="45" t="inlineStr">
+        <is>
+          <t>Actuator, Fail/Air-To</t>
+        </is>
+      </c>
+      <c r="AB26" s="45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC26" s="45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD26" s="45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE26" s="45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF26" s="45" t="inlineStr">
+        <is>
+          <t>LS AR</t>
+        </is>
+      </c>
+      <c r="AG26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Process Fluid</t>
+        </is>
+      </c>
+      <c r="AH26" s="45" t="inlineStr">
+        <is>
+          <t>LIQUID</t>
+        </is>
+      </c>
+      <c r="AI26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Process Fluid</t>
+        </is>
+      </c>
+      <c r="AJ26" s="45" t="inlineStr">
+        <is>
+          <t>164332.000 kg/h</t>
+        </is>
+      </c>
+      <c r="AK26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Liq Flow Rate (kg/h), Nor</t>
+        </is>
+      </c>
+      <c r="AL26" s="45" t="inlineStr">
+        <is>
+          <t>19.1 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Inlet Press, Nor</t>
+        </is>
+      </c>
+      <c r="AN26" s="45" t="inlineStr">
+        <is>
+          <t>291.2 °C</t>
+        </is>
+      </c>
+      <c r="AO26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Temperature (°C), Nor</t>
+        </is>
+      </c>
+      <c r="AP26" s="45" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
+      <c r="AQ26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, SG-MW</t>
+        </is>
+      </c>
+      <c r="AR26" s="45" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, 1.705</t>
+        </is>
+      </c>
+      <c r="AS26" s="45" t="inlineStr">
+        <is>
+          <t>Viscosity (cP)</t>
+        </is>
+      </c>
+      <c r="AT26" s="45" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU26" s="45" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Model / Body Type / Trim Type</t>
+        </is>
+      </c>
+      <c r="AV26" s="47" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW26" s="45" t="inlineStr">
+        <is>
+          <t>Max Shutoff / Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX26" s="45" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY26" s="45" t="inlineStr">
+        <is>
+          <t>Trim # - Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ26" s="45" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BA26" s="45" t="inlineStr">
+        <is>
+          <t>Plug Mtl/ Facing|Treatment / Stem Cvr</t>
+        </is>
+      </c>
+      <c r="BB26" s="48" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BC26" s="45" t="inlineStr">
+        <is>
+          <t>Seat Retainer Mtl</t>
+        </is>
+      </c>
+      <c r="BD26" s="45" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BE26" s="45" t="inlineStr">
+        <is>
+          <t>Seat Ring Mtl/ Facing|Treatment</t>
+        </is>
+      </c>
+      <c r="BF26" s="46" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BG26" s="45" t="inlineStr">
+        <is>
+          <t>Stem Mtl/ Facing|Treatment / Pilot Spr</t>
+        </is>
+      </c>
+      <c r="BH26" s="49" t="inlineStr">
+        <is>
+          <t>CYLINDER</t>
+        </is>
+      </c>
+      <c r="BI26" s="45" t="inlineStr">
+        <is>
+          <t>Act. Type</t>
+        </is>
+      </c>
+      <c r="BJ26" s="45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK26" s="45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL26" s="48" t="inlineStr">
+        <is>
+          <t>Logix 3800 Series</t>
+        </is>
+      </c>
+      <c r="BM26" s="45" t="inlineStr">
+        <is>
+          <t>Positioner Model</t>
+        </is>
+      </c>
+      <c r="BN26" s="45" t="inlineStr">
+        <is>
+          <t>Cage정보가 없는걸 현재 Retainer로 받고있는게 많아서 고민 필요</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -9241,148 +9587,975 @@
           <t>d025</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="13" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="13" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="13" t="n"/>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="13" t="n"/>
-      <c r="U27" s="13" t="n"/>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="13" t="n"/>
-      <c r="X27" s="13" t="n"/>
-      <c r="Y27" s="13" t="n"/>
-      <c r="Z27" s="13" t="n"/>
-      <c r="AA27" s="13" t="n"/>
-      <c r="AB27" s="13" t="n"/>
-      <c r="AC27" s="13" t="n"/>
-      <c r="AD27" s="13" t="n"/>
-      <c r="AE27" s="13" t="n"/>
-      <c r="AF27" s="13" t="n"/>
-      <c r="AG27" s="13" t="n"/>
-      <c r="AH27" s="13" t="n"/>
-      <c r="AI27" s="13" t="n"/>
-      <c r="AJ27" s="13" t="n"/>
-      <c r="AK27" s="13" t="n"/>
-      <c r="AL27" s="13" t="n"/>
-      <c r="AM27" s="13" t="n"/>
-      <c r="AN27" s="13" t="n"/>
-      <c r="AO27" s="13" t="n"/>
-      <c r="AP27" s="13" t="n"/>
-      <c r="AQ27" s="13" t="n"/>
-      <c r="AR27" s="13" t="n"/>
-      <c r="AS27" s="13" t="n"/>
-      <c r="AT27" s="13" t="n"/>
-      <c r="AU27" s="13" t="n"/>
-      <c r="AV27" s="13" t="n"/>
-      <c r="AW27" s="13" t="n"/>
-      <c r="AX27" s="13" t="n"/>
-      <c r="AY27" s="13" t="n"/>
-      <c r="AZ27" s="13" t="n"/>
-      <c r="BA27" s="13" t="n"/>
-      <c r="BB27" s="13" t="n"/>
-      <c r="BC27" s="13" t="n"/>
-      <c r="BD27" s="13" t="n"/>
-      <c r="BE27" s="13" t="n"/>
-      <c r="BF27" s="13" t="n"/>
-      <c r="BG27" s="13" t="n"/>
-      <c r="BH27" s="13" t="n"/>
-      <c r="BI27" s="13" t="n"/>
-      <c r="BJ27" s="13" t="n"/>
-      <c r="BK27" s="13" t="n"/>
-      <c r="BL27" s="13" t="n"/>
-      <c r="BM27" s="13" t="n"/>
-      <c r="BN27" s="13" t="n"/>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>10HV010-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>10-HV-010</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>667-ED</t>
+        </is>
+      </c>
+      <c r="O27" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q27" s="13" t="inlineStr">
+        <is>
+          <t>Valve Coefficient Cg = 7580 (C1=33.8) — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S27" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cg☒ = 5214 — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T27" s="27" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U27" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y27" s="13" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z27" s="38" t="inlineStr">
+        <is>
+          <t>FAIL CLOSE</t>
+        </is>
+      </c>
+      <c r="AA27" s="27" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE27" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF27" s="13" t="inlineStr">
+        <is>
+          <t>S.H. STEAM</t>
+        </is>
+      </c>
+      <c r="AG27" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH27" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI27" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK27" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL27" s="13" t="inlineStr">
+        <is>
+          <t>2.7 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM27" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN27" s="13" t="inlineStr">
+        <is>
+          <t>371 ℃</t>
+        </is>
+      </c>
+      <c r="AO27" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ27" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity 행 = 1.196 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+        </is>
+      </c>
+      <c r="AR27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT27" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU27" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV27" s="38" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW27" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX27" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY27" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ27" s="13" t="inlineStr">
+        <is>
+          <t>316 SST/CoCr-A</t>
+        </is>
+      </c>
+      <c r="BA27" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB27" s="13" t="inlineStr">
+        <is>
+          <t>17-4PH SST</t>
+        </is>
+      </c>
+      <c r="BC27" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD27" s="13" t="inlineStr">
+        <is>
+          <t>CAST CoCr-A</t>
+        </is>
+      </c>
+      <c r="BE27" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF27" s="29" t="inlineStr">
+        <is>
+          <t>Std.</t>
+        </is>
+      </c>
+      <c r="BG27" s="29" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
+        </is>
+      </c>
+      <c r="BH27" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI27" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
+        </is>
+      </c>
+      <c r="BJ27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK27" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL27" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM27" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
+        </is>
+      </c>
+      <c r="BN27" s="18" t="inlineStr">
+        <is>
+          <t>Nippon Fisher 계열 Cg 기반 양식 — 유량계수가 Cg 로만 기재되고 Cv 는 문서에 없다. Cg = C1 × Cv 이나 환산값은 마스터 열에서 읽은 값과 구별되지 않으므로 NA + 원문라벨로 남긴다(TODO T7).</t>
+        </is>
+      </c>
     </row>
-    <row r="28">
+    <row r="28" ht="47.25" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
           <t>d026</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="13" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="13" t="n"/>
-      <c r="U28" s="13" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="13" t="n"/>
-      <c r="X28" s="13" t="n"/>
-      <c r="Y28" s="13" t="n"/>
-      <c r="Z28" s="13" t="n"/>
-      <c r="AA28" s="13" t="n"/>
-      <c r="AB28" s="13" t="n"/>
-      <c r="AC28" s="13" t="n"/>
-      <c r="AD28" s="13" t="n"/>
-      <c r="AE28" s="13" t="n"/>
-      <c r="AF28" s="13" t="n"/>
-      <c r="AG28" s="13" t="n"/>
-      <c r="AH28" s="13" t="n"/>
-      <c r="AI28" s="13" t="n"/>
-      <c r="AJ28" s="13" t="n"/>
-      <c r="AK28" s="13" t="n"/>
-      <c r="AL28" s="13" t="n"/>
-      <c r="AM28" s="13" t="n"/>
-      <c r="AN28" s="13" t="n"/>
-      <c r="AO28" s="13" t="n"/>
-      <c r="AP28" s="13" t="n"/>
-      <c r="AQ28" s="13" t="n"/>
-      <c r="AR28" s="13" t="n"/>
-      <c r="AS28" s="13" t="n"/>
-      <c r="AT28" s="13" t="n"/>
-      <c r="AU28" s="13" t="n"/>
-      <c r="AV28" s="13" t="n"/>
-      <c r="AW28" s="13" t="n"/>
-      <c r="AX28" s="13" t="n"/>
-      <c r="AY28" s="13" t="n"/>
-      <c r="AZ28" s="13" t="n"/>
-      <c r="BA28" s="13" t="n"/>
-      <c r="BB28" s="13" t="n"/>
-      <c r="BC28" s="13" t="n"/>
-      <c r="BD28" s="13" t="n"/>
-      <c r="BE28" s="13" t="n"/>
-      <c r="BF28" s="13" t="n"/>
-      <c r="BG28" s="13" t="n"/>
-      <c r="BH28" s="13" t="n"/>
-      <c r="BI28" s="13" t="n"/>
-      <c r="BJ28" s="13" t="n"/>
-      <c r="BK28" s="13" t="n"/>
-      <c r="BL28" s="13" t="n"/>
-      <c r="BM28" s="13" t="n"/>
-      <c r="BN28" s="13" t="n"/>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>10HV013-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>10-HV-013</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N28" s="13" t="inlineStr">
+        <is>
+          <t>667-ES</t>
+        </is>
+      </c>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q28" s="13" t="inlineStr">
+        <is>
+          <t>Valve Coefficient Cg = 4910 (C1=35.3) — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S28" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cg☒ = 1603 — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T28" s="27" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U28" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V28" s="13" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W28" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X28" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y28" s="13" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z28" s="38" t="inlineStr">
+        <is>
+          <t>FAIL CLOSE</t>
+        </is>
+      </c>
+      <c r="AA28" s="27" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE28" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF28" s="13" t="inlineStr">
+        <is>
+          <t>M.P. STEAM</t>
+        </is>
+      </c>
+      <c r="AG28" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH28" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI28" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK28" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL28" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM28" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN28" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO28" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ28" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity 행에 손으로 'Density' 로 고쳐 씀 · 4.95 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+        </is>
+      </c>
+      <c r="AR28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT28" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU28" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV28" s="38" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW28" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX28" s="13" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="AY28" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ28" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA28" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB28" s="13" t="inlineStr">
+        <is>
+          <t>316 SST/ENC</t>
+        </is>
+      </c>
+      <c r="BC28" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD28" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE28" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF28" s="29" t="inlineStr">
+        <is>
+          <t>Std.</t>
+        </is>
+      </c>
+      <c r="BG28" s="29" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
+        </is>
+      </c>
+      <c r="BH28" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI28" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
+        </is>
+      </c>
+      <c r="BJ28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK28" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL28" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM28" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
+        </is>
+      </c>
+      <c r="BN28" s="18" t="inlineStr">
+        <is>
+          <t>Nippon Fisher 계열 Cg 기반 양식 — 유량계수가 Cg 로만 기재되고 Cv 는 문서에 없다. Cg = C1 × Cv 이나 환산값은 마스터 열에서 읽은 값과 구별되지 않으므로 NA + 원문라벨로 남긴다(TODO T7).</t>
+        </is>
+      </c>
     </row>
-    <row r="29">
+    <row r="29" ht="47.25" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
           <t>d027</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>10HV014-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>10-HV-014</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>667-ED</t>
+        </is>
+      </c>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q29" s="13" t="inlineStr">
+        <is>
+          <t>Valve Coefficient Cg = 14900 (C1=34.4) — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S29" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff. 칸에 'Later' 라고만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T29" s="27" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U29" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V29" s="13" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X29" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y29" s="13" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z29" s="38" t="inlineStr">
+        <is>
+          <t>FAIL CLOSE</t>
+        </is>
+      </c>
+      <c r="AA29" s="27" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE29" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF29" s="13" t="inlineStr">
+        <is>
+          <t>M.P. STEAM</t>
+        </is>
+      </c>
+      <c r="AG29" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH29" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI29" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK29" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL29" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM29" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN29" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO29" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ29" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity 행 = 4.96 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+        </is>
+      </c>
+      <c r="AR29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT29" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU29" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV29" s="38" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW29" s="13" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX29" s="13" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="AY29" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ29" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA29" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB29" s="13" t="inlineStr">
+        <is>
+          <t>316 SST/ENC</t>
+        </is>
+      </c>
+      <c r="BC29" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD29" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE29" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF29" s="29" t="inlineStr">
+        <is>
+          <t>Std.</t>
+        </is>
+      </c>
+      <c r="BG29" s="29" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
+        </is>
+      </c>
+      <c r="BH29" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI29" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
+        </is>
+      </c>
+      <c r="BJ29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL29" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM29" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
+        </is>
+      </c>
+      <c r="BN29" s="18" t="inlineStr">
+        <is>
+          <t>Nippon Fisher 계열 Cg 기반 양식 — 유량계수가 Cg 로만 기재되고 Cv 는 문서에 없다. Cg = C1 × Cv 이나 환산값은 마스터 열에서 읽은 값과 구별되지 않으므로 NA + 원문라벨로 남긴다(TODO T7).</t>
         </is>
       </c>
     </row>
@@ -9392,6 +10565,315 @@
           <t>d028</t>
         </is>
       </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>10LV012-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>10-LV-012</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>1051-7600</t>
+        </is>
+      </c>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>Size Type and Class</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q30" s="13" t="inlineStr">
+        <is>
+          <t>Maximum Valve Coefficient, Cv</t>
+        </is>
+      </c>
+      <c r="R30" s="13" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="S30" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cv, Normal</t>
+        </is>
+      </c>
+      <c r="T30" s="27" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U30" s="13" t="inlineStr">
+        <is>
+          <t>End Connections, ANSI Class</t>
+        </is>
+      </c>
+      <c r="V30" s="13" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W30" s="13" t="inlineStr">
+        <is>
+          <t>Size Type and Class</t>
+        </is>
+      </c>
+      <c r="X30" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y30" s="13" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z30" s="13" t="inlineStr">
+        <is>
+          <t>FAIL CLOSE</t>
+        </is>
+      </c>
+      <c r="AA30" s="27" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE30" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF30" s="13" t="inlineStr">
+        <is>
+          <t>KEROSENE</t>
+        </is>
+      </c>
+      <c r="AG30" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH30" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI30" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ30" s="13" t="inlineStr">
+        <is>
+          <t>102.4 m3/H</t>
+        </is>
+      </c>
+      <c r="AK30" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL30" s="13" t="inlineStr">
+        <is>
+          <t>2.86 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM30" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN30" s="13" t="inlineStr">
+        <is>
+          <t>195 ℃</t>
+        </is>
+      </c>
+      <c r="AO30" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP30" s="13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ30" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT30" s="13" t="inlineStr">
+        <is>
+          <t>FISHTAIL BUTTERFLY</t>
+        </is>
+      </c>
+      <c r="AU30" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV30" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 1</t>
+        </is>
+      </c>
+      <c r="AW30" s="13" t="inlineStr">
+        <is>
+          <t>Note, Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX30" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY30" s="13" t="inlineStr">
+        <is>
+          <t>Note, Trim Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE30" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seal/Liner Material</t>
+        </is>
+      </c>
+      <c r="BF30" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH30" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI30" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
+        </is>
+      </c>
+      <c r="BJ30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK30" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL30" s="13" t="inlineStr">
+        <is>
+          <t>3610J</t>
+        </is>
+      </c>
+      <c r="BM30" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
+        </is>
+      </c>
+      <c r="BN30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -9399,71 +10881,321 @@
           <t>d029</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="O31" s="13" t="n"/>
-      <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="13" t="n"/>
-      <c r="R31" s="13" t="n"/>
-      <c r="S31" s="13" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="13" t="n"/>
-      <c r="V31" s="13" t="n"/>
-      <c r="W31" s="13" t="n"/>
-      <c r="X31" s="13" t="n"/>
-      <c r="Y31" s="13" t="n"/>
-      <c r="Z31" s="13" t="n"/>
-      <c r="AA31" s="13" t="n"/>
-      <c r="AB31" s="13" t="n"/>
-      <c r="AC31" s="13" t="n"/>
-      <c r="AD31" s="13" t="n"/>
-      <c r="AE31" s="13" t="n"/>
-      <c r="AF31" s="13" t="n"/>
-      <c r="AG31" s="13" t="n"/>
-      <c r="AH31" s="13" t="n"/>
-      <c r="AI31" s="13" t="n"/>
-      <c r="AJ31" s="13" t="n"/>
-      <c r="AK31" s="13" t="n"/>
-      <c r="AL31" s="13" t="n"/>
-      <c r="AM31" s="13" t="n"/>
-      <c r="AN31" s="13" t="n"/>
-      <c r="AO31" s="13" t="n"/>
-      <c r="AP31" s="13" t="n"/>
-      <c r="AQ31" s="13" t="n"/>
-      <c r="AR31" s="13" t="n"/>
-      <c r="AS31" s="13" t="n"/>
-      <c r="AT31" s="13" t="n"/>
-      <c r="AU31" s="13" t="n"/>
-      <c r="AV31" s="13" t="n"/>
-      <c r="AW31" s="13" t="n"/>
-      <c r="AX31" s="13" t="n"/>
-      <c r="AY31" s="13" t="n"/>
-      <c r="AZ31" s="13" t="n"/>
-      <c r="BA31" s="13" t="n"/>
-      <c r="BB31" s="13" t="n"/>
-      <c r="BC31" s="13" t="n"/>
-      <c r="BD31" s="13" t="n"/>
-      <c r="BE31" s="13" t="n"/>
-      <c r="BF31" s="13" t="n"/>
-      <c r="BG31" s="13" t="n"/>
-      <c r="BH31" s="13" t="n"/>
-      <c r="BI31" s="13" t="n"/>
-      <c r="BJ31" s="13" t="n"/>
-      <c r="BK31" s="13" t="n"/>
-      <c r="BL31" s="13" t="n"/>
-      <c r="BM31" s="13" t="n"/>
-      <c r="BN31" s="13" t="n"/>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>10PCV071-DATA SHEET_REV1.pdf</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>pdf(텍스트)</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>10-PCV-071</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>1098-EGR</t>
+        </is>
+      </c>
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="Q31" s="13" t="inlineStr">
+        <is>
+          <t>Wide Open Cv.</t>
+        </is>
+      </c>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>21.119</t>
+        </is>
+      </c>
+      <c r="S31" s="13" t="inlineStr">
+        <is>
+          <t>Sizing Coefficient (Cv), Normal</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t>Body Style, End Connect/In/Out</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr">
+        <is>
+          <t>2"</t>
+        </is>
+      </c>
+      <c r="W31" s="13" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>WCC Steel</t>
+        </is>
+      </c>
+      <c r="Y31" s="13" t="inlineStr">
+        <is>
+          <t>Body Style, Material</t>
+        </is>
+      </c>
+      <c r="Z31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AB31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF31" s="13" t="inlineStr">
+        <is>
+          <t>Fuel GAS</t>
+        </is>
+      </c>
+      <c r="AG31" s="13" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="AH31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ31" s="13" t="inlineStr">
+        <is>
+          <t>1730.00000Nm3/h</t>
+        </is>
+      </c>
+      <c r="AK31" s="13" t="inlineStr">
+        <is>
+          <t>Volumetric Flow Rate Gas (Qg), Normal</t>
+        </is>
+      </c>
+      <c r="AL31" s="13" t="inlineStr">
+        <is>
+          <t>2.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM31" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Pressure (P1), Normal</t>
+        </is>
+      </c>
+      <c r="AN31" s="13" t="inlineStr">
+        <is>
+          <t>49  ℃</t>
+        </is>
+      </c>
+      <c r="AO31" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature (T1), Normal</t>
+        </is>
+      </c>
+      <c r="AP31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AR31" s="13" t="inlineStr">
+        <is>
+          <t>1 cP</t>
+        </is>
+      </c>
+      <c r="AS31" s="13" t="inlineStr">
+        <is>
+          <t>Dynamic Viscosity (Mu)</t>
+        </is>
+      </c>
+      <c r="AT31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD31" s="13" t="inlineStr">
+        <is>
+          <t>NBR</t>
+        </is>
+      </c>
+      <c r="BE31" s="13" t="inlineStr">
+        <is>
+          <t>Disk/Seat Material:</t>
+        </is>
+      </c>
+      <c r="BF31" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BJ31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK31" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL31" s="13" t="n">
+        <v>6351</v>
+      </c>
+      <c r="BM31" s="13" t="inlineStr">
+        <is>
+          <t>Pilot Type</t>
+        </is>
+      </c>
+      <c r="BN31" s="13" t="inlineStr">
+        <is>
+          <t>PCV는 제외 고민(별도 시스템으로 분리 고민)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -9471,71 +11203,325 @@
           <t>d030</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="13" t="n"/>
-      <c r="N32" s="13" t="n"/>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="13" t="n"/>
-      <c r="S32" s="13" t="n"/>
-      <c r="T32" s="13" t="n"/>
-      <c r="U32" s="13" t="n"/>
-      <c r="V32" s="13" t="n"/>
-      <c r="W32" s="13" t="n"/>
-      <c r="X32" s="13" t="n"/>
-      <c r="Y32" s="13" t="n"/>
-      <c r="Z32" s="13" t="n"/>
-      <c r="AA32" s="13" t="n"/>
-      <c r="AB32" s="13" t="n"/>
-      <c r="AC32" s="13" t="n"/>
-      <c r="AD32" s="13" t="n"/>
-      <c r="AE32" s="13" t="n"/>
-      <c r="AF32" s="13" t="n"/>
-      <c r="AG32" s="13" t="n"/>
-      <c r="AH32" s="13" t="n"/>
-      <c r="AI32" s="13" t="n"/>
-      <c r="AJ32" s="13" t="n"/>
-      <c r="AK32" s="13" t="n"/>
-      <c r="AL32" s="13" t="n"/>
-      <c r="AM32" s="13" t="n"/>
-      <c r="AN32" s="13" t="n"/>
-      <c r="AO32" s="13" t="n"/>
-      <c r="AP32" s="13" t="n"/>
-      <c r="AQ32" s="13" t="n"/>
-      <c r="AR32" s="13" t="n"/>
-      <c r="AS32" s="13" t="n"/>
-      <c r="AT32" s="13" t="n"/>
-      <c r="AU32" s="13" t="n"/>
-      <c r="AV32" s="13" t="n"/>
-      <c r="AW32" s="13" t="n"/>
-      <c r="AX32" s="13" t="n"/>
-      <c r="AY32" s="13" t="n"/>
-      <c r="AZ32" s="13" t="n"/>
-      <c r="BA32" s="13" t="n"/>
-      <c r="BB32" s="13" t="n"/>
-      <c r="BC32" s="13" t="n"/>
-      <c r="BD32" s="13" t="n"/>
-      <c r="BE32" s="13" t="n"/>
-      <c r="BF32" s="13" t="n"/>
-      <c r="BG32" s="13" t="n"/>
-      <c r="BH32" s="13" t="n"/>
-      <c r="BI32" s="13" t="n"/>
-      <c r="BJ32" s="13" t="n"/>
-      <c r="BK32" s="13" t="n"/>
-      <c r="BL32" s="13" t="n"/>
-      <c r="BM32" s="13" t="n"/>
-      <c r="BN32" s="13" t="n"/>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>10PDV067-DATA SHEET_REV2.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>datasheet_embedded</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>10-PDV-067</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Tag No.</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N32" s="13" t="inlineStr">
+        <is>
+          <t>667-EZ</t>
+        </is>
+      </c>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q32" s="13" t="inlineStr">
+        <is>
+          <t>'Rated Cg' = 365 — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S32" s="13" t="inlineStr">
+        <is>
+          <t>'Calculated Cg' = 46.7 / 132 / 159 (최소·정상·최대) — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T32" s="13" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U32" s="13" t="inlineStr">
+        <is>
+          <t>BODY, Rating</t>
+        </is>
+      </c>
+      <c r="V32" s="13" t="inlineStr">
+        <is>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="W32" s="13" t="inlineStr">
+        <is>
+          <t>Body Size</t>
+        </is>
+      </c>
+      <c r="X32" s="13" t="inlineStr">
+        <is>
+          <t>A216 Gr-WCB</t>
+        </is>
+      </c>
+      <c r="Y32" s="13" t="inlineStr">
+        <is>
+          <t>Material, Body</t>
+        </is>
+      </c>
+      <c r="Z32" s="13" t="inlineStr">
+        <is>
+          <t>FAIL CLOSE</t>
+        </is>
+      </c>
+      <c r="AA32" s="13" t="inlineStr">
+        <is>
+          <t>ACT'N, Fail Position</t>
+        </is>
+      </c>
+      <c r="AB32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF32" s="13" t="inlineStr">
+        <is>
+          <t>ATOMIZING STEAM</t>
+        </is>
+      </c>
+      <c r="AG32" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITION, Fluid</t>
+        </is>
+      </c>
+      <c r="AH32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ32" s="13" t="inlineStr">
+        <is>
+          <t>380 kg/h</t>
+        </is>
+      </c>
+      <c r="AK32" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, Flow Rate, NOR</t>
+        </is>
+      </c>
+      <c r="AL32" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM32" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, In.Press., NOR</t>
+        </is>
+      </c>
+      <c r="AN32" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO32" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, Temp., NOR</t>
+        </is>
+      </c>
+      <c r="AP32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ32" s="13" t="inlineStr">
+        <is>
+          <t>'Density' 행 = 4.95 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+        </is>
+      </c>
+      <c r="AR32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT32" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU32" s="13" t="inlineStr">
+        <is>
+          <t>Body Type</t>
+        </is>
+      </c>
+      <c r="AV32" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW32" s="13" t="inlineStr">
+        <is>
+          <t>Leakage Spec.</t>
+        </is>
+      </c>
+      <c r="AX32" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY32" s="13" t="inlineStr">
+        <is>
+          <t>BODY, Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ32" s="13" t="inlineStr">
+        <is>
+          <t>316SST+STELLITE</t>
+        </is>
+      </c>
+      <c r="BA32" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Plug</t>
+        </is>
+      </c>
+      <c r="BB32" s="13" t="inlineStr">
+        <is>
+          <t>316SST</t>
+        </is>
+      </c>
+      <c r="BC32" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Retainer or Cage</t>
+        </is>
+      </c>
+      <c r="BD32" s="13" t="inlineStr">
+        <is>
+          <t>316 SST+STELLITE</t>
+        </is>
+      </c>
+      <c r="BE32" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Seat Ring</t>
+        </is>
+      </c>
+      <c r="BF32" s="29" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BG32" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Stem</t>
+        </is>
+      </c>
+      <c r="BH32" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI32" s="13" t="inlineStr">
+        <is>
+          <t>Actuator Type</t>
+        </is>
+      </c>
+      <c r="BJ32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK32" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL32" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM32" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="BN32" s="13" t="inlineStr">
+        <is>
+          <t>Nippon Fisher 계열 Cg 기반 양식 — 유량계수가 Cg 로만 기재되고 Cv 는 문서에 없다. Cg = C1 × Cv 이나 환산값은 마스터 열에서 읽은 값과 구별되지 않으므로 NA + 원문라벨로 남긴다(TODO T7).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9543,9 +11529,323 @@
           <t>d031</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>11PV037-DATA SHEET_REV0.tif</t>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>10PV031-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>10-PV-031</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N33" s="13" t="inlineStr">
+        <is>
+          <t>657-ED</t>
+        </is>
+      </c>
+      <c r="O33" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q33" s="13" t="inlineStr">
+        <is>
+          <t>Valve Coefficient Cg = 13900 (C1=35.3) — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S33" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cg☒ = 1634 — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T33" s="13" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U33" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V33" s="13" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="W33" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X33" s="13" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y33" s="13" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z33" s="29" t="inlineStr">
+        <is>
+          <t>FAIL OPEN</t>
+        </is>
+      </c>
+      <c r="AA33" s="27" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF33" s="13" t="inlineStr">
+        <is>
+          <t>M.P. STEAM</t>
+        </is>
+      </c>
+      <c r="AG33" s="13" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ33" s="13" t="inlineStr">
+        <is>
+          <t>3330 kg/h</t>
+        </is>
+      </c>
+      <c r="AK33" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL33" s="13" t="inlineStr">
+        <is>
+          <t>12.9 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM33" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN33" s="13" t="inlineStr">
+        <is>
+          <t>194 ℃</t>
+        </is>
+      </c>
+      <c r="AO33" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ33" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity 행 = 6.97 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+        </is>
+      </c>
+      <c r="AR33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT33" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU33" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV33" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 2</t>
+        </is>
+      </c>
+      <c r="AW33" s="27" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX33" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY33" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ33" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA33" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB33" s="13" t="inlineStr">
+        <is>
+          <t>17-4PH SST</t>
+        </is>
+      </c>
+      <c r="BC33" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD33" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE33" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF33" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH33" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI33" s="13" t="inlineStr">
+        <is>
+          <t>Actuator - Style</t>
+        </is>
+      </c>
+      <c r="BJ33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL33" s="13" t="inlineStr">
+        <is>
+          <t>3582G</t>
+        </is>
+      </c>
+      <c r="BM33" s="13" t="inlineStr">
+        <is>
+          <t>Positioner, Type</t>
+        </is>
+      </c>
+      <c r="BN33" s="13" t="inlineStr">
+        <is>
+          <t>Nippon Fisher 계열 Cg 기반 양식 — 유량계수가 Cg 로만 기재되고 Cv 는 문서에 없다. Cg = C1 × Cv 이나 환산값은 마스터 열에서 읽은 값과 구별되지 않으므로 NA + 원문라벨로 남긴다(TODO T7).</t>
         </is>
       </c>
     </row>
@@ -9555,11 +11855,321 @@
           <t>d032</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>23PCV005-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>10PV081-DATA SHEET_REV2.pdf</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>pdf(텍스트)</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>datasheet_embedded</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>강민호</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>10-PV-081</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Tag Number</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>VALSTONE</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>(우측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N34" s="13" t="inlineStr">
+        <is>
+          <t>680-4122</t>
+        </is>
+      </c>
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+      <c r="P34" s="13" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="Q34" s="13" t="inlineStr">
+        <is>
+          <t>Rated Cv</t>
+        </is>
+      </c>
+      <c r="R34" s="13" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="S34" s="13" t="inlineStr">
+        <is>
+          <t>Calculated Cv, NOR</t>
+        </is>
+      </c>
+      <c r="T34" s="13" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U34" s="13" t="inlineStr">
+        <is>
+          <t>BODY, Rating</t>
+        </is>
+      </c>
+      <c r="V34" s="13" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="W34" s="13" t="inlineStr">
+        <is>
+          <t>Body Size</t>
+        </is>
+      </c>
+      <c r="X34" s="13" t="inlineStr">
+        <is>
+          <t>A216 Gr.-WCB</t>
+        </is>
+      </c>
+      <c r="Y34" s="13" t="inlineStr">
+        <is>
+          <t>Material, Body</t>
+        </is>
+      </c>
+      <c r="Z34" s="13" t="inlineStr">
+        <is>
+          <t>FAIL OPEN</t>
+        </is>
+      </c>
+      <c r="AA34" s="13" t="inlineStr">
+        <is>
+          <t>ACT'N, Fail Position</t>
+        </is>
+      </c>
+      <c r="AB34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF34" s="13" t="inlineStr">
+        <is>
+          <t>HS CRUDE</t>
+        </is>
+      </c>
+      <c r="AG34" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, Fluid</t>
+        </is>
+      </c>
+      <c r="AH34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ34" s="13" t="inlineStr">
+        <is>
+          <t>553 m3/hr</t>
+        </is>
+      </c>
+      <c r="AK34" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS. Flow Rate, NOR</t>
+        </is>
+      </c>
+      <c r="AL34" s="13" t="inlineStr">
+        <is>
+          <t>12 kg/cm2</t>
+        </is>
+      </c>
+      <c r="AM34" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, Inlet Press., NOR</t>
+        </is>
+      </c>
+      <c r="AN34" s="13" t="inlineStr">
+        <is>
+          <t>143 ℃</t>
+        </is>
+      </c>
+      <c r="AO34" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, Inlet Temp., NOR</t>
+        </is>
+      </c>
+      <c r="AP34" s="13" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="AQ34" s="13" t="inlineStr">
+        <is>
+          <t>SERVICE CONDITIONS, Density(Sp.Gr.), NOR</t>
+        </is>
+      </c>
+      <c r="AR34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS34" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT34" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>Body Type</t>
+        </is>
+      </c>
+      <c r="AV34" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 3</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>Leakage Spec.</t>
+        </is>
+      </c>
+      <c r="AX34" s="13" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY34" s="13" t="inlineStr">
+        <is>
+          <t>Flow Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ34" s="13" t="inlineStr">
+        <is>
+          <t>630SST</t>
+        </is>
+      </c>
+      <c r="BA34" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Plug</t>
+        </is>
+      </c>
+      <c r="BB34" s="13" t="inlineStr">
+        <is>
+          <t>630SST</t>
+        </is>
+      </c>
+      <c r="BC34" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Cage</t>
+        </is>
+      </c>
+      <c r="BD34" s="13" t="inlineStr">
+        <is>
+          <t>410SST</t>
+        </is>
+      </c>
+      <c r="BE34" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Seat Ring</t>
+        </is>
+      </c>
+      <c r="BF34" s="29" t="inlineStr">
+        <is>
+          <t>630SST</t>
+        </is>
+      </c>
+      <c r="BG34" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Stem</t>
+        </is>
+      </c>
+      <c r="BH34" s="13" t="inlineStr">
+        <is>
+          <t>CYLINDER</t>
+        </is>
+      </c>
+      <c r="BI34" s="13" t="inlineStr">
+        <is>
+          <t>Actuator Type</t>
+        </is>
+      </c>
+      <c r="BJ34" s="13" t="inlineStr">
+        <is>
+          <t>MASONEILAN</t>
+        </is>
+      </c>
+      <c r="BK34" s="13" t="inlineStr">
+        <is>
+          <t>POSITIONER, Model No.</t>
+        </is>
+      </c>
+      <c r="BL34" s="13" t="inlineStr">
+        <is>
+          <t>4280E</t>
+        </is>
+      </c>
+      <c r="BM34" s="13" t="inlineStr">
+        <is>
+          <t>POSITIONER, Model No.</t>
+        </is>
+      </c>
+      <c r="BN34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9567,11 +12177,6 @@
           <t>d033</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>19FV064-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9579,11 +12184,6 @@
           <t>d034</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>070055_REV0.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9591,11 +12191,6 @@
           <t>d035</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>B10LV1073-DATA SHEET_REV1.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -9603,315 +12198,11 @@
           <t>d036</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>10FV634-DATA SHEET_REV0.pdf</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>pdf(텍스트)</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>현행</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
-        <is>
-          <t>10-FV-634</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>Valve Tag #</t>
-        </is>
-      </c>
-      <c r="L38" s="13" t="inlineStr">
-        <is>
-          <t>FLOWSERVE</t>
-        </is>
-      </c>
-      <c r="M38" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N38" s="13" t="inlineStr">
-        <is>
-          <t>?Mark One</t>
-        </is>
-      </c>
-      <c r="O38" s="13" t="inlineStr">
-        <is>
-          <t>Model / Body Type / Trim Type</t>
-        </is>
-      </c>
-      <c r="P38" s="13" t="n">
-        <v>538</v>
-      </c>
-      <c r="Q38" s="13" t="inlineStr">
-        <is>
-          <t>Trim # - Cv</t>
-        </is>
-      </c>
-      <c r="R38" s="13" t="inlineStr">
-        <is>
-          <t>249.719</t>
-        </is>
-      </c>
-      <c r="S38" s="13" t="inlineStr">
-        <is>
-          <t>Flow Coeff. (Cv)</t>
-        </is>
-      </c>
-      <c r="T38" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="U38" s="13" t="inlineStr">
-        <is>
-          <t>Size/Pressure Class/Body Form</t>
-        </is>
-      </c>
-      <c r="V38" s="13" t="inlineStr">
-        <is>
-          <t>8"</t>
-        </is>
-      </c>
-      <c r="W38" s="13" t="inlineStr">
-        <is>
-          <t>Size/Pressure Class/Body Form</t>
-        </is>
-      </c>
-      <c r="X38" s="13" t="inlineStr">
-        <is>
-          <t>Cr-Mo C5; F5a</t>
-        </is>
-      </c>
-      <c r="Y38" s="13" t="inlineStr">
-        <is>
-          <t>Body Matl / Bonnet Matl</t>
-        </is>
-      </c>
-      <c r="Z38" s="13" t="inlineStr">
-        <is>
-          <t>Fail Open</t>
-        </is>
-      </c>
-      <c r="AA38" s="13" t="inlineStr">
-        <is>
-          <t>Fail/Air-To</t>
-        </is>
-      </c>
-      <c r="AB38" s="13" t="inlineStr">
-        <is>
-          <t>Flow Control Valve</t>
-        </is>
-      </c>
-      <c r="AC38" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 FV를 보고 Flow Control Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF38" s="13" t="inlineStr">
-        <is>
-          <t>LS AR / LIQUID</t>
-        </is>
-      </c>
-      <c r="AG38" s="13" t="inlineStr">
-        <is>
-          <t>Process Fluid</t>
-        </is>
-      </c>
-      <c r="AH38" s="13" t="inlineStr">
-        <is>
-          <t>LIQUID</t>
-        </is>
-      </c>
-      <c r="AI38" s="13" t="inlineStr">
-        <is>
-          <t>Process Fluid</t>
-        </is>
-      </c>
-      <c r="AJ38" s="13" t="inlineStr">
-        <is>
-          <t>164332.000 kg/h</t>
-        </is>
-      </c>
-      <c r="AK38" s="13" t="inlineStr">
-        <is>
-          <t>Liq Flow Rate (kg/h)</t>
-        </is>
-      </c>
-      <c r="AL38" s="13" t="inlineStr">
-        <is>
-          <t>19.1 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM38" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Press</t>
-        </is>
-      </c>
-      <c r="AN38" s="13" t="inlineStr">
-        <is>
-          <t>291.2 °C</t>
-        </is>
-      </c>
-      <c r="AO38" s="13" t="inlineStr">
-        <is>
-          <t>Temperature (°C)</t>
-        </is>
-      </c>
-      <c r="AP38" s="13" t="inlineStr">
-        <is>
-          <t>0.845</t>
-        </is>
-      </c>
-      <c r="AQ38" s="13" t="inlineStr">
-        <is>
-          <t>SG-MW</t>
-        </is>
-      </c>
-      <c r="AR38" s="13" t="n">
-        <v>1.705</v>
-      </c>
-      <c r="AS38" s="13" t="inlineStr">
-        <is>
-          <t>Viscosity (cP)</t>
-        </is>
-      </c>
-      <c r="AT38" s="13" t="inlineStr">
-        <is>
-          <t>GLOBE</t>
-        </is>
-      </c>
-      <c r="AU38" s="13" t="inlineStr">
-        <is>
-          <t>Model / Body Type / Trim Type</t>
-        </is>
-      </c>
-      <c r="AV38" s="13" t="inlineStr">
-        <is>
-          <t>Class IV</t>
-        </is>
-      </c>
-      <c r="AW38" s="13" t="inlineStr">
-        <is>
-          <t>Max Shutoff / Shutoff Class</t>
-        </is>
-      </c>
-      <c r="AX38" s="13" t="inlineStr">
-        <is>
-          <t>EQUAL PERCENT</t>
-        </is>
-      </c>
-      <c r="AY38" s="13" t="inlineStr">
-        <is>
-          <t>Trim # - Characteristic</t>
-        </is>
-      </c>
-      <c r="AZ38" s="13" t="inlineStr">
-        <is>
-          <t>316 SS</t>
-        </is>
-      </c>
-      <c r="BA38" s="13" t="inlineStr">
-        <is>
-          <t>Plug Mtl/ Facing|Treatment / Stem Cvr</t>
-        </is>
-      </c>
-      <c r="BB38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BC38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BD38" s="13" t="inlineStr">
-        <is>
-          <t>316 SS</t>
-        </is>
-      </c>
-      <c r="BE38" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring Mtl/ Facing|Treatment</t>
-        </is>
-      </c>
-      <c r="BF38" s="29" t="inlineStr">
-        <is>
-          <t>316 SS</t>
-        </is>
-      </c>
-      <c r="BG38" s="13" t="inlineStr">
-        <is>
-          <t>Stem Mtl/ Facing|Treatment / Pilot Spr</t>
-        </is>
-      </c>
-      <c r="BH38" s="13" t="inlineStr">
-        <is>
-          <t>VL Cylinder</t>
-        </is>
-      </c>
-      <c r="BI38" s="13" t="inlineStr">
-        <is>
-          <t>Act. Type</t>
-        </is>
-      </c>
-      <c r="BJ38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL38" s="13" t="inlineStr">
-        <is>
-          <t>3821-28EA-D41L-0130-00</t>
-        </is>
-      </c>
-      <c r="BM38" s="13" t="inlineStr">
-        <is>
-          <t>Positioner Model #</t>
-        </is>
-      </c>
-      <c r="BN38" s="13" t="n"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11PV037-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -9919,319 +12210,11 @@
           <t>d037</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>10HV010-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>tif</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>레거시</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>10-HV-010</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="M39" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N39" s="13" t="inlineStr">
-        <is>
-          <t>667-ED</t>
-        </is>
-      </c>
-      <c r="O39" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="P39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="S39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T39" s="13" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="U39" s="13" t="inlineStr">
-        <is>
-          <t>Fig. ANSI class</t>
-        </is>
-      </c>
-      <c r="V39" s="13" t="inlineStr">
-        <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="W39" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="X39" s="13" t="inlineStr">
-        <is>
-          <t>WCB Steel</t>
-        </is>
-      </c>
-      <c r="Y39" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="Z39" s="13" t="inlineStr">
-        <is>
-          <t>Fail Close</t>
-        </is>
-      </c>
-      <c r="AA39" s="13" t="inlineStr">
-        <is>
-          <t>Air Fails Valve to</t>
-        </is>
-      </c>
-      <c r="AB39" s="13" t="inlineStr">
-        <is>
-          <t>Hand Valve</t>
-        </is>
-      </c>
-      <c r="AC39" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 HV를 보고 Hand Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF39" s="13" t="inlineStr">
-        <is>
-          <t>S.H. STEAM</t>
-        </is>
-      </c>
-      <c r="AG39" s="13" t="inlineStr">
-        <is>
-          <t>Flowing Media</t>
-        </is>
-      </c>
-      <c r="AH39" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="AI39" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AK39" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate, Give Units</t>
-        </is>
-      </c>
-      <c r="AL39" s="13" t="inlineStr">
-        <is>
-          <t>2.7 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM39" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Pressure</t>
-        </is>
-      </c>
-      <c r="AN39" s="13" t="inlineStr">
-        <is>
-          <t>371 ℃</t>
-        </is>
-      </c>
-      <c r="AO39" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temperature</t>
-        </is>
-      </c>
-      <c r="AP39" s="13" t="inlineStr">
-        <is>
-          <t>1.196 kg/m3</t>
-        </is>
-      </c>
-      <c r="AQ39" s="13" t="inlineStr">
-        <is>
-          <t>Specific Gravity</t>
-        </is>
-      </c>
-      <c r="AR39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT39" s="13" t="inlineStr">
-        <is>
-          <t>GLOBE</t>
-        </is>
-      </c>
-      <c r="AU39" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="AV39" s="13" t="inlineStr">
-        <is>
-          <t>ANSI Class IV</t>
-        </is>
-      </c>
-      <c r="AW39" s="13" t="inlineStr">
-        <is>
-          <t>Shutoff Class</t>
-        </is>
-      </c>
-      <c r="AX39" s="13" t="inlineStr">
-        <is>
-          <t>EQUAL PERCENT</t>
-        </is>
-      </c>
-      <c r="AY39" s="13" t="inlineStr">
-        <is>
-          <t>Plug or Cage</t>
-        </is>
-      </c>
-      <c r="AZ39" s="13" t="inlineStr">
-        <is>
-          <t>316 SST/CoCr-A</t>
-        </is>
-      </c>
-      <c r="BA39" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="BB39" s="13" t="inlineStr">
-        <is>
-          <t>17-4PH SST</t>
-        </is>
-      </c>
-      <c r="BC39" s="13" t="inlineStr">
-        <is>
-          <t>Cage and/or Bushing Material</t>
-        </is>
-      </c>
-      <c r="BD39" s="13" t="inlineStr">
-        <is>
-          <t>CAST CoCr-A</t>
-        </is>
-      </c>
-      <c r="BE39" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring Material</t>
-        </is>
-      </c>
-      <c r="BF39" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BH39" s="13" t="inlineStr">
-        <is>
-          <t>Diaph</t>
-        </is>
-      </c>
-      <c r="BI39" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="BJ39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK39" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL39" s="13" t="inlineStr">
-        <is>
-          <t>3582G</t>
-        </is>
-      </c>
-      <c r="BM39" s="13" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
-        </is>
-      </c>
-      <c r="BN39" s="13" t="n"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>23PCV005-DATA SHEET_REV0.tif</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -10239,321 +12222,9 @@
           <t>d038</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>10HV013-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>tif</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>레거시</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>10-HV-013</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="M40" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N40" s="13" t="inlineStr">
-        <is>
-          <t>667-ES</t>
-        </is>
-      </c>
-      <c r="O40" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="P40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="S40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T40" s="13" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="U40" s="13" t="inlineStr">
-        <is>
-          <t>Flg. ANSI Class</t>
-        </is>
-      </c>
-      <c r="V40" s="13" t="inlineStr">
-        <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="W40" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="X40" s="13" t="inlineStr">
-        <is>
-          <t>WCB Steel</t>
-        </is>
-      </c>
-      <c r="Y40" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="Z40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AA40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AB40" s="13" t="inlineStr">
-        <is>
-          <t>Hand Valve</t>
-        </is>
-      </c>
-      <c r="AC40" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 HV를 보고 Hand Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF40" s="13" t="inlineStr">
-        <is>
-          <t>M.P. STEAM</t>
-        </is>
-      </c>
-      <c r="AG40" s="13" t="inlineStr">
-        <is>
-          <t>Flowing Media</t>
-        </is>
-      </c>
-      <c r="AH40" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="AI40" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AK40" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate, Give Units</t>
-        </is>
-      </c>
-      <c r="AL40" s="13" t="inlineStr">
-        <is>
-          <t>10.5 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM40" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Pressure</t>
-        </is>
-      </c>
-      <c r="AN40" s="13" t="inlineStr">
-        <is>
-          <t>243 ℃</t>
-        </is>
-      </c>
-      <c r="AO40" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temperature °C</t>
-        </is>
-      </c>
-      <c r="AP40" s="13" t="inlineStr">
-        <is>
-          <t>4.95 kg/m3</t>
-        </is>
-      </c>
-      <c r="AQ40" s="13" t="inlineStr">
-        <is>
-          <t>Specific Gravity</t>
-        </is>
-      </c>
-      <c r="AR40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT40" s="13" t="inlineStr">
-        <is>
-          <t>GLOBE</t>
-        </is>
-      </c>
-      <c r="AU40" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="AV40" s="13" t="inlineStr">
-        <is>
-          <t>ANSI Class IV</t>
-        </is>
-      </c>
-      <c r="AW40" s="13" t="inlineStr">
-        <is>
-          <t>Shutoff Class</t>
-        </is>
-      </c>
-      <c r="AX40" s="13" t="inlineStr">
-        <is>
-          <t>LINEAR</t>
-        </is>
-      </c>
-      <c r="AY40" s="13" t="inlineStr">
-        <is>
-          <t>Plug or Cage</t>
-        </is>
-      </c>
-      <c r="AZ40" s="13" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BA40" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="BB40" s="13" t="inlineStr">
-        <is>
-          <t>316 SST/ENC</t>
-        </is>
-      </c>
-      <c r="BC40" s="13" t="inlineStr">
-        <is>
-          <t>Cage and/or Bushing Material</t>
-        </is>
-      </c>
-      <c r="BD40" s="13" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BE40" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring Material</t>
-        </is>
-      </c>
-      <c r="BF40" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BH40" s="13" t="inlineStr">
-        <is>
-          <t>Diaph.</t>
-        </is>
-      </c>
-      <c r="BI40" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="BJ40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL40" s="13" t="inlineStr">
-        <is>
-          <t>3582G</t>
-        </is>
-      </c>
-      <c r="BM40" s="13" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
-        </is>
-      </c>
-      <c r="BN40" s="13" t="inlineStr">
-        <is>
-          <t>Fail Close/Open 식별 불가(중복 표기)</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19FV064-DATA SHEET_REV0.tif</t>
         </is>
       </c>
     </row>
@@ -10563,319 +12234,11 @@
           <t>d039</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>10HV014-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>tif</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>레거시</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
-        <is>
-          <t>10-HV-014</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="M41" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N41" s="13" t="inlineStr">
-        <is>
-          <t>667-ED</t>
-        </is>
-      </c>
-      <c r="O41" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="P41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="S41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T41" s="13" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="U41" s="13" t="inlineStr">
-        <is>
-          <t>Flg. ANSI class</t>
-        </is>
-      </c>
-      <c r="V41" s="13" t="inlineStr">
-        <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="W41" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="X41" s="13" t="inlineStr">
-        <is>
-          <t>WCB Steel</t>
-        </is>
-      </c>
-      <c r="Y41" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="Z41" s="13" t="inlineStr">
-        <is>
-          <t>Fail Close</t>
-        </is>
-      </c>
-      <c r="AA41" s="13" t="inlineStr">
-        <is>
-          <t>Air Fails Valve to</t>
-        </is>
-      </c>
-      <c r="AB41" s="13" t="inlineStr">
-        <is>
-          <t>Hand Valve</t>
-        </is>
-      </c>
-      <c r="AC41" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 HV를 보고 Hand Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF41" s="13" t="inlineStr">
-        <is>
-          <t>M.P. STEAM</t>
-        </is>
-      </c>
-      <c r="AG41" s="13" t="inlineStr">
-        <is>
-          <t>Flowing Media</t>
-        </is>
-      </c>
-      <c r="AH41" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="AI41" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AK41" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate, Give Units</t>
-        </is>
-      </c>
-      <c r="AL41" s="13" t="inlineStr">
-        <is>
-          <t>10.5 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM41" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Pressure</t>
-        </is>
-      </c>
-      <c r="AN41" s="13" t="inlineStr">
-        <is>
-          <t>243 ℃</t>
-        </is>
-      </c>
-      <c r="AO41" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temperature</t>
-        </is>
-      </c>
-      <c r="AP41" s="13" t="inlineStr">
-        <is>
-          <t>4.96 kg/m3</t>
-        </is>
-      </c>
-      <c r="AQ41" s="13" t="inlineStr">
-        <is>
-          <t>Specific Gravity</t>
-        </is>
-      </c>
-      <c r="AR41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT41" s="13" t="inlineStr">
-        <is>
-          <t>GLOBE</t>
-        </is>
-      </c>
-      <c r="AU41" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="AV41" s="13" t="inlineStr">
-        <is>
-          <t>ANSI Class IV</t>
-        </is>
-      </c>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>Shutoff Class</t>
-        </is>
-      </c>
-      <c r="AX41" s="13" t="inlineStr">
-        <is>
-          <t>LINEAR</t>
-        </is>
-      </c>
-      <c r="AY41" s="13" t="inlineStr">
-        <is>
-          <t>Plug or Cage</t>
-        </is>
-      </c>
-      <c r="AZ41" s="13" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BA41" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="BB41" s="13" t="inlineStr">
-        <is>
-          <t>316 SST/ENC</t>
-        </is>
-      </c>
-      <c r="BC41" s="13" t="inlineStr">
-        <is>
-          <t>Cage and/or Bushing Material</t>
-        </is>
-      </c>
-      <c r="BD41" s="13" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BE41" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring Material</t>
-        </is>
-      </c>
-      <c r="BF41" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BH41" s="13" t="inlineStr">
-        <is>
-          <t>Diaph.</t>
-        </is>
-      </c>
-      <c r="BI41" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="BJ41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK41" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL41" s="13" t="inlineStr">
-        <is>
-          <t>3582G</t>
-        </is>
-      </c>
-      <c r="BM41" s="13" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
-        </is>
-      </c>
-      <c r="BN41" s="13" t="n"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>070055_REV0.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -10883,311 +12246,11 @@
           <t>d040</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>10LV012-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>tif</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>레거시</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>10-LV-012</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="L42" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N42" s="13" t="inlineStr">
-        <is>
-          <t>1051-7600</t>
-        </is>
-      </c>
-      <c r="O42" s="13" t="inlineStr">
-        <is>
-          <t>Size Type and Class</t>
-        </is>
-      </c>
-      <c r="P42" s="13" t="n">
-        <v>357</v>
-      </c>
-      <c r="Q42" s="13" t="inlineStr">
-        <is>
-          <t>Maximum Valve Coefficient, Cv</t>
-        </is>
-      </c>
-      <c r="R42" s="13" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="S42" s="13" t="inlineStr">
-        <is>
-          <t>Req'd Flow Coeff., Cv</t>
-        </is>
-      </c>
-      <c r="T42" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="U42" s="13" t="inlineStr">
-        <is>
-          <t>End Connections, ANSI Class</t>
-        </is>
-      </c>
-      <c r="V42" s="13" t="inlineStr">
-        <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="W42" s="13" t="inlineStr">
-        <is>
-          <t>Size Type and Class</t>
-        </is>
-      </c>
-      <c r="X42" s="13" t="inlineStr">
-        <is>
-          <t>WCB Steel</t>
-        </is>
-      </c>
-      <c r="Y42" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="Z42" s="13" t="inlineStr">
-        <is>
-          <t>Fail Close</t>
-        </is>
-      </c>
-      <c r="AA42" s="13" t="inlineStr">
-        <is>
-          <t>Air Fails Valve to</t>
-        </is>
-      </c>
-      <c r="AB42" s="13" t="inlineStr">
-        <is>
-          <t>Level Control Valve</t>
-        </is>
-      </c>
-      <c r="AC42" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 LV를 보고 Level Control Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF42" s="13" t="inlineStr">
-        <is>
-          <t>KEROSENE</t>
-        </is>
-      </c>
-      <c r="AG42" s="13" t="inlineStr">
-        <is>
-          <t>Flowing Media</t>
-        </is>
-      </c>
-      <c r="AH42" s="13" t="inlineStr">
-        <is>
-          <t>LIQUID</t>
-        </is>
-      </c>
-      <c r="AI42" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ42" s="13" t="inlineStr">
-        <is>
-          <t>102.4 m3/H</t>
-        </is>
-      </c>
-      <c r="AK42" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate, Give Units</t>
-        </is>
-      </c>
-      <c r="AL42" s="13" t="inlineStr">
-        <is>
-          <t>2.86 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM42" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Pressure</t>
-        </is>
-      </c>
-      <c r="AN42" s="13" t="inlineStr">
-        <is>
-          <t>195 ℃</t>
-        </is>
-      </c>
-      <c r="AO42" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temperature</t>
-        </is>
-      </c>
-      <c r="AP42" s="13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AQ42" s="13" t="inlineStr">
-        <is>
-          <t>Specific Gravity</t>
-        </is>
-      </c>
-      <c r="AR42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AV42" s="13" t="inlineStr">
-        <is>
-          <t>ANSI Class I</t>
-        </is>
-      </c>
-      <c r="AW42" s="13" t="inlineStr">
-        <is>
-          <t>Shutoff Class</t>
-        </is>
-      </c>
-      <c r="AX42" s="13" t="inlineStr">
-        <is>
-          <t>EQUAL PERCENT</t>
-        </is>
-      </c>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Trim Characteristic</t>
-        </is>
-      </c>
-      <c r="AZ42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BA42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BB42" s="13" t="inlineStr">
-        <is>
-          <t>TFE Lined Fiberglass</t>
-        </is>
-      </c>
-      <c r="BC42" s="13" t="inlineStr">
-        <is>
-          <t>Bushing/Bearing Material</t>
-        </is>
-      </c>
-      <c r="BD42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BE42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BF42" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BH42" s="13" t="inlineStr">
-        <is>
-          <t>Diaph.</t>
-        </is>
-      </c>
-      <c r="BI42" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="BJ42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK42" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL42" s="13" t="inlineStr">
-        <is>
-          <t>3610J</t>
-        </is>
-      </c>
-      <c r="BM42" s="13" t="inlineStr">
-        <is>
-          <t>Positioner Type</t>
-        </is>
-      </c>
-      <c r="BN42" s="13" t="n"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B10LV1073-DATA SHEET_REV1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -11195,315 +12258,6 @@
           <t>d041</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>10PCV071-DATA SHEET_REV1.pdf</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>pdf(텍스트)</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>레거시</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
-        <is>
-          <t>10-PCV-071</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>Tags</t>
-        </is>
-      </c>
-      <c r="L43" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="M43" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N43" s="13" t="inlineStr">
-        <is>
-          <t>1098-EGR</t>
-        </is>
-      </c>
-      <c r="O43" s="13" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="P43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R43" s="13" t="inlineStr">
-        <is>
-          <t>21.119</t>
-        </is>
-      </c>
-      <c r="S43" s="13" t="inlineStr">
-        <is>
-          <t>Sizing Coefficient (Cv)</t>
-        </is>
-      </c>
-      <c r="T43" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="U43" s="13" t="inlineStr">
-        <is>
-          <t>End Connect/In/Out</t>
-        </is>
-      </c>
-      <c r="V43" s="13" t="inlineStr">
-        <is>
-          <t>2"</t>
-        </is>
-      </c>
-      <c r="W43" s="13" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="X43" s="13" t="inlineStr">
-        <is>
-          <t>WCC Steel</t>
-        </is>
-      </c>
-      <c r="Y43" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="Z43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AA43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AB43" s="13" t="inlineStr">
-        <is>
-          <t>Pressure Control Valve</t>
-        </is>
-      </c>
-      <c r="AC43" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 PV를 보고 Pressure Control Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF43" s="13" t="inlineStr">
-        <is>
-          <t>Fuel GAS</t>
-        </is>
-      </c>
-      <c r="AG43" s="13" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="AH43" s="13" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="AI43" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ43" s="13" t="inlineStr">
-        <is>
-          <t>1730.00000Nm3/h</t>
-        </is>
-      </c>
-      <c r="AK43" s="13" t="inlineStr">
-        <is>
-          <t>Volumetric Flow Rate Gas (Qg)</t>
-        </is>
-      </c>
-      <c r="AL43" s="13" t="inlineStr">
-        <is>
-          <t>2.5 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM43" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Pressure (P1)</t>
-        </is>
-      </c>
-      <c r="AN43" s="13" t="inlineStr">
-        <is>
-          <t>49  ℃</t>
-        </is>
-      </c>
-      <c r="AO43" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temperature (T1)</t>
-        </is>
-      </c>
-      <c r="AP43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AQ43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AR43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="13" t="inlineStr">
-        <is>
-          <t>Dynamic Viscosity (Mu)</t>
-        </is>
-      </c>
-      <c r="AT43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AV43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AW43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AX43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AY43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AZ43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BA43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BB43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BC43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BD43" s="13" t="inlineStr">
-        <is>
-          <t>NBR</t>
-        </is>
-      </c>
-      <c r="BE43" s="13" t="inlineStr">
-        <is>
-          <t>Disk/Seat Material:</t>
-        </is>
-      </c>
-      <c r="BF43" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BH43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BI43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BJ43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL43" s="13" t="inlineStr">
-        <is>
-          <t>?6351</t>
-        </is>
-      </c>
-      <c r="BM43" s="13" t="inlineStr">
-        <is>
-          <t>Pilot Type</t>
-        </is>
-      </c>
-      <c r="BN43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -11511,319 +12265,6 @@
           <t>d042</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>10PDV067-DATA SHEET_REV2.xlsx</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>현행</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>datasheet_embedded</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>10-PDV-067</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>Tag No.</t>
-        </is>
-      </c>
-      <c r="L44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="M44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N44" s="13" t="inlineStr">
-        <is>
-          <t>667-EZ</t>
-        </is>
-      </c>
-      <c r="O44" s="13" t="inlineStr">
-        <is>
-          <t>Model No.</t>
-        </is>
-      </c>
-      <c r="P44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="S44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T44" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="U44" s="13" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="V44" s="13" t="inlineStr">
-        <is>
-          <t>1"</t>
-        </is>
-      </c>
-      <c r="W44" s="13" t="inlineStr">
-        <is>
-          <t>Body Size</t>
-        </is>
-      </c>
-      <c r="X44" s="13" t="inlineStr">
-        <is>
-          <t>A216 Gr-WCB</t>
-        </is>
-      </c>
-      <c r="Y44" s="13" t="inlineStr">
-        <is>
-          <t>Material - Body</t>
-        </is>
-      </c>
-      <c r="Z44" s="13" t="inlineStr">
-        <is>
-          <t>Fail Close</t>
-        </is>
-      </c>
-      <c r="AA44" s="13" t="inlineStr">
-        <is>
-          <t>Fail Position</t>
-        </is>
-      </c>
-      <c r="AB44" s="13" t="inlineStr">
-        <is>
-          <t>Pressure Differential Valve</t>
-        </is>
-      </c>
-      <c r="AC44" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 PDV를 보고 Pressure Differential Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF44" s="13" t="inlineStr">
-        <is>
-          <t>ATOMIZING STEAM</t>
-        </is>
-      </c>
-      <c r="AG44" s="13" t="inlineStr">
-        <is>
-          <t>Fluid</t>
-        </is>
-      </c>
-      <c r="AH44" s="13" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="AI44" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ44" s="13" t="inlineStr">
-        <is>
-          <t>380 kg/h</t>
-        </is>
-      </c>
-      <c r="AK44" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate</t>
-        </is>
-      </c>
-      <c r="AL44" s="13" t="inlineStr">
-        <is>
-          <t>10.5 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM44" s="13" t="inlineStr">
-        <is>
-          <t>In.Press.</t>
-        </is>
-      </c>
-      <c r="AN44" s="13" t="inlineStr">
-        <is>
-          <t>243 ℃</t>
-        </is>
-      </c>
-      <c r="AO44" s="13" t="inlineStr">
-        <is>
-          <t>Temp.</t>
-        </is>
-      </c>
-      <c r="AP44" s="13" t="inlineStr">
-        <is>
-          <t>4.95 kg/m3</t>
-        </is>
-      </c>
-      <c r="AQ44" s="13" t="inlineStr">
-        <is>
-          <t>Density</t>
-        </is>
-      </c>
-      <c r="AR44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT44" s="13" t="inlineStr">
-        <is>
-          <t>GLOBE</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>Body Type</t>
-        </is>
-      </c>
-      <c r="AV44" s="13" t="inlineStr">
-        <is>
-          <t>CLASS 4</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>Leakage Spec.</t>
-        </is>
-      </c>
-      <c r="AX44" s="13" t="inlineStr">
-        <is>
-          <t>EQUAL PERCENT</t>
-        </is>
-      </c>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Characteristic</t>
-        </is>
-      </c>
-      <c r="AZ44" s="13" t="inlineStr">
-        <is>
-          <t>316SST+STELLITE</t>
-        </is>
-      </c>
-      <c r="BA44" s="13" t="inlineStr">
-        <is>
-          <t>Plug</t>
-        </is>
-      </c>
-      <c r="BB44" s="13" t="inlineStr">
-        <is>
-          <t>316SST</t>
-        </is>
-      </c>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Retainer or Cage</t>
-        </is>
-      </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>316 SST+STELLITE</t>
-        </is>
-      </c>
-      <c r="BE44" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring</t>
-        </is>
-      </c>
-      <c r="BF44" s="29" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BG44" s="13" t="inlineStr">
-        <is>
-          <t>Stem</t>
-        </is>
-      </c>
-      <c r="BH44" s="13" t="inlineStr">
-        <is>
-          <t>DIAPHRAGM</t>
-        </is>
-      </c>
-      <c r="BI44" s="13" t="inlineStr">
-        <is>
-          <t>Actuator Type</t>
-        </is>
-      </c>
-      <c r="BJ44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK44" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL44" s="13" t="inlineStr">
-        <is>
-          <t>3582G</t>
-        </is>
-      </c>
-      <c r="BM44" s="13" t="inlineStr">
-        <is>
-          <t>Model No.</t>
-        </is>
-      </c>
-      <c r="BN44" s="13" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -11831,319 +12272,6 @@
           <t>d043</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>10PV031-DATA SHEET_REV0.tif</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>tif</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>레거시</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>datasheet</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>10-PV-031</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="L45" s="13" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="M45" s="13" t="inlineStr">
-        <is>
-          <t>(좌측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N45" s="13" t="inlineStr">
-        <is>
-          <t>657-ED</t>
-        </is>
-      </c>
-      <c r="O45" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="P45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="S45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="T45" s="13" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="U45" s="13" t="inlineStr">
-        <is>
-          <t>Flg. ANSI class</t>
-        </is>
-      </c>
-      <c r="V45" s="13" t="inlineStr">
-        <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="W45" s="13" t="inlineStr">
-        <is>
-          <t>Size and Type</t>
-        </is>
-      </c>
-      <c r="X45" s="13" t="inlineStr">
-        <is>
-          <t>WCB Steel</t>
-        </is>
-      </c>
-      <c r="Y45" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="Z45" s="13" t="inlineStr">
-        <is>
-          <t>Fail Open</t>
-        </is>
-      </c>
-      <c r="AA45" s="13" t="inlineStr">
-        <is>
-          <t>Air Fails Valve to</t>
-        </is>
-      </c>
-      <c r="AB45" s="13" t="inlineStr">
-        <is>
-          <t>Pressure Control Valve</t>
-        </is>
-      </c>
-      <c r="AC45" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 PV를 보고 Pressure Control Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF45" s="13" t="inlineStr">
-        <is>
-          <t>M.P. STEAM</t>
-        </is>
-      </c>
-      <c r="AG45" s="13" t="inlineStr">
-        <is>
-          <t>Flowing Media</t>
-        </is>
-      </c>
-      <c r="AH45" s="13" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="AI45" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ45" s="13" t="inlineStr">
-        <is>
-          <t>3330 kg/h</t>
-        </is>
-      </c>
-      <c r="AK45" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate, Give Units</t>
-        </is>
-      </c>
-      <c r="AL45" s="13" t="inlineStr">
-        <is>
-          <t>12.9 kg/cm2G</t>
-        </is>
-      </c>
-      <c r="AM45" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Pressure</t>
-        </is>
-      </c>
-      <c r="AN45" s="13" t="inlineStr">
-        <is>
-          <t>194 ℃</t>
-        </is>
-      </c>
-      <c r="AO45" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temperature</t>
-        </is>
-      </c>
-      <c r="AP45" s="13" t="inlineStr">
-        <is>
-          <t>6.97 kg/m3</t>
-        </is>
-      </c>
-      <c r="AQ45" s="13" t="inlineStr">
-        <is>
-          <t>Specific Gravity</t>
-        </is>
-      </c>
-      <c r="AR45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT45" s="13" t="inlineStr">
-        <is>
-          <t>Globe</t>
-        </is>
-      </c>
-      <c r="AU45" s="13" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-      <c r="AV45" s="13" t="inlineStr">
-        <is>
-          <t>ANSI Class II</t>
-        </is>
-      </c>
-      <c r="AW45" s="13" t="inlineStr">
-        <is>
-          <t>Shutoff Class</t>
-        </is>
-      </c>
-      <c r="AX45" s="13" t="inlineStr">
-        <is>
-          <t>EQUAL PERCENT</t>
-        </is>
-      </c>
-      <c r="AY45" s="13" t="inlineStr">
-        <is>
-          <t>Plug or Cage</t>
-        </is>
-      </c>
-      <c r="AZ45" s="13" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BA45" s="13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="BB45" s="13" t="inlineStr">
-        <is>
-          <t>17-4PH SST</t>
-        </is>
-      </c>
-      <c r="BC45" s="13" t="inlineStr">
-        <is>
-          <t>Cage and/or Bushing Material</t>
-        </is>
-      </c>
-      <c r="BD45" s="13" t="inlineStr">
-        <is>
-          <t>316 SST</t>
-        </is>
-      </c>
-      <c r="BE45" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring Material</t>
-        </is>
-      </c>
-      <c r="BF45" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BH45" s="13" t="inlineStr">
-        <is>
-          <t>DIAPHRAGM</t>
-        </is>
-      </c>
-      <c r="BI45" s="13" t="inlineStr">
-        <is>
-          <t>Actuator - Style</t>
-        </is>
-      </c>
-      <c r="BJ45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK45" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL45" s="13" t="inlineStr">
-        <is>
-          <t>3582G</t>
-        </is>
-      </c>
-      <c r="BM45" s="13" t="inlineStr">
-        <is>
-          <t>Positioner - Type</t>
-        </is>
-      </c>
-      <c r="BN45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -12151,321 +12279,6 @@
           <t>d044</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>10PV081-DATA SHEET_REV2.pdf</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>pdf(텍스트)</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>현행</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>datasheet_embedded</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>AI초안(Claude)</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>10-PV-081</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>Tag Number</t>
-        </is>
-      </c>
-      <c r="L46" s="13" t="inlineStr">
-        <is>
-          <t>VALSTONE</t>
-        </is>
-      </c>
-      <c r="M46" s="13" t="inlineStr">
-        <is>
-          <t>(우측 상단 로고)</t>
-        </is>
-      </c>
-      <c r="N46" s="13" t="inlineStr">
-        <is>
-          <t>680-4122</t>
-        </is>
-      </c>
-      <c r="O46" s="13" t="inlineStr">
-        <is>
-          <t>Model No.</t>
-        </is>
-      </c>
-      <c r="P46" s="13" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="Q46" s="13" t="inlineStr">
-        <is>
-          <t>Rated Cv</t>
-        </is>
-      </c>
-      <c r="R46" s="13" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="S46" s="13" t="inlineStr">
-        <is>
-          <t>Calculated Cv</t>
-        </is>
-      </c>
-      <c r="T46" s="13" t="inlineStr">
-        <is>
-          <t>ANSI CLASS 300</t>
-        </is>
-      </c>
-      <c r="U46" s="13" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="V46" s="13" t="inlineStr">
-        <is>
-          <t>12"</t>
-        </is>
-      </c>
-      <c r="W46" s="13" t="inlineStr">
-        <is>
-          <t>Body Size</t>
-        </is>
-      </c>
-      <c r="X46" s="13" t="inlineStr">
-        <is>
-          <t>A216 Gr.-WCB</t>
-        </is>
-      </c>
-      <c r="Y46" s="13" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="Z46" s="13" t="inlineStr">
-        <is>
-          <t>FAIL OPEN</t>
-        </is>
-      </c>
-      <c r="AA46" s="13" t="inlineStr">
-        <is>
-          <t>Fail Position</t>
-        </is>
-      </c>
-      <c r="AB46" s="13" t="inlineStr">
-        <is>
-          <t>Pressure Control Valve</t>
-        </is>
-      </c>
-      <c r="AC46" s="13" t="inlineStr">
-        <is>
-          <t>NA (Tag에서 PV를 보고 Pressure Control Valve임을 유추)</t>
-        </is>
-      </c>
-      <c r="AD46" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE46" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF46" s="13" t="inlineStr">
-        <is>
-          <t>HS CRUDE</t>
-        </is>
-      </c>
-      <c r="AG46" s="13" t="inlineStr">
-        <is>
-          <t>Fluid</t>
-        </is>
-      </c>
-      <c r="AH46" s="13" t="inlineStr">
-        <is>
-          <t>LIQUID</t>
-        </is>
-      </c>
-      <c r="AI46" s="13" t="inlineStr">
-        <is>
-          <t>NA (FLUID NAME을 보고 유추)</t>
-        </is>
-      </c>
-      <c r="AJ46" s="13" t="inlineStr">
-        <is>
-          <t>553 m3/hr</t>
-        </is>
-      </c>
-      <c r="AK46" s="13" t="inlineStr">
-        <is>
-          <t>Flow Rate</t>
-        </is>
-      </c>
-      <c r="AL46" s="13" t="inlineStr">
-        <is>
-          <t>12 kg/cm2</t>
-        </is>
-      </c>
-      <c r="AM46" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Press.</t>
-        </is>
-      </c>
-      <c r="AN46" s="13" t="inlineStr">
-        <is>
-          <t>143 ℃</t>
-        </is>
-      </c>
-      <c r="AO46" s="13" t="inlineStr">
-        <is>
-          <t>Inlet Temp.</t>
-        </is>
-      </c>
-      <c r="AP46" s="13" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="AQ46" s="13" t="inlineStr">
-        <is>
-          <t>Density</t>
-        </is>
-      </c>
-      <c r="AR46" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS46" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT46" s="13" t="inlineStr">
-        <is>
-          <t>GLOBE</t>
-        </is>
-      </c>
-      <c r="AU46" s="13" t="inlineStr">
-        <is>
-          <t>Body Type</t>
-        </is>
-      </c>
-      <c r="AV46" s="13" t="inlineStr">
-        <is>
-          <t>ANSI CLASS 3</t>
-        </is>
-      </c>
-      <c r="AW46" s="13" t="inlineStr">
-        <is>
-          <t>Leakage Spec.</t>
-        </is>
-      </c>
-      <c r="AX46" s="13" t="inlineStr">
-        <is>
-          <t>EQ%</t>
-        </is>
-      </c>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Flow Characteristic</t>
-        </is>
-      </c>
-      <c r="AZ46" s="13" t="inlineStr">
-        <is>
-          <t>630SST</t>
-        </is>
-      </c>
-      <c r="BA46" s="13" t="inlineStr">
-        <is>
-          <t>Plug</t>
-        </is>
-      </c>
-      <c r="BB46" s="13" t="inlineStr">
-        <is>
-          <t>630SST</t>
-        </is>
-      </c>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Cage</t>
-        </is>
-      </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>410SST</t>
-        </is>
-      </c>
-      <c r="BE46" s="13" t="inlineStr">
-        <is>
-          <t>Seat Ring</t>
-        </is>
-      </c>
-      <c r="BF46" s="29" t="inlineStr">
-        <is>
-          <t>630SST</t>
-        </is>
-      </c>
-      <c r="BG46" s="13" t="inlineStr">
-        <is>
-          <t>Stem</t>
-        </is>
-      </c>
-      <c r="BH46" s="13" t="inlineStr">
-        <is>
-          <t>CYLINDER</t>
-        </is>
-      </c>
-      <c r="BI46" s="13" t="inlineStr">
-        <is>
-          <t>Actuator Type</t>
-        </is>
-      </c>
-      <c r="BJ46" s="13" t="inlineStr">
-        <is>
-          <t>MASONEILAN</t>
-        </is>
-      </c>
-      <c r="BK46" s="13" t="inlineStr">
-        <is>
-          <t>Model No.</t>
-        </is>
-      </c>
-      <c r="BL46" s="13" t="inlineStr">
-        <is>
-          <t>4280E</t>
-        </is>
-      </c>
-      <c r="BM46" s="13" t="inlineStr">
-        <is>
-          <t>Model No.</t>
-        </is>
-      </c>
-      <c r="BN46" s="13" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:BN32"/>
@@ -12500,13 +12313,13 @@
     <mergeCell ref="R1:S1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C3:C28 C31:C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"xlsx,xlsm,xls,pdf(텍스트),pdf(스캔),tif"</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D25 D27:D28 D31:D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D3:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"현행,레거시"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E25 E27:E28 E31:E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"datasheet,datasheet_embedded,out_of_scope"</formula1>
     </dataValidation>
   </dataValidations>

--- a/readme/labeling_kit.xlsx
+++ b/readme/labeling_kit.xlsx
@@ -262,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -311,6 +311,24 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FFC8CEDC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC8CEDC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFC8CEDC"/>
@@ -333,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -440,16 +458,6 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -465,6 +473,31 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1847,174 +1880,174 @@
           <t>문서 정보</t>
         </is>
       </c>
-      <c r="J1" s="42" t="inlineStr">
+      <c r="J1" s="53" t="inlineStr">
         <is>
           <t>ENGINEERING TAG NO.  ※안전</t>
         </is>
       </c>
-      <c r="K1" s="41" t="n"/>
-      <c r="L1" s="43" t="inlineStr">
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="54" t="inlineStr">
         <is>
           <t>MANUFACTURER</t>
         </is>
       </c>
-      <c r="M1" s="41" t="n"/>
-      <c r="N1" s="43" t="inlineStr">
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="54" t="inlineStr">
         <is>
           <t>MODEL NO.</t>
         </is>
       </c>
-      <c r="O1" s="41" t="n"/>
-      <c r="P1" s="43" t="inlineStr">
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="54" t="inlineStr">
         <is>
           <t>RATED CV</t>
         </is>
       </c>
-      <c r="Q1" s="41" t="n"/>
-      <c r="R1" s="43" t="inlineStr">
+      <c r="Q1" s="52" t="n"/>
+      <c r="R1" s="54" t="inlineStr">
         <is>
           <t>REQUIRED CV</t>
         </is>
       </c>
-      <c r="S1" s="41" t="n"/>
-      <c r="T1" s="43" t="inlineStr">
+      <c r="S1" s="52" t="n"/>
+      <c r="T1" s="54" t="inlineStr">
         <is>
           <t>VALVE BODY RATING</t>
         </is>
       </c>
-      <c r="U1" s="41" t="n"/>
-      <c r="V1" s="43" t="inlineStr">
+      <c r="U1" s="52" t="n"/>
+      <c r="V1" s="54" t="inlineStr">
         <is>
           <t>VALVE BODY SIZE</t>
         </is>
       </c>
-      <c r="W1" s="41" t="n"/>
-      <c r="X1" s="43" t="inlineStr">
+      <c r="W1" s="52" t="n"/>
+      <c r="X1" s="54" t="inlineStr">
         <is>
           <t>VALVE BODY MATERIAL</t>
         </is>
       </c>
-      <c r="Y1" s="41" t="n"/>
-      <c r="Z1" s="42" t="inlineStr">
+      <c r="Y1" s="52" t="n"/>
+      <c r="Z1" s="53" t="inlineStr">
         <is>
           <t>ACTUATOR FAIL ACTION  ※안전</t>
         </is>
       </c>
-      <c r="AA1" s="41" t="n"/>
-      <c r="AB1" s="40" t="inlineStr">
+      <c r="AA1" s="52" t="n"/>
+      <c r="AB1" s="51" t="inlineStr">
         <is>
           <t>· TYPE NAME</t>
         </is>
       </c>
-      <c r="AC1" s="41" t="n"/>
-      <c r="AD1" s="40" t="inlineStr">
+      <c r="AC1" s="52" t="n"/>
+      <c r="AD1" s="51" t="inlineStr">
         <is>
           <t>· EQUIPMENT FULL DESCRIPTION</t>
         </is>
       </c>
-      <c r="AE1" s="41" t="n"/>
-      <c r="AF1" s="40" t="inlineStr">
+      <c r="AE1" s="52" t="n"/>
+      <c r="AF1" s="51" t="inlineStr">
         <is>
           <t>· FLUID NAME</t>
         </is>
       </c>
-      <c r="AG1" s="41" t="n"/>
-      <c r="AH1" s="40" t="inlineStr">
+      <c r="AG1" s="52" t="n"/>
+      <c r="AH1" s="51" t="inlineStr">
         <is>
           <t>· FLUID STATE</t>
         </is>
       </c>
-      <c r="AI1" s="41" t="n"/>
-      <c r="AJ1" s="40" t="inlineStr">
+      <c r="AI1" s="52" t="n"/>
+      <c r="AJ1" s="51" t="inlineStr">
         <is>
           <t>· NORMAL FLOW RATE</t>
         </is>
       </c>
-      <c r="AK1" s="41" t="n"/>
-      <c r="AL1" s="40" t="inlineStr">
+      <c r="AK1" s="52" t="n"/>
+      <c r="AL1" s="51" t="inlineStr">
         <is>
           <t>· NORMAL PRESSURE</t>
         </is>
       </c>
-      <c r="AM1" s="41" t="n"/>
-      <c r="AN1" s="40" t="inlineStr">
+      <c r="AM1" s="52" t="n"/>
+      <c r="AN1" s="51" t="inlineStr">
         <is>
           <t>· NORMAL TEMPERATURE</t>
         </is>
       </c>
-      <c r="AO1" s="41" t="n"/>
-      <c r="AP1" s="40" t="inlineStr">
+      <c r="AO1" s="52" t="n"/>
+      <c r="AP1" s="51" t="inlineStr">
         <is>
           <t>· SPECIFIC GRAVITY</t>
         </is>
       </c>
-      <c r="AQ1" s="41" t="n"/>
-      <c r="AR1" s="40" t="inlineStr">
+      <c r="AQ1" s="52" t="n"/>
+      <c r="AR1" s="51" t="inlineStr">
         <is>
           <t>· VISCOSITY</t>
         </is>
       </c>
-      <c r="AS1" s="41" t="n"/>
-      <c r="AT1" s="40" t="inlineStr">
+      <c r="AS1" s="52" t="n"/>
+      <c r="AT1" s="51" t="inlineStr">
         <is>
           <t>· VALVE BODY TYPE</t>
         </is>
       </c>
-      <c r="AU1" s="41" t="n"/>
-      <c r="AV1" s="40" t="inlineStr">
+      <c r="AU1" s="52" t="n"/>
+      <c r="AV1" s="51" t="inlineStr">
         <is>
           <t>· VALVE LEAKAGE CLASS</t>
         </is>
       </c>
-      <c r="AW1" s="41" t="n"/>
-      <c r="AX1" s="40" t="inlineStr">
+      <c r="AW1" s="52" t="n"/>
+      <c r="AX1" s="51" t="inlineStr">
         <is>
           <t>· CHARACTERISTIC (TRIM FORM)</t>
         </is>
       </c>
-      <c r="AY1" s="41" t="n"/>
-      <c r="AZ1" s="40" t="inlineStr">
+      <c r="AY1" s="52" t="n"/>
+      <c r="AZ1" s="51" t="inlineStr">
         <is>
           <t>· VALVE PLUG MATERIAL</t>
         </is>
       </c>
-      <c r="BA1" s="41" t="n"/>
-      <c r="BB1" s="40" t="inlineStr">
+      <c r="BA1" s="52" t="n"/>
+      <c r="BB1" s="51" t="inlineStr">
         <is>
           <t>· VALVE CAGE MATERIAL</t>
         </is>
       </c>
-      <c r="BC1" s="41" t="n"/>
-      <c r="BD1" s="40" t="inlineStr">
+      <c r="BC1" s="52" t="n"/>
+      <c r="BD1" s="51" t="inlineStr">
         <is>
           <t>· VALVE SEAT MATERIAL</t>
         </is>
       </c>
-      <c r="BE1" s="41" t="n"/>
-      <c r="BF1" s="40" t="inlineStr">
+      <c r="BE1" s="52" t="n"/>
+      <c r="BF1" s="51" t="inlineStr">
         <is>
           <t>· VALVE STEM MATERIAL</t>
         </is>
       </c>
-      <c r="BG1" s="41" t="n"/>
-      <c r="BH1" s="40" t="inlineStr">
+      <c r="BG1" s="52" t="n"/>
+      <c r="BH1" s="51" t="inlineStr">
         <is>
           <t>· ACTUATOR TYPE</t>
         </is>
       </c>
-      <c r="BI1" s="41" t="n"/>
-      <c r="BJ1" s="40" t="inlineStr">
+      <c r="BI1" s="52" t="n"/>
+      <c r="BJ1" s="51" t="inlineStr">
         <is>
           <t>· POSITIONER MANUFACTURER</t>
         </is>
       </c>
-      <c r="BK1" s="41" t="n"/>
-      <c r="BL1" s="40" t="inlineStr">
+      <c r="BK1" s="52" t="n"/>
+      <c r="BL1" s="51" t="inlineStr">
         <is>
           <t>· POSITIONER MODEL NO.</t>
         </is>
       </c>
-      <c r="BM1" s="41" t="n"/>
+      <c r="BM1" s="52" t="n"/>
       <c r="BN1" s="8" t="inlineStr">
         <is>
           <t>비고</t>
@@ -2067,57 +2100,57 @@
           <t>소요(분)</t>
         </is>
       </c>
-      <c r="J2" s="42" t="inlineStr">
+      <c r="J2" s="53" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="K2" s="42" t="inlineStr">
+      <c r="K2" s="53" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="L2" s="43" t="inlineStr">
+      <c r="L2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="M2" s="43" t="inlineStr">
+      <c r="M2" s="54" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="N2" s="43" t="inlineStr">
+      <c r="N2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="O2" s="43" t="inlineStr">
+      <c r="O2" s="54" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="P2" s="43" t="inlineStr">
+      <c r="P2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="Q2" s="43" t="inlineStr">
+      <c r="Q2" s="54" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="R2" s="43" t="inlineStr">
+      <c r="R2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="S2" s="43" t="inlineStr">
+      <c r="S2" s="54" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="T2" s="43" t="inlineStr">
+      <c r="T2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
@@ -2127,222 +2160,222 @@
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="V2" s="43" t="inlineStr">
+      <c r="V2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="W2" s="43" t="inlineStr">
+      <c r="W2" s="54" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="X2" s="43" t="inlineStr">
+      <c r="X2" s="54" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="Y2" s="43" t="inlineStr">
+      <c r="Y2" s="54" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="Z2" s="42" t="inlineStr">
+      <c r="Z2" s="53" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AA2" s="42" t="inlineStr">
+      <c r="AA2" s="53" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AB2" s="40" t="inlineStr">
+      <c r="AB2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AC2" s="40" t="inlineStr">
+      <c r="AC2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AD2" s="40" t="inlineStr">
+      <c r="AD2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AE2" s="40" t="inlineStr">
+      <c r="AE2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AF2" s="40" t="inlineStr">
+      <c r="AF2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AG2" s="40" t="inlineStr">
+      <c r="AG2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AH2" s="40" t="inlineStr">
+      <c r="AH2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AI2" s="40" t="inlineStr">
+      <c r="AI2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AJ2" s="40" t="inlineStr">
+      <c r="AJ2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AK2" s="40" t="inlineStr">
+      <c r="AK2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AL2" s="40" t="inlineStr">
+      <c r="AL2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AM2" s="40" t="inlineStr">
+      <c r="AM2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AN2" s="40" t="inlineStr">
+      <c r="AN2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AO2" s="40" t="inlineStr">
+      <c r="AO2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AP2" s="40" t="inlineStr">
+      <c r="AP2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AQ2" s="40" t="inlineStr">
+      <c r="AQ2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AR2" s="40" t="inlineStr">
+      <c r="AR2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AS2" s="40" t="inlineStr">
+      <c r="AS2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AT2" s="40" t="inlineStr">
+      <c r="AT2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AU2" s="40" t="inlineStr">
+      <c r="AU2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AV2" s="40" t="inlineStr">
+      <c r="AV2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AW2" s="40" t="inlineStr">
+      <c r="AW2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AX2" s="40" t="inlineStr">
+      <c r="AX2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="AY2" s="40" t="inlineStr">
+      <c r="AY2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="AZ2" s="40" t="inlineStr">
+      <c r="AZ2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BA2" s="40" t="inlineStr">
+      <c r="BA2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="BB2" s="40" t="inlineStr">
+      <c r="BB2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BC2" s="40" t="inlineStr">
+      <c r="BC2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="BD2" s="40" t="inlineStr">
+      <c r="BD2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BE2" s="40" t="inlineStr">
+      <c r="BE2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="BF2" s="40" t="inlineStr">
+      <c r="BF2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BG2" s="40" t="inlineStr">
+      <c r="BG2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="BH2" s="40" t="inlineStr">
+      <c r="BH2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BI2" s="40" t="inlineStr">
+      <c r="BI2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="BJ2" s="40" t="inlineStr">
+      <c r="BJ2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BK2" s="40" t="inlineStr">
+      <c r="BK2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
       </c>
-      <c r="BL2" s="40" t="inlineStr">
+      <c r="BL2" s="51" t="inlineStr">
         <is>
           <t>정답값</t>
         </is>
       </c>
-      <c r="BM2" s="40" t="inlineStr">
+      <c r="BM2" s="51" t="inlineStr">
         <is>
           <t>원문라벨</t>
         </is>
@@ -3993,12 +4026,12 @@
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>FISHER</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>NA (Body Model 보고 유추)</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -5794,17 +5827,17 @@
       </c>
       <c r="BB13" s="13" t="inlineStr">
         <is>
-          <t>SUS440B</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="BC13" s="13" t="inlineStr">
         <is>
-          <t>MATERIAL Guide Bushing</t>
+          <t>Retainer or Cage</t>
         </is>
       </c>
       <c r="BD13" s="13" t="inlineStr">
         <is>
-          <t>SCS14A + STELLITE</t>
+          <t>SCS14A + STELL.</t>
         </is>
       </c>
       <c r="BE13" s="13" t="inlineStr">
@@ -8857,7 +8890,7 @@
       </c>
       <c r="AZ24" s="13" t="inlineStr">
         <is>
-          <t>CoCR-A</t>
+          <t>CoCr-A</t>
         </is>
       </c>
       <c r="BA24" s="13" t="inlineStr">
@@ -9257,325 +9290,325 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="48">
-      <c r="A26" s="44" t="inlineStr">
+    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="44">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>d024</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>10FV634-DATA SHEET_REV0.pdf</t>
         </is>
       </c>
-      <c r="C26" s="44" t="inlineStr">
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>pdf(텍스트)</t>
         </is>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D26" s="40" t="inlineStr">
         <is>
           <t>현행</t>
         </is>
       </c>
-      <c r="E26" s="44" t="inlineStr">
+      <c r="E26" s="40" t="inlineStr">
         <is>
           <t>datasheet</t>
         </is>
       </c>
-      <c r="F26" s="44" t="n">
+      <c r="F26" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="44" t="n">
+      <c r="G26" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="44" t="inlineStr">
+      <c r="H26" s="40" t="inlineStr">
         <is>
           <t>강민호</t>
         </is>
       </c>
-      <c r="I26" s="44" t="n">
+      <c r="I26" s="40" t="n">
         <v>35</v>
       </c>
-      <c r="J26" s="45" t="inlineStr">
+      <c r="J26" s="41" t="inlineStr">
         <is>
           <t>10-FV-634</t>
         </is>
       </c>
-      <c r="K26" s="45" t="inlineStr">
+      <c r="K26" s="41" t="inlineStr">
         <is>
           <t>Valve Tag #</t>
         </is>
       </c>
-      <c r="L26" s="45" t="inlineStr">
+      <c r="L26" s="41" t="inlineStr">
         <is>
           <t>FLOWSERVE</t>
         </is>
       </c>
-      <c r="M26" s="45" t="inlineStr">
+      <c r="M26" s="41" t="inlineStr">
         <is>
           <t>(좌측 상단 로고)</t>
         </is>
       </c>
-      <c r="N26" s="45" t="inlineStr">
+      <c r="N26" s="41" t="inlineStr">
         <is>
           <t>Mark One</t>
         </is>
       </c>
-      <c r="O26" s="45" t="inlineStr">
+      <c r="O26" s="41" t="inlineStr">
         <is>
           <t>Model / Body Type / Trim Type</t>
         </is>
       </c>
-      <c r="P26" s="45" t="n">
+      <c r="P26" s="41" t="n">
         <v>538</v>
       </c>
-      <c r="Q26" s="45" t="inlineStr">
+      <c r="Q26" s="41" t="inlineStr">
         <is>
           <t>Valve Body Assembly, Trim # - Cv</t>
         </is>
       </c>
-      <c r="R26" s="45" t="inlineStr">
+      <c r="R26" s="41" t="inlineStr">
         <is>
           <t>249.719</t>
         </is>
       </c>
-      <c r="S26" s="45" t="inlineStr">
+      <c r="S26" s="41" t="inlineStr">
         <is>
           <t>Calculated Data, Flow Coeff. (Cv), Nor</t>
         </is>
       </c>
-      <c r="T26" s="45" t="inlineStr">
+      <c r="T26" s="41" t="inlineStr">
         <is>
           <t>300#</t>
         </is>
       </c>
-      <c r="U26" s="45" t="inlineStr">
+      <c r="U26" s="41" t="inlineStr">
         <is>
           <t>Valve Body Assembly, Size/Pressure Class/Body Form</t>
         </is>
       </c>
-      <c r="V26" s="45" t="inlineStr">
+      <c r="V26" s="41" t="inlineStr">
         <is>
           <t>8"</t>
         </is>
       </c>
-      <c r="W26" s="45" t="inlineStr">
+      <c r="W26" s="41" t="inlineStr">
         <is>
           <t>Valve Body Assembly, Size/Pressure Class/Body Form</t>
         </is>
       </c>
-      <c r="X26" s="45" t="inlineStr">
+      <c r="X26" s="41" t="inlineStr">
         <is>
           <t>Cr-Mo C5; F5a</t>
         </is>
       </c>
-      <c r="Y26" s="45" t="inlineStr">
+      <c r="Y26" s="41" t="inlineStr">
         <is>
           <t>Valve Body Assembly, Body Matl / Bonnet Matl</t>
         </is>
       </c>
-      <c r="Z26" s="46" t="inlineStr">
+      <c r="Z26" s="42" t="inlineStr">
         <is>
           <t>FAIL OPEN</t>
         </is>
       </c>
-      <c r="AA26" s="45" t="inlineStr">
+      <c r="AA26" s="41" t="inlineStr">
         <is>
           <t>Actuator, Fail/Air-To</t>
         </is>
       </c>
-      <c r="AB26" s="45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AC26" s="45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AD26" s="45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AE26" s="45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AF26" s="45" t="inlineStr">
+      <c r="AB26" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC26" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD26" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE26" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF26" s="41" t="inlineStr">
         <is>
           <t>LS AR</t>
         </is>
       </c>
-      <c r="AG26" s="45" t="inlineStr">
+      <c r="AG26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, Process Fluid</t>
         </is>
       </c>
-      <c r="AH26" s="45" t="inlineStr">
+      <c r="AH26" s="41" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="AI26" s="45" t="inlineStr">
+      <c r="AI26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, Process Fluid</t>
         </is>
       </c>
-      <c r="AJ26" s="45" t="inlineStr">
+      <c r="AJ26" s="41" t="inlineStr">
         <is>
           <t>164332.000 kg/h</t>
         </is>
       </c>
-      <c r="AK26" s="45" t="inlineStr">
+      <c r="AK26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, Liq Flow Rate (kg/h), Nor</t>
         </is>
       </c>
-      <c r="AL26" s="45" t="inlineStr">
+      <c r="AL26" s="41" t="inlineStr">
         <is>
           <t>19.1 kg/cm2G</t>
         </is>
       </c>
-      <c r="AM26" s="45" t="inlineStr">
+      <c r="AM26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, Inlet Press, Nor</t>
         </is>
       </c>
-      <c r="AN26" s="45" t="inlineStr">
+      <c r="AN26" s="41" t="inlineStr">
         <is>
           <t>291.2 °C</t>
         </is>
       </c>
-      <c r="AO26" s="45" t="inlineStr">
+      <c r="AO26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, Temperature (°C), Nor</t>
         </is>
       </c>
-      <c r="AP26" s="45" t="inlineStr">
+      <c r="AP26" s="41" t="inlineStr">
         <is>
           <t>0.845</t>
         </is>
       </c>
-      <c r="AQ26" s="45" t="inlineStr">
+      <c r="AQ26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, SG-MW</t>
         </is>
       </c>
-      <c r="AR26" s="45" t="inlineStr">
+      <c r="AR26" s="41" t="inlineStr">
         <is>
           <t>Process Data For Control Valve Selection, 1.705</t>
         </is>
       </c>
-      <c r="AS26" s="45" t="inlineStr">
+      <c r="AS26" s="41" t="inlineStr">
         <is>
           <t>Viscosity (cP)</t>
         </is>
       </c>
-      <c r="AT26" s="45" t="inlineStr">
+      <c r="AT26" s="41" t="inlineStr">
         <is>
           <t>GLOBE</t>
         </is>
       </c>
-      <c r="AU26" s="45" t="inlineStr">
+      <c r="AU26" s="41" t="inlineStr">
         <is>
           <t>Valve Body Assembly, Model / Body Type / Trim Type</t>
         </is>
       </c>
-      <c r="AV26" s="47" t="inlineStr">
+      <c r="AV26" s="43" t="inlineStr">
         <is>
           <t>CLASS 4</t>
         </is>
       </c>
-      <c r="AW26" s="45" t="inlineStr">
+      <c r="AW26" s="41" t="inlineStr">
         <is>
           <t>Max Shutoff / Shutoff Class</t>
         </is>
       </c>
-      <c r="AX26" s="45" t="inlineStr">
+      <c r="AX26" s="41" t="inlineStr">
         <is>
           <t>EQUAL PERCENTAGE</t>
         </is>
       </c>
-      <c r="AY26" s="45" t="inlineStr">
+      <c r="AY26" s="41" t="inlineStr">
         <is>
           <t>Trim # - Characteristic</t>
         </is>
       </c>
-      <c r="AZ26" s="45" t="inlineStr">
+      <c r="AZ26" s="41" t="inlineStr">
         <is>
           <t>316 SS</t>
         </is>
       </c>
-      <c r="BA26" s="45" t="inlineStr">
+      <c r="BA26" s="41" t="inlineStr">
         <is>
           <t>Plug Mtl/ Facing|Treatment / Stem Cvr</t>
         </is>
       </c>
-      <c r="BB26" s="48" t="inlineStr">
+      <c r="BB26" s="44" t="inlineStr">
         <is>
           <t>316 SS</t>
         </is>
       </c>
-      <c r="BC26" s="45" t="inlineStr">
+      <c r="BC26" s="41" t="inlineStr">
         <is>
           <t>Seat Retainer Mtl</t>
         </is>
       </c>
-      <c r="BD26" s="45" t="inlineStr">
+      <c r="BD26" s="41" t="inlineStr">
         <is>
           <t>316 SS</t>
         </is>
       </c>
-      <c r="BE26" s="45" t="inlineStr">
+      <c r="BE26" s="41" t="inlineStr">
         <is>
           <t>Seat Ring Mtl/ Facing|Treatment</t>
         </is>
       </c>
-      <c r="BF26" s="46" t="inlineStr">
+      <c r="BF26" s="42" t="inlineStr">
         <is>
           <t>316 SS</t>
         </is>
       </c>
-      <c r="BG26" s="45" t="inlineStr">
+      <c r="BG26" s="41" t="inlineStr">
         <is>
           <t>Stem Mtl/ Facing|Treatment / Pilot Spr</t>
         </is>
       </c>
-      <c r="BH26" s="49" t="inlineStr">
+      <c r="BH26" s="45" t="inlineStr">
         <is>
           <t>CYLINDER</t>
         </is>
       </c>
-      <c r="BI26" s="45" t="inlineStr">
+      <c r="BI26" s="41" t="inlineStr">
         <is>
           <t>Act. Type</t>
         </is>
       </c>
-      <c r="BJ26" s="45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BK26" s="45" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BL26" s="48" t="inlineStr">
+      <c r="BJ26" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK26" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL26" s="44" t="inlineStr">
         <is>
           <t>Logix 3800 Series</t>
         </is>
       </c>
-      <c r="BM26" s="45" t="inlineStr">
+      <c r="BM26" s="41" t="inlineStr">
         <is>
           <t>Positioner Model</t>
         </is>
       </c>
-      <c r="BN26" s="45" t="inlineStr">
+      <c r="BN26" s="41" t="inlineStr">
         <is>
           <t>Cage정보가 없는걸 현재 Retainer로 받고있는게 많아서 고민 필요</t>
         </is>
@@ -9783,12 +9816,12 @@
       </c>
       <c r="AP27" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1.196 kg/m3</t>
         </is>
       </c>
       <c r="AQ27" s="13" t="inlineStr">
         <is>
-          <t>Specific Gravity 행 = 1.196 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+          <t>Specific Gravity 행에 손으로 'Density' 로 고쳐 씀 · Normal 열</t>
         </is>
       </c>
       <c r="AR27" s="13" t="inlineStr">
@@ -10109,12 +10142,12 @@
       </c>
       <c r="AP28" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4.95 kg/m3</t>
         </is>
       </c>
       <c r="AQ28" s="13" t="inlineStr">
         <is>
-          <t>Specific Gravity 행에 손으로 'Density' 로 고쳐 씀 · 4.95 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+          <t>Specific Gravity 행에 손으로 'Density' 로 고쳐 씀 · Normal 열</t>
         </is>
       </c>
       <c r="AR28" s="13" t="inlineStr">
@@ -10435,12 +10468,12 @@
       </c>
       <c r="AP29" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4.96 kg/m3</t>
         </is>
       </c>
       <c r="AQ29" s="13" t="inlineStr">
         <is>
-          <t>Specific Gravity 행 = 4.96 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+          <t>Specific Gravity 행에 손으로 'Density' 로 고쳐 씀 · Normal 열</t>
         </is>
       </c>
       <c r="AR29" s="13" t="inlineStr">
@@ -10667,7 +10700,7 @@
       </c>
       <c r="X30" s="13" t="inlineStr">
         <is>
-          <t>WCB Steel</t>
+          <t>Carbon Steel</t>
         </is>
       </c>
       <c r="Y30" s="13" t="inlineStr">
@@ -11399,12 +11432,12 @@
       </c>
       <c r="AP32" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4.95 kg/m3</t>
         </is>
       </c>
       <c r="AQ32" s="13" t="inlineStr">
         <is>
-          <t>'Density' 행 = 4.95 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+          <t>'Density | kg/m3' 행 · Normal 열 (xlsx)</t>
         </is>
       </c>
       <c r="AR32" s="13" t="inlineStr">
@@ -11668,9 +11701,9 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AE33" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="AE33" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
         </is>
       </c>
       <c r="AF33" s="13" t="inlineStr">
@@ -11725,12 +11758,12 @@
       </c>
       <c r="AP33" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6.97 kg/m3</t>
         </is>
       </c>
       <c r="AQ33" s="13" t="inlineStr">
         <is>
-          <t>Specific Gravity 행 = 6.97 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+          <t>Specific Gravity 행에 손으로 'Density' 로 고쳐 씀 · Normal 열</t>
         </is>
       </c>
       <c r="AR33" s="13" t="inlineStr">
@@ -12203,6 +12236,316 @@
           <t>11PV037-DATA SHEET_REV0.tif</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>이종수</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>11-PV-037</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NA(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>657-EWD</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Valve Coefficient Cg— 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>8798</v>
+      </c>
+      <c r="S38" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cg☒ = 1634 — 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U38" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Size and Type (6 X 4"로 되어있을경우 앞이 바디사이즈)</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>FAIL OPEN</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE38" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF38" s="46" t="inlineStr">
+        <is>
+          <t>STEAM</t>
+        </is>
+      </c>
+      <c r="AG38" s="46" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ38" s="13" t="inlineStr">
+        <is>
+          <t>14.000 kg/H</t>
+        </is>
+      </c>
+      <c r="AK38" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL38" s="13" t="inlineStr">
+        <is>
+          <t>10.5 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM38" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN38" s="13" t="inlineStr">
+        <is>
+          <t>243 ℃</t>
+        </is>
+      </c>
+      <c r="AO38" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ38" s="13" t="inlineStr">
+        <is>
+          <t>'Density' 행 = 4.95 kg/m3 — 비중 아님 — 밀도(kg/m3) 다</t>
+        </is>
+      </c>
+      <c r="AR38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT38" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU38" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV38" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW38" s="27" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX38" s="13" t="inlineStr">
+        <is>
+          <t>QUICK OPENING</t>
+        </is>
+      </c>
+      <c r="AY38" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ38" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BA38" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB38" s="13" t="inlineStr">
+        <is>
+          <t>316SST w/ENC</t>
+        </is>
+      </c>
+      <c r="BC38" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD38" s="13" t="inlineStr">
+        <is>
+          <t>316 SST</t>
+        </is>
+      </c>
+      <c r="BE38" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF38" s="29" t="inlineStr">
+        <is>
+          <t>std.</t>
+        </is>
+      </c>
+      <c r="BG38" s="13" t="inlineStr">
+        <is>
+          <t>MATERIAL, Stem</t>
+        </is>
+      </c>
+      <c r="BH38" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI38" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
+        </is>
+      </c>
+      <c r="BJ38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM38" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN38" s="38" t="inlineStr">
+        <is>
+          <t>Positioner 없는 타입</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -12215,6 +12558,312 @@
           <t>23PCV005-DATA SHEET_REV0.tif</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>이종수</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>23-PCV-005</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NA(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>620</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Full Opening Cg— 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Required Cg— 문서에 Cv 표기 없음 — Cg 로만 적혀 있다</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U39" s="27" t="inlineStr">
+        <is>
+          <t>End Connection Casting Rating</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>3/4"</t>
+        </is>
+      </c>
+      <c r="W39" s="13" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AB39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE39" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF39" s="46" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="AG39" s="46" t="inlineStr">
+        <is>
+          <t>Fluid</t>
+        </is>
+      </c>
+      <c r="AH39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ39" s="13" t="inlineStr">
+        <is>
+          <t>30 (MAX) Nm3/H</t>
+        </is>
+      </c>
+      <c r="AK39" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate</t>
+        </is>
+      </c>
+      <c r="AL39" s="13" t="inlineStr">
+        <is>
+          <t>7.0 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM39" s="27" t="inlineStr">
+        <is>
+          <t>In.Press.</t>
+        </is>
+      </c>
+      <c r="AN39" s="13" t="inlineStr">
+        <is>
+          <t>38 ℃</t>
+        </is>
+      </c>
+      <c r="AO39" s="13" t="inlineStr">
+        <is>
+          <t>Temp.</t>
+        </is>
+      </c>
+      <c r="AP39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU39" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW39" s="27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY39" s="38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ39" s="13" t="inlineStr">
+        <is>
+          <t>Aluminum/Nitrile</t>
+        </is>
+      </c>
+      <c r="BA39" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC39" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD39" s="13" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="BE39" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF39" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH39" s="13" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="BI39" s="13" t="inlineStr">
+        <is>
+          <t>Actuator - Type No.</t>
+        </is>
+      </c>
+      <c r="BJ39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM39" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN39" s="13" t="inlineStr">
+        <is>
+          <t>PCV는 제외 고민(별도 시스템으로 분리 고민)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -12227,6 +12876,314 @@
           <t>19FV064-DATA SHEET_REV0.tif</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tif</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>레거시</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>datasheet</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>이종수</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>19-FV-064</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NA(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>37-21114</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Valve Coefficient Cv</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S40" s="13" t="inlineStr">
+        <is>
+          <t>Req'd Flow Coeff., Cv, Normal</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2500#</t>
+        </is>
+      </c>
+      <c r="U40" s="27" t="inlineStr">
+        <is>
+          <t>End Connection/Flg. ANSI class</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1"</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Size and Type</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>WCB Steel</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Body, Material</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>FAIL OPEN</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Actuator, Air Fails Valve to</t>
+        </is>
+      </c>
+      <c r="AB40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD40" s="13" t="inlineStr">
+        <is>
+          <t>QUENCH GAS TO HC REACTOR RED No.1</t>
+        </is>
+      </c>
+      <c r="AE40" s="38" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="AF40" s="46" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="AG40" s="46" t="inlineStr">
+        <is>
+          <t>Flowing Media</t>
+        </is>
+      </c>
+      <c r="AH40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ40" s="13" t="inlineStr">
+        <is>
+          <t>9340 m3/hr</t>
+        </is>
+      </c>
+      <c r="AK40" s="13" t="inlineStr">
+        <is>
+          <t>Flow Rate, Give Units, Normal</t>
+        </is>
+      </c>
+      <c r="AL40" s="13" t="inlineStr">
+        <is>
+          <t>219.55 kg/cm2G</t>
+        </is>
+      </c>
+      <c r="AM40" s="27" t="inlineStr">
+        <is>
+          <t>Inlet Pressure, Normal</t>
+        </is>
+      </c>
+      <c r="AN40" s="13" t="inlineStr">
+        <is>
+          <t>82 ℃</t>
+        </is>
+      </c>
+      <c r="AO40" s="13" t="inlineStr">
+        <is>
+          <t>Inlet Temperature, Normal</t>
+        </is>
+      </c>
+      <c r="AP40" s="13" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AQ40" s="13" t="inlineStr">
+        <is>
+          <t>Specific Gravity</t>
+        </is>
+      </c>
+      <c r="AR40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT40" s="13" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU40" s="38" t="inlineStr">
+        <is>
+          <t>Body, Style</t>
+        </is>
+      </c>
+      <c r="AV40" s="13" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW40" s="27" t="inlineStr">
+        <is>
+          <t>Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX40" s="13" t="inlineStr">
+        <is>
+          <t>LINEAR</t>
+        </is>
+      </c>
+      <c r="AY40" s="38" t="inlineStr">
+        <is>
+          <t>Trim, Plug or Cage</t>
+        </is>
+      </c>
+      <c r="AZ40" s="13" t="inlineStr">
+        <is>
+          <t>CoCr-A</t>
+        </is>
+      </c>
+      <c r="BA40" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Valve Plug Material</t>
+        </is>
+      </c>
+      <c r="BB40" s="13" t="inlineStr">
+        <is>
+          <t>SUS 316 Cr.P1.</t>
+        </is>
+      </c>
+      <c r="BC40" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Cage and/or Bushing Material</t>
+        </is>
+      </c>
+      <c r="BD40" s="13" t="inlineStr">
+        <is>
+          <t>SUS 316/CoCr-A</t>
+        </is>
+      </c>
+      <c r="BE40" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Seat Ring Material</t>
+        </is>
+      </c>
+      <c r="BF40" s="29" t="inlineStr">
+        <is>
+          <t>std.</t>
+        </is>
+      </c>
+      <c r="BG40" s="13" t="inlineStr">
+        <is>
+          <t>Trim, Stem</t>
+        </is>
+      </c>
+      <c r="BH40" s="13" t="inlineStr">
+        <is>
+          <t>DIAPHRAGM</t>
+        </is>
+      </c>
+      <c r="BI40" s="29" t="inlineStr">
+        <is>
+          <t>Actuator, Style</t>
+        </is>
+      </c>
+      <c r="BJ40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN40" s="38" t="inlineStr">
+        <is>
+          <t>Positioner 없는 타입</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -12239,6 +13196,312 @@
           <t>070055_REV0.pdf</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>datasheet_embedded</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>이종수</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>B10-PV-1631A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Valve Tag #</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>FLOWSERVE</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>NA(좌측 상단 로고)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Mark One</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Valve Model</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Trim # - Cv</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>85.973</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Calculated Data, Flow Coeff. (Cv), Cond1</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U41" s="41" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Size/Pressure Rating/Type</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="W41" s="41" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Size/Pressure Rating</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Carbon Steel</t>
+        </is>
+      </c>
+      <c r="Y41" s="41" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Body Matl / Bonnet Matl</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA41" s="48" t="inlineStr">
+        <is>
+          <t>NA (Air to 만 써있음)</t>
+        </is>
+      </c>
+      <c r="AB41" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC41" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD41" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE41" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF41" s="49" t="inlineStr">
+        <is>
+          <t>Naphtha</t>
+        </is>
+      </c>
+      <c r="AG41" s="41" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Process Fluid</t>
+        </is>
+      </c>
+      <c r="AH41" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI41" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ41" s="41" t="inlineStr">
+        <is>
+          <t>100 m3h</t>
+        </is>
+      </c>
+      <c r="AK41" s="41" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Liq Flow Rate (kg/h), Cond1</t>
+        </is>
+      </c>
+      <c r="AL41" s="41" t="inlineStr">
+        <is>
+          <t>14.300 kg/cm2(g)</t>
+        </is>
+      </c>
+      <c r="AM41" s="41" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Inlet Press, Cond1</t>
+        </is>
+      </c>
+      <c r="AN41" s="41" t="n">
+        <v>204</v>
+      </c>
+      <c r="AO41" s="41" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, Temperature (?), Cond1</t>
+        </is>
+      </c>
+      <c r="AP41" s="41" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ41" s="41" t="inlineStr">
+        <is>
+          <t>Process Data For Control Valve Selection, SG-MW, Cond1</t>
+        </is>
+      </c>
+      <c r="AR41" s="41" t="inlineStr">
+        <is>
+          <t>0.380 cP</t>
+        </is>
+      </c>
+      <c r="AS41" s="41" t="inlineStr">
+        <is>
+          <t>Viscosity (cP)</t>
+        </is>
+      </c>
+      <c r="AT41" s="41" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU41" s="41" t="inlineStr">
+        <is>
+          <t>Valve Body Assembly, Model / Body Type / Trim Type</t>
+        </is>
+      </c>
+      <c r="AV41" s="43" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW41" s="41" t="inlineStr">
+        <is>
+          <t>Max Shutoff / Shutoff Class</t>
+        </is>
+      </c>
+      <c r="AX41" s="41" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY41" s="41" t="inlineStr">
+        <is>
+          <t>Trim # - Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ41" s="41" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BA41" s="41" t="inlineStr">
+        <is>
+          <t>Plug Mtl/ Facing</t>
+        </is>
+      </c>
+      <c r="BB41" s="44" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BC41" s="41" t="inlineStr">
+        <is>
+          <t>Seat Retainer Mtl</t>
+        </is>
+      </c>
+      <c r="BD41" s="41" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="BE41" s="41" t="inlineStr">
+        <is>
+          <t>Seat Ring Mtl/ Facing</t>
+        </is>
+      </c>
+      <c r="BF41" s="42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG41" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH41" s="45" t="inlineStr">
+        <is>
+          <t>CYLINDER</t>
+        </is>
+      </c>
+      <c r="BI41" s="41" t="inlineStr">
+        <is>
+          <t>Act. Type</t>
+        </is>
+      </c>
+      <c r="BJ41" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK41" s="41" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL41" s="44" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="BM41" s="41" t="inlineStr">
+        <is>
+          <t>Positioner, Model</t>
+        </is>
+      </c>
+      <c r="BN41" s="41" t="inlineStr">
+        <is>
+          <t>Cage정보가 없는걸 현재 Retainer로 받고있는게 많아서 고민 필요</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -12249,6 +13512,318 @@
       <c r="B42" t="inlineStr">
         <is>
           <t>B10LV1073-DATA SHEET_REV1.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>현행</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>datasheet_embedded</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>이종수</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10-LV-01073</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>TAG NO</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Rated Cv</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>300#</t>
+        </is>
+      </c>
+      <c r="U42" s="47" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Body Size(4" X 2.62"로 되어있을 경우 앞이 Body Size)</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A216 Gr-WCB</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Body Material</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>FAIL CLOSE</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Fail Position</t>
+        </is>
+      </c>
+      <c r="AB42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AD42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AE42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AF42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AG42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AH42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AI42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AJ42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AK42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AL42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AM42" s="47" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AP42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AR42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT42" s="49" t="inlineStr">
+        <is>
+          <t>GLOBE</t>
+        </is>
+      </c>
+      <c r="AU42" s="49" t="inlineStr">
+        <is>
+          <t>Body Model(Type)</t>
+        </is>
+      </c>
+      <c r="AV42" s="49" t="inlineStr">
+        <is>
+          <t>CLASS 4</t>
+        </is>
+      </c>
+      <c r="AW42" s="47" t="inlineStr">
+        <is>
+          <t>Leakage Spec.</t>
+        </is>
+      </c>
+      <c r="AX42" s="49" t="inlineStr">
+        <is>
+          <t>EQUAL PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="AY42" s="49" t="inlineStr">
+        <is>
+          <t>Characteristic</t>
+        </is>
+      </c>
+      <c r="AZ42" s="49" t="inlineStr">
+        <is>
+          <t>316SS STELLITE</t>
+        </is>
+      </c>
+      <c r="BA42" s="49" t="inlineStr">
+        <is>
+          <t>Plug Material</t>
+        </is>
+      </c>
+      <c r="BB42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC42" s="49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD42" s="49" t="inlineStr">
+        <is>
+          <t>316SS STELLITE</t>
+        </is>
+      </c>
+      <c r="BE42" s="49" t="inlineStr">
+        <is>
+          <t>Seat Material</t>
+        </is>
+      </c>
+      <c r="BF42" s="50" t="inlineStr">
+        <is>
+          <t>316SST</t>
+        </is>
+      </c>
+      <c r="BG42" s="49" t="inlineStr">
+        <is>
+          <t>NRETROFIT ACTIONS 2. 4)</t>
+        </is>
+      </c>
+      <c r="BH42" s="49" t="inlineStr">
+        <is>
+          <t>CYLINDER</t>
+        </is>
+      </c>
+      <c r="BI42" s="49" t="inlineStr">
+        <is>
+          <t>Actuator Type</t>
+        </is>
+      </c>
+      <c r="BJ42" s="49" t="inlineStr">
+        <is>
+          <t>FLOWSERVE</t>
+        </is>
+      </c>
+      <c r="BK42" s="49" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="BL42" s="49" t="inlineStr">
+        <is>
+          <t>I/P 2000 E/P</t>
+        </is>
+      </c>
+      <c r="BM42" s="49" t="inlineStr">
+        <is>
+          <t>Positioner</t>
+        </is>
+      </c>
+      <c r="BN42" s="49" t="inlineStr">
+        <is>
+          <t>Manufacturer가 없는데 포지셔너 제조사만 써있어서 햇갈릴수있음</t>
         </is>
       </c>
     </row>
